--- a/ai収集/機種一覧_MY_コイン単価.xlsx
+++ b/ai収集/機種一覧_MY_コイン単価.xlsx
@@ -1083,9 +1083,13 @@
       <c r="K3" s="38" t="n">
         <v>3.2</v>
       </c>
-      <c r="L3" s="39" t="n"/>
+      <c r="L3" s="39" t="n">
+        <v>1860</v>
+      </c>
       <c r="M3" s="40" t="n"/>
-      <c r="N3" s="41" t="n"/>
+      <c r="N3" s="41" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
@@ -1133,9 +1137,13 @@
       <c r="K4" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L4" s="45" t="n"/>
+      <c r="L4" s="45" t="n">
+        <v>3926</v>
+      </c>
       <c r="M4" s="46" t="n"/>
-      <c r="N4" s="47" t="n"/>
+      <c r="N4" s="47" t="n">
+        <v>97.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
@@ -1183,9 +1191,13 @@
       <c r="K5" s="38" t="n">
         <v>7.2</v>
       </c>
-      <c r="L5" s="39" t="n"/>
+      <c r="L5" s="39" t="n">
+        <v>8400</v>
+      </c>
       <c r="M5" s="40" t="n"/>
-      <c r="N5" s="41" t="n"/>
+      <c r="N5" s="41" t="n">
+        <v>98.09999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
@@ -1223,9 +1235,13 @@
       <c r="I6" s="44" t="n"/>
       <c r="J6" s="44" t="n"/>
       <c r="K6" s="44" t="n"/>
-      <c r="L6" s="44" t="n"/>
+      <c r="L6" s="44" t="n">
+        <v>2791</v>
+      </c>
       <c r="M6" s="44" t="n"/>
-      <c r="N6" s="44" t="n"/>
+      <c r="N6" s="44" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="36" t="inlineStr">
@@ -1259,9 +1275,13 @@
       <c r="I7" s="38" t="n"/>
       <c r="J7" s="38" t="n"/>
       <c r="K7" s="38" t="n"/>
-      <c r="L7" s="38" t="n"/>
+      <c r="L7" s="38" t="n">
+        <v>3471</v>
+      </c>
       <c r="M7" s="38" t="n"/>
-      <c r="N7" s="38" t="n"/>
+      <c r="N7" s="38" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="42" t="inlineStr">
@@ -1299,9 +1319,13 @@
       <c r="I8" s="45" t="n"/>
       <c r="J8" s="44" t="n"/>
       <c r="K8" s="44" t="n"/>
-      <c r="L8" s="45" t="n"/>
+      <c r="L8" s="45" t="n">
+        <v>1570</v>
+      </c>
       <c r="M8" s="46" t="n"/>
-      <c r="N8" s="47" t="n"/>
+      <c r="N8" s="47" t="n">
+        <v>98.09999999999999</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="36" t="inlineStr">
@@ -1349,9 +1373,13 @@
       <c r="K9" s="38" t="n">
         <v>2.6</v>
       </c>
-      <c r="L9" s="38" t="n"/>
+      <c r="L9" s="38" t="n">
+        <v>2664</v>
+      </c>
       <c r="M9" s="38" t="n"/>
-      <c r="N9" s="38" t="n"/>
+      <c r="N9" s="38" t="n">
+        <v>97.90000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="42" t="inlineStr">
@@ -1395,9 +1423,13 @@
       <c r="K10" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L10" s="45" t="n"/>
+      <c r="L10" s="45" t="n">
+        <v>10993</v>
+      </c>
       <c r="M10" s="46" t="n"/>
-      <c r="N10" s="47" t="n"/>
+      <c r="N10" s="47" t="n">
+        <v>98.59999999999999</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="36" t="inlineStr">
@@ -1435,9 +1467,13 @@
       <c r="I11" s="39" t="n"/>
       <c r="J11" s="38" t="n"/>
       <c r="K11" s="38" t="n"/>
-      <c r="L11" s="39" t="n"/>
+      <c r="L11" s="39" t="n">
+        <v>9815</v>
+      </c>
       <c r="M11" s="40" t="n"/>
-      <c r="N11" s="41" t="n"/>
+      <c r="N11" s="41" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="42" t="inlineStr">
@@ -1485,9 +1521,13 @@
       <c r="K12" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="L12" s="44" t="n"/>
+      <c r="L12" s="44" t="n">
+        <v>3044</v>
+      </c>
       <c r="M12" s="44" t="n"/>
-      <c r="N12" s="44" t="n"/>
+      <c r="N12" s="44" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="36" t="inlineStr">
@@ -1535,9 +1575,13 @@
       <c r="K13" s="38" t="n">
         <v>2.7</v>
       </c>
-      <c r="L13" s="38" t="n"/>
+      <c r="L13" s="38" t="n">
+        <v>5667</v>
+      </c>
       <c r="M13" s="38" t="n"/>
-      <c r="N13" s="38" t="n"/>
+      <c r="N13" s="38" t="n">
+        <v>98.90000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="42" t="inlineStr">
@@ -1585,9 +1629,13 @@
       <c r="K14" s="44" t="n">
         <v>2.7</v>
       </c>
-      <c r="L14" s="45" t="n"/>
+      <c r="L14" s="45" t="n">
+        <v>2943</v>
+      </c>
       <c r="M14" s="46" t="n"/>
-      <c r="N14" s="47" t="n"/>
+      <c r="N14" s="47" t="n">
+        <v>97.90000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
@@ -1625,9 +1673,13 @@
       <c r="I15" s="39" t="n"/>
       <c r="J15" s="38" t="n"/>
       <c r="K15" s="38" t="n"/>
-      <c r="L15" s="39" t="n"/>
+      <c r="L15" s="39" t="n">
+        <v>4207</v>
+      </c>
       <c r="M15" s="40" t="n"/>
-      <c r="N15" s="41" t="n"/>
+      <c r="N15" s="41" t="n">
+        <v>98.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="42" t="inlineStr">
@@ -1675,9 +1727,13 @@
       <c r="K16" s="44" t="n">
         <v>2.8</v>
       </c>
-      <c r="L16" s="44" t="n"/>
+      <c r="L16" s="44" t="n">
+        <v>5784</v>
+      </c>
       <c r="M16" s="44" t="n"/>
-      <c r="N16" s="44" t="n"/>
+      <c r="N16" s="44" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="36" t="inlineStr">
@@ -1767,9 +1823,13 @@
       <c r="K18" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="44" t="n"/>
+      <c r="L18" s="44" t="n">
+        <v>4989</v>
+      </c>
       <c r="M18" s="44" t="n"/>
-      <c r="N18" s="44" t="n"/>
+      <c r="N18" s="44" t="n">
+        <v>98.40000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="36" t="inlineStr">
@@ -1817,9 +1877,13 @@
       <c r="K19" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="39" t="n"/>
+      <c r="L19" s="39" t="n">
+        <v>4001</v>
+      </c>
       <c r="M19" s="40" t="n"/>
-      <c r="N19" s="41" t="n"/>
+      <c r="N19" s="41" t="n">
+        <v>98.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="42" t="inlineStr">
@@ -1867,9 +1931,13 @@
       <c r="K20" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="L20" s="45" t="n"/>
+      <c r="L20" s="45" t="n">
+        <v>3270</v>
+      </c>
       <c r="M20" s="46" t="n"/>
-      <c r="N20" s="47" t="n"/>
+      <c r="N20" s="47" t="n">
+        <v>98.90000000000001</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="36" t="inlineStr">
@@ -1913,9 +1981,13 @@
       <c r="K21" s="38" t="n">
         <v>4.5</v>
       </c>
-      <c r="L21" s="39" t="n"/>
+      <c r="L21" s="39" t="n">
+        <v>5120</v>
+      </c>
       <c r="M21" s="40" t="n"/>
-      <c r="N21" s="41" t="n"/>
+      <c r="N21" s="41" t="n">
+        <v>98.59999999999999</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="42" t="inlineStr">
@@ -1963,9 +2035,13 @@
       <c r="K22" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L22" s="45" t="n"/>
+      <c r="L22" s="45" t="n">
+        <v>3609</v>
+      </c>
       <c r="M22" s="46" t="n"/>
-      <c r="N22" s="47" t="n"/>
+      <c r="N22" s="47" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="36" t="inlineStr">
@@ -2013,9 +2089,13 @@
       <c r="K23" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="L23" s="39" t="n"/>
+      <c r="L23" s="39" t="n">
+        <v>3286</v>
+      </c>
       <c r="M23" s="40" t="n"/>
-      <c r="N23" s="41" t="n"/>
+      <c r="N23" s="41" t="n">
+        <v>97.8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
@@ -2053,9 +2133,13 @@
       <c r="I24" s="44" t="n"/>
       <c r="J24" s="44" t="n"/>
       <c r="K24" s="44" t="n"/>
-      <c r="L24" s="45" t="n"/>
+      <c r="L24" s="45" t="n">
+        <v>10912</v>
+      </c>
       <c r="M24" s="46" t="n"/>
-      <c r="N24" s="47" t="n"/>
+      <c r="N24" s="47" t="n">
+        <v>99.59999999999999</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="36" t="inlineStr">
@@ -2099,9 +2183,13 @@
       <c r="K25" s="38" t="n">
         <v>2.7</v>
       </c>
-      <c r="L25" s="39" t="n"/>
+      <c r="L25" s="39" t="n">
+        <v>4298</v>
+      </c>
       <c r="M25" s="40" t="n"/>
-      <c r="N25" s="41" t="n"/>
+      <c r="N25" s="41" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="42" t="inlineStr">
@@ -2149,9 +2237,13 @@
       <c r="K26" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L26" s="45" t="n"/>
+      <c r="L26" s="45" t="n">
+        <v>5037</v>
+      </c>
       <c r="M26" s="46" t="n"/>
-      <c r="N26" s="47" t="n"/>
+      <c r="N26" s="47" t="n">
+        <v>96.2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
@@ -2199,9 +2291,13 @@
       <c r="K27" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="L27" s="38" t="n"/>
+      <c r="L27" s="38" t="n">
+        <v>4989</v>
+      </c>
       <c r="M27" s="38" t="n"/>
-      <c r="N27" s="38" t="n"/>
+      <c r="N27" s="38" t="n">
+        <v>98.09999999999999</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
@@ -2249,9 +2345,13 @@
       <c r="K28" s="44" t="n">
         <v>2.4</v>
       </c>
-      <c r="L28" s="45" t="n"/>
+      <c r="L28" s="45" t="n">
+        <v>3511</v>
+      </c>
       <c r="M28" s="46" t="n"/>
-      <c r="N28" s="47" t="n"/>
+      <c r="N28" s="47" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="36" t="inlineStr">
@@ -2299,9 +2399,13 @@
       <c r="K29" s="38" t="n">
         <v>2.9</v>
       </c>
-      <c r="L29" s="39" t="n"/>
+      <c r="L29" s="39" t="n">
+        <v>3612</v>
+      </c>
       <c r="M29" s="40" t="n"/>
-      <c r="N29" s="41" t="n"/>
+      <c r="N29" s="41" t="n">
+        <v>98.2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="42" t="inlineStr">
@@ -2461,9 +2565,13 @@
       <c r="K32" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="45" t="n"/>
+      <c r="L32" s="45" t="n">
+        <v>5301</v>
+      </c>
       <c r="M32" s="46" t="n"/>
-      <c r="N32" s="47" t="n"/>
+      <c r="N32" s="47" t="n">
+        <v>100.1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="36" t="inlineStr">
@@ -2551,9 +2659,13 @@
       <c r="K34" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="45" t="n"/>
+      <c r="L34" s="45" t="n">
+        <v>6844</v>
+      </c>
       <c r="M34" s="46" t="n"/>
-      <c r="N34" s="47" t="n"/>
+      <c r="N34" s="47" t="n">
+        <v>99.09999999999999</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="36" t="inlineStr">
@@ -2601,9 +2713,13 @@
       <c r="K35" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L35" s="39" t="n"/>
+      <c r="L35" s="39" t="n">
+        <v>6909</v>
+      </c>
       <c r="M35" s="40" t="n"/>
-      <c r="N35" s="41" t="n"/>
+      <c r="N35" s="41" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="42" t="inlineStr">
@@ -2651,9 +2767,13 @@
       <c r="K36" s="44" t="n">
         <v>2.7</v>
       </c>
-      <c r="L36" s="45" t="n"/>
+      <c r="L36" s="45" t="n">
+        <v>7853</v>
+      </c>
       <c r="M36" s="46" t="n"/>
-      <c r="N36" s="47" t="n"/>
+      <c r="N36" s="47" t="n">
+        <v>99.3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="36" t="inlineStr">
@@ -2697,9 +2817,13 @@
       <c r="K37" s="38" t="n">
         <v>3.5</v>
       </c>
-      <c r="L37" s="39" t="n"/>
+      <c r="L37" s="39" t="n">
+        <v>3030</v>
+      </c>
       <c r="M37" s="40" t="n"/>
-      <c r="N37" s="41" t="n"/>
+      <c r="N37" s="41" t="n">
+        <v>97.90000000000001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="42" t="inlineStr">
@@ -2747,9 +2871,13 @@
       <c r="K38" s="44" t="n">
         <v>2.5</v>
       </c>
-      <c r="L38" s="45" t="n"/>
+      <c r="L38" s="45" t="n">
+        <v>4242</v>
+      </c>
       <c r="M38" s="46" t="n"/>
-      <c r="N38" s="47" t="n"/>
+      <c r="N38" s="47" t="n">
+        <v>98.09999999999999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
@@ -2797,9 +2925,13 @@
       <c r="K39" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L39" s="38" t="n"/>
+      <c r="L39" s="38" t="n">
+        <v>3233</v>
+      </c>
       <c r="M39" s="38" t="n"/>
-      <c r="N39" s="38" t="n"/>
+      <c r="N39" s="38" t="n">
+        <v>98.09999999999999</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="42" t="inlineStr">
@@ -2843,9 +2975,13 @@
       <c r="K40" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L40" s="45" t="n"/>
+      <c r="L40" s="45" t="n">
+        <v>6719</v>
+      </c>
       <c r="M40" s="46" t="n"/>
-      <c r="N40" s="47" t="n"/>
+      <c r="N40" s="47" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="36" t="inlineStr">
@@ -2891,9 +3027,13 @@
       <c r="K41" s="38" t="n">
         <v>0.1</v>
       </c>
-      <c r="L41" s="39" t="n"/>
+      <c r="L41" s="39" t="n">
+        <v>6917</v>
+      </c>
       <c r="M41" s="40" t="n"/>
-      <c r="N41" s="41" t="n"/>
+      <c r="N41" s="41" t="n">
+        <v>99.8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="42" t="inlineStr">
@@ -2941,9 +3081,13 @@
       <c r="K42" s="44" t="n">
         <v>2.7</v>
       </c>
-      <c r="L42" s="45" t="n"/>
+      <c r="L42" s="45" t="n">
+        <v>4486</v>
+      </c>
       <c r="M42" s="46" t="n"/>
-      <c r="N42" s="47" t="n"/>
+      <c r="N42" s="47" t="n">
+        <v>98.2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="36" t="inlineStr">
@@ -2991,9 +3135,13 @@
       <c r="K43" s="38" t="n">
         <v>2.8</v>
       </c>
-      <c r="L43" s="39" t="n"/>
+      <c r="L43" s="39" t="n">
+        <v>2675</v>
+      </c>
       <c r="M43" s="40" t="n"/>
-      <c r="N43" s="41" t="n"/>
+      <c r="N43" s="41" t="n">
+        <v>98.40000000000001</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="42" t="inlineStr">
@@ -3041,9 +3189,13 @@
       <c r="K44" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L44" s="45" t="n"/>
+      <c r="L44" s="45" t="n">
+        <v>3653</v>
+      </c>
       <c r="M44" s="46" t="n"/>
-      <c r="N44" s="47" t="n"/>
+      <c r="N44" s="47" t="n">
+        <v>98.40000000000001</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="36" t="inlineStr">
@@ -3085,9 +3237,13 @@
       <c r="K45" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="39" t="n"/>
+      <c r="L45" s="39" t="n">
+        <v>10189</v>
+      </c>
       <c r="M45" s="40" t="n"/>
-      <c r="N45" s="41" t="n"/>
+      <c r="N45" s="41" t="n">
+        <v>100.1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="42" t="inlineStr">
@@ -3135,9 +3291,13 @@
       <c r="K46" s="44" t="n">
         <v>2.5</v>
       </c>
-      <c r="L46" s="45" t="n"/>
+      <c r="L46" s="45" t="n">
+        <v>3578</v>
+      </c>
       <c r="M46" s="46" t="n"/>
-      <c r="N46" s="47" t="n"/>
+      <c r="N46" s="47" t="n">
+        <v>98.3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="36" t="inlineStr">
@@ -3175,9 +3335,13 @@
       <c r="I47" s="39" t="n"/>
       <c r="J47" s="38" t="n"/>
       <c r="K47" s="38" t="n"/>
-      <c r="L47" s="39" t="n"/>
+      <c r="L47" s="39" t="n">
+        <v>11235</v>
+      </c>
       <c r="M47" s="40" t="n"/>
-      <c r="N47" s="41" t="n"/>
+      <c r="N47" s="41" t="n">
+        <v>99.3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="42" t="inlineStr">
@@ -3221,9 +3385,13 @@
       <c r="K48" s="44" t="n">
         <v>2.7</v>
       </c>
-      <c r="L48" s="45" t="n"/>
+      <c r="L48" s="45" t="n">
+        <v>6169</v>
+      </c>
       <c r="M48" s="46" t="n"/>
-      <c r="N48" s="47" t="n"/>
+      <c r="N48" s="47" t="n">
+        <v>99.5</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="36" t="inlineStr">
@@ -3321,9 +3489,13 @@
       <c r="K50" s="44" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L50" s="45" t="n"/>
+      <c r="L50" s="45" t="n">
+        <v>7534</v>
+      </c>
       <c r="M50" s="46" t="n"/>
-      <c r="N50" s="47" t="n"/>
+      <c r="N50" s="47" t="n">
+        <v>99.59999999999999</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="36" t="inlineStr">
@@ -3371,9 +3543,13 @@
       <c r="K51" s="38" t="n">
         <v>6.1</v>
       </c>
-      <c r="L51" s="39" t="n"/>
+      <c r="L51" s="39" t="n">
+        <v>7643</v>
+      </c>
       <c r="M51" s="40" t="n"/>
-      <c r="N51" s="41" t="n"/>
+      <c r="N51" s="41" t="n">
+        <v>100.2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="42" t="inlineStr">
@@ -3421,9 +3597,13 @@
       <c r="K52" s="44" t="n">
         <v>3.1</v>
       </c>
-      <c r="L52" s="45" t="n"/>
+      <c r="L52" s="45" t="n">
+        <v>2763</v>
+      </c>
       <c r="M52" s="46" t="n"/>
-      <c r="N52" s="47" t="n"/>
+      <c r="N52" s="47" t="n">
+        <v>99.8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="36" t="inlineStr">
@@ -3467,9 +3647,13 @@
       <c r="K53" s="38" t="n">
         <v>1.1</v>
       </c>
-      <c r="L53" s="39" t="n"/>
+      <c r="L53" s="39" t="n">
+        <v>5430</v>
+      </c>
       <c r="M53" s="40" t="n"/>
-      <c r="N53" s="41" t="n"/>
+      <c r="N53" s="41" t="n">
+        <v>99.8</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="42" t="inlineStr">
@@ -3517,9 +3701,13 @@
       <c r="K54" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="L54" s="45" t="n"/>
+      <c r="L54" s="45" t="n">
+        <v>6031</v>
+      </c>
       <c r="M54" s="46" t="n"/>
-      <c r="N54" s="47" t="n"/>
+      <c r="N54" s="47" t="n">
+        <v>98.2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="36" t="inlineStr">
@@ -3563,9 +3751,13 @@
       <c r="K55" s="38" t="n">
         <v>2.8</v>
       </c>
-      <c r="L55" s="39" t="n"/>
+      <c r="L55" s="39" t="n">
+        <v>3356</v>
+      </c>
       <c r="M55" s="40" t="n"/>
-      <c r="N55" s="41" t="n"/>
+      <c r="N55" s="41" t="n">
+        <v>97.7</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="42" t="inlineStr">
@@ -3613,9 +3805,13 @@
       <c r="K56" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="L56" s="44" t="n"/>
+      <c r="L56" s="44" t="n">
+        <v>7360</v>
+      </c>
       <c r="M56" s="44" t="n"/>
-      <c r="N56" s="44" t="n"/>
+      <c r="N56" s="44" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="36" t="inlineStr">
@@ -3663,9 +3859,13 @@
       <c r="K57" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="L57" s="39" t="n"/>
+      <c r="L57" s="39" t="n">
+        <v>6157</v>
+      </c>
       <c r="M57" s="40" t="n"/>
-      <c r="N57" s="41" t="n"/>
+      <c r="N57" s="41" t="n">
+        <v>98.2</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="42" t="inlineStr">
@@ -3709,9 +3909,13 @@
       <c r="K58" s="44" t="n">
         <v>3.2</v>
       </c>
-      <c r="L58" s="45" t="n"/>
+      <c r="L58" s="45" t="n">
+        <v>5628</v>
+      </c>
       <c r="M58" s="46" t="n"/>
-      <c r="N58" s="47" t="n"/>
+      <c r="N58" s="47" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="36" t="inlineStr">
@@ -3759,9 +3963,13 @@
       <c r="K59" s="38" t="n">
         <v>2.8</v>
       </c>
-      <c r="L59" s="39" t="n"/>
+      <c r="L59" s="39" t="n">
+        <v>3531</v>
+      </c>
       <c r="M59" s="40" t="n"/>
-      <c r="N59" s="41" t="n"/>
+      <c r="N59" s="41" t="n">
+        <v>98.90000000000001</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="42" t="inlineStr">
@@ -3807,9 +4015,13 @@
       <c r="K60" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="L60" s="45" t="n"/>
+      <c r="L60" s="45" t="n">
+        <v>6782</v>
+      </c>
       <c r="M60" s="46" t="n"/>
-      <c r="N60" s="47" t="n"/>
+      <c r="N60" s="47" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="36" t="inlineStr">
@@ -3855,9 +4067,13 @@
       <c r="K61" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L61" s="39" t="n"/>
+      <c r="L61" s="39" t="n">
+        <v>10308</v>
+      </c>
       <c r="M61" s="40" t="n"/>
-      <c r="N61" s="41" t="n"/>
+      <c r="N61" s="41" t="n">
+        <v>99.09999999999999</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="42" t="inlineStr">
@@ -3905,9 +4121,13 @@
       <c r="K62" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="L62" s="44" t="n"/>
+      <c r="L62" s="44" t="n">
+        <v>4901</v>
+      </c>
       <c r="M62" s="44" t="n"/>
-      <c r="N62" s="44" t="n"/>
+      <c r="N62" s="44" t="n">
+        <v>97.8</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="36" t="inlineStr">
@@ -3955,9 +4175,13 @@
       <c r="K63" s="38" t="n">
         <v>2.5</v>
       </c>
-      <c r="L63" s="39" t="n"/>
+      <c r="L63" s="39" t="n">
+        <v>5554</v>
+      </c>
       <c r="M63" s="40" t="n"/>
-      <c r="N63" s="41" t="n"/>
+      <c r="N63" s="41" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="42" t="inlineStr">
@@ -4005,9 +4229,13 @@
       <c r="K64" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L64" s="45" t="n"/>
+      <c r="L64" s="45" t="n">
+        <v>5574</v>
+      </c>
       <c r="M64" s="46" t="n"/>
-      <c r="N64" s="47" t="n"/>
+      <c r="N64" s="47" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="36" t="inlineStr">
@@ -4055,9 +4283,13 @@
       <c r="K65" s="38" t="n">
         <v>3.3</v>
       </c>
-      <c r="L65" s="39" t="n"/>
+      <c r="L65" s="39" t="n">
+        <v>6631</v>
+      </c>
       <c r="M65" s="40" t="n"/>
-      <c r="N65" s="41" t="n"/>
+      <c r="N65" s="41" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="42" t="inlineStr">
@@ -4105,9 +4337,13 @@
       <c r="K66" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="L66" s="45" t="n"/>
+      <c r="L66" s="45" t="n">
+        <v>2503</v>
+      </c>
       <c r="M66" s="46" t="n"/>
-      <c r="N66" s="47" t="n"/>
+      <c r="N66" s="47" t="n">
+        <v>98.59999999999999</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="36" t="inlineStr">
@@ -4155,9 +4391,13 @@
       <c r="K67" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L67" s="38" t="n"/>
+      <c r="L67" s="38" t="n">
+        <v>4543</v>
+      </c>
       <c r="M67" s="38" t="n"/>
-      <c r="N67" s="38" t="n"/>
+      <c r="N67" s="38" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="42" t="inlineStr">
@@ -4203,9 +4443,13 @@
       <c r="K68" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L68" s="44" t="n"/>
+      <c r="L68" s="44" t="n">
+        <v>2282</v>
+      </c>
       <c r="M68" s="44" t="n"/>
-      <c r="N68" s="44" t="n"/>
+      <c r="N68" s="44" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="36" t="inlineStr">
@@ -4253,9 +4497,13 @@
       <c r="K69" s="38" t="n">
         <v>4.1</v>
       </c>
-      <c r="L69" s="39" t="n"/>
+      <c r="L69" s="39" t="n">
+        <v>6039</v>
+      </c>
       <c r="M69" s="40" t="n"/>
-      <c r="N69" s="41" t="n"/>
+      <c r="N69" s="41" t="n">
+        <v>98.59999999999999</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="42" t="inlineStr">
@@ -4303,9 +4551,13 @@
       <c r="K70" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="L70" s="45" t="n"/>
+      <c r="L70" s="45" t="n">
+        <v>9038</v>
+      </c>
       <c r="M70" s="46" t="n"/>
-      <c r="N70" s="47" t="n"/>
+      <c r="N70" s="47" t="n">
+        <v>99.40000000000001</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="36" t="inlineStr">
@@ -4353,9 +4605,13 @@
       <c r="K71" s="38" t="n">
         <v>2.7</v>
       </c>
-      <c r="L71" s="39" t="n"/>
+      <c r="L71" s="39" t="n">
+        <v>3493</v>
+      </c>
       <c r="M71" s="40" t="n"/>
-      <c r="N71" s="41" t="n"/>
+      <c r="N71" s="41" t="n">
+        <v>97.5</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="42" t="inlineStr">
@@ -4397,9 +4653,13 @@
       <c r="K72" s="44" t="n">
         <v>0.9</v>
       </c>
-      <c r="L72" s="45" t="n"/>
+      <c r="L72" s="45" t="n">
+        <v>5438</v>
+      </c>
       <c r="M72" s="46" t="n"/>
-      <c r="N72" s="47" t="n"/>
+      <c r="N72" s="47" t="n">
+        <v>99.2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="36" t="inlineStr">
@@ -4487,9 +4747,13 @@
       <c r="K74" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="L74" s="44" t="n"/>
+      <c r="L74" s="44" t="n">
+        <v>3612</v>
+      </c>
       <c r="M74" s="44" t="n"/>
-      <c r="N74" s="44" t="n"/>
+      <c r="N74" s="44" t="n">
+        <v>98.40000000000001</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="36" t="inlineStr">
@@ -4527,9 +4791,13 @@
       <c r="I75" s="38" t="n"/>
       <c r="J75" s="38" t="n"/>
       <c r="K75" s="38" t="n"/>
-      <c r="L75" s="39" t="n"/>
+      <c r="L75" s="39" t="n">
+        <v>11934</v>
+      </c>
       <c r="M75" s="40" t="n"/>
-      <c r="N75" s="41" t="n"/>
+      <c r="N75" s="41" t="n">
+        <v>99.90000000000001</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="42" t="inlineStr">
@@ -4577,9 +4845,13 @@
       <c r="K76" s="44" t="n">
         <v>2.9</v>
       </c>
-      <c r="L76" s="44" t="n"/>
+      <c r="L76" s="44" t="n">
+        <v>7344</v>
+      </c>
       <c r="M76" s="44" t="n"/>
-      <c r="N76" s="44" t="n"/>
+      <c r="N76" s="44" t="n">
+        <v>98.90000000000001</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="36" t="inlineStr">
@@ -4627,9 +4899,13 @@
       <c r="K77" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="L77" s="38" t="n"/>
+      <c r="L77" s="38" t="n">
+        <v>7116</v>
+      </c>
       <c r="M77" s="38" t="n"/>
-      <c r="N77" s="38" t="n"/>
+      <c r="N77" s="38" t="n">
+        <v>98.2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="42" t="inlineStr">
@@ -4733,9 +5009,13 @@
       <c r="K79" s="38" t="n">
         <v>4.5</v>
       </c>
-      <c r="L79" s="38" t="n"/>
+      <c r="L79" s="38" t="n">
+        <v>2858</v>
+      </c>
       <c r="M79" s="38" t="n"/>
-      <c r="N79" s="38" t="n"/>
+      <c r="N79" s="38" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="42" t="inlineStr">
@@ -4769,9 +5049,13 @@
       <c r="I80" s="45" t="n"/>
       <c r="J80" s="44" t="n"/>
       <c r="K80" s="44" t="n"/>
-      <c r="L80" s="44" t="n"/>
+      <c r="L80" s="44" t="n">
+        <v>8294</v>
+      </c>
       <c r="M80" s="44" t="n"/>
-      <c r="N80" s="44" t="n"/>
+      <c r="N80" s="44" t="n">
+        <v>99.40000000000001</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="36" t="inlineStr">
@@ -4819,9 +5103,13 @@
       <c r="K81" s="38" t="n">
         <v>2.7</v>
       </c>
-      <c r="L81" s="38" t="n"/>
+      <c r="L81" s="38" t="n">
+        <v>7390</v>
+      </c>
       <c r="M81" s="38" t="n"/>
-      <c r="N81" s="38" t="n"/>
+      <c r="N81" s="38" t="n">
+        <v>98.40000000000001</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="42" t="inlineStr">
@@ -4869,9 +5157,13 @@
       <c r="K82" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="L82" s="45" t="n"/>
+      <c r="L82" s="45" t="n">
+        <v>5958</v>
+      </c>
       <c r="M82" s="46" t="n"/>
-      <c r="N82" s="47" t="n"/>
+      <c r="N82" s="47" t="n">
+        <v>97.59999999999999</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="36" t="inlineStr">
@@ -4919,9 +5211,13 @@
       <c r="K83" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="L83" s="38" t="n"/>
+      <c r="L83" s="38" t="n">
+        <v>9336</v>
+      </c>
       <c r="M83" s="38" t="n"/>
-      <c r="N83" s="38" t="n"/>
+      <c r="N83" s="38" t="n">
+        <v>97.09999999999999</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="42" t="inlineStr">
@@ -4969,9 +5265,13 @@
       <c r="K84" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="L84" s="44" t="n"/>
+      <c r="L84" s="44" t="n">
+        <v>5660</v>
+      </c>
       <c r="M84" s="44" t="n"/>
-      <c r="N84" s="44" t="n"/>
+      <c r="N84" s="44" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="36" t="inlineStr">
@@ -5019,9 +5319,13 @@
       <c r="K85" s="38" t="n">
         <v>2.5</v>
       </c>
-      <c r="L85" s="38" t="n"/>
+      <c r="L85" s="38" t="n">
+        <v>4099</v>
+      </c>
       <c r="M85" s="38" t="n"/>
-      <c r="N85" s="38" t="n"/>
+      <c r="N85" s="38" t="n">
+        <v>99.3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="42" t="inlineStr">
@@ -5125,9 +5429,13 @@
       <c r="K87" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L87" s="38" t="n"/>
+      <c r="L87" s="38" t="n">
+        <v>4608</v>
+      </c>
       <c r="M87" s="38" t="n"/>
-      <c r="N87" s="38" t="n"/>
+      <c r="N87" s="38" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="42" t="inlineStr">
@@ -5175,9 +5483,13 @@
       <c r="K88" s="44" t="n">
         <v>3.5</v>
       </c>
-      <c r="L88" s="45" t="n"/>
+      <c r="L88" s="45" t="n">
+        <v>2352</v>
+      </c>
       <c r="M88" s="46" t="n"/>
-      <c r="N88" s="47" t="n"/>
+      <c r="N88" s="47" t="n">
+        <v>98.3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="36" t="inlineStr">
@@ -5225,9 +5537,13 @@
       <c r="K89" s="38" t="n">
         <v>2.8</v>
       </c>
-      <c r="L89" s="38" t="n"/>
+      <c r="L89" s="38" t="n">
+        <v>4589</v>
+      </c>
       <c r="M89" s="38" t="n"/>
-      <c r="N89" s="38" t="n"/>
+      <c r="N89" s="38" t="n">
+        <v>99.09999999999999</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="42" t="inlineStr">
@@ -5275,9 +5591,13 @@
       <c r="K90" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="L90" s="44" t="n"/>
+      <c r="L90" s="44" t="n">
+        <v>5465</v>
+      </c>
       <c r="M90" s="44" t="n"/>
-      <c r="N90" s="44" t="n"/>
+      <c r="N90" s="44" t="n">
+        <v>98.2</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="36" t="inlineStr">
@@ -5325,9 +5645,13 @@
       <c r="K91" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L91" s="38" t="n"/>
+      <c r="L91" s="38" t="n">
+        <v>4215</v>
+      </c>
       <c r="M91" s="38" t="n"/>
-      <c r="N91" s="38" t="n"/>
+      <c r="N91" s="38" t="n">
+        <v>98.3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="42" t="inlineStr">
@@ -5375,9 +5699,13 @@
       <c r="K92" s="44" t="n">
         <v>4.7</v>
       </c>
-      <c r="L92" s="44" t="n"/>
+      <c r="L92" s="44" t="n">
+        <v>5960</v>
+      </c>
       <c r="M92" s="44" t="n"/>
-      <c r="N92" s="44" t="n"/>
+      <c r="N92" s="44" t="n">
+        <v>99.3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="36" t="inlineStr">
@@ -5481,9 +5809,13 @@
       <c r="K94" s="44" t="n">
         <v>5.2</v>
       </c>
-      <c r="L94" s="44" t="n"/>
+      <c r="L94" s="44" t="n">
+        <v>6195</v>
+      </c>
       <c r="M94" s="44" t="n"/>
-      <c r="N94" s="44" t="n"/>
+      <c r="N94" s="44" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="36" t="inlineStr">
@@ -5529,9 +5861,13 @@
       <c r="K95" s="38" t="n">
         <v>0.5</v>
       </c>
-      <c r="L95" s="38" t="n"/>
+      <c r="L95" s="38" t="n">
+        <v>3905</v>
+      </c>
       <c r="M95" s="38" t="n"/>
-      <c r="N95" s="38" t="n"/>
+      <c r="N95" s="38" t="n">
+        <v>99.7</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="42" t="inlineStr">
@@ -5579,9 +5915,13 @@
       <c r="K96" s="44" t="n">
         <v>4.5</v>
       </c>
-      <c r="L96" s="44" t="n"/>
+      <c r="L96" s="44" t="n">
+        <v>4800</v>
+      </c>
       <c r="M96" s="44" t="n"/>
-      <c r="N96" s="44" t="n"/>
+      <c r="N96" s="44" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="36" t="inlineStr">
@@ -5629,9 +5969,13 @@
       <c r="K97" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="L97" s="38" t="n"/>
+      <c r="L97" s="38" t="n">
+        <v>2421</v>
+      </c>
       <c r="M97" s="38" t="n"/>
-      <c r="N97" s="38" t="n"/>
+      <c r="N97" s="38" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="42" t="inlineStr">
@@ -5669,9 +6013,13 @@
       <c r="I98" s="44" t="n"/>
       <c r="J98" s="44" t="n"/>
       <c r="K98" s="44" t="n"/>
-      <c r="L98" s="44" t="n"/>
+      <c r="L98" s="44" t="n">
+        <v>7211</v>
+      </c>
       <c r="M98" s="44" t="n"/>
-      <c r="N98" s="44" t="n"/>
+      <c r="N98" s="44" t="n">
+        <v>98.90000000000001</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="36" t="inlineStr">
@@ -5717,9 +6065,13 @@
       <c r="K99" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="L99" s="38" t="n"/>
+      <c r="L99" s="38" t="n">
+        <v>7795</v>
+      </c>
       <c r="M99" s="38" t="n"/>
-      <c r="N99" s="38" t="n"/>
+      <c r="N99" s="38" t="n">
+        <v>100.3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="42" t="inlineStr">
@@ -5765,9 +6117,13 @@
       <c r="K100" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="L100" s="44" t="n"/>
+      <c r="L100" s="44" t="n">
+        <v>4826</v>
+      </c>
       <c r="M100" s="44" t="n"/>
-      <c r="N100" s="44" t="n"/>
+      <c r="N100" s="44" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="36" t="inlineStr">
@@ -5815,9 +6171,13 @@
       <c r="K101" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="L101" s="38" t="n"/>
+      <c r="L101" s="38" t="n">
+        <v>5552</v>
+      </c>
       <c r="M101" s="38" t="n"/>
-      <c r="N101" s="38" t="n"/>
+      <c r="N101" s="38" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="42" t="inlineStr">
@@ -5865,9 +6225,13 @@
       <c r="K102" s="44" t="n">
         <v>4.5</v>
       </c>
-      <c r="L102" s="44" t="n"/>
+      <c r="L102" s="44" t="n">
+        <v>9657</v>
+      </c>
       <c r="M102" s="44" t="n"/>
-      <c r="N102" s="44" t="n"/>
+      <c r="N102" s="44" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="36" t="inlineStr">
@@ -5905,9 +6269,13 @@
       <c r="I103" s="39" t="n"/>
       <c r="J103" s="38" t="n"/>
       <c r="K103" s="38" t="n"/>
-      <c r="L103" s="38" t="n"/>
+      <c r="L103" s="38" t="n">
+        <v>3942</v>
+      </c>
       <c r="M103" s="38" t="n"/>
-      <c r="N103" s="38" t="n"/>
+      <c r="N103" s="38" t="n">
+        <v>97.59999999999999</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="42" t="inlineStr">
@@ -5955,9 +6323,13 @@
       <c r="K104" s="44" t="n">
         <v>0.4</v>
       </c>
-      <c r="L104" s="44" t="n"/>
+      <c r="L104" s="44" t="n">
+        <v>5573</v>
+      </c>
       <c r="M104" s="44" t="n"/>
-      <c r="N104" s="44" t="n"/>
+      <c r="N104" s="44" t="n">
+        <v>99.40000000000001</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="36" t="inlineStr">
@@ -6005,9 +6377,13 @@
       <c r="K105" s="38" t="n">
         <v>4.5</v>
       </c>
-      <c r="L105" s="38" t="n"/>
+      <c r="L105" s="38" t="n">
+        <v>6771</v>
+      </c>
       <c r="M105" s="38" t="n"/>
-      <c r="N105" s="38" t="n"/>
+      <c r="N105" s="38" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="42" t="inlineStr">
@@ -6097,9 +6473,13 @@
       <c r="K107" s="38" t="n">
         <v>4.5</v>
       </c>
-      <c r="L107" s="38" t="n"/>
+      <c r="L107" s="38" t="n">
+        <v>5088</v>
+      </c>
       <c r="M107" s="38" t="n"/>
-      <c r="N107" s="38" t="n"/>
+      <c r="N107" s="38" t="n">
+        <v>98.59999999999999</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="42" t="inlineStr">
@@ -6137,9 +6517,13 @@
       <c r="I108" s="45" t="n"/>
       <c r="J108" s="44" t="n"/>
       <c r="K108" s="44" t="n"/>
-      <c r="L108" s="44" t="n"/>
+      <c r="L108" s="44" t="n">
+        <v>9984</v>
+      </c>
       <c r="M108" s="44" t="n"/>
-      <c r="N108" s="44" t="n"/>
+      <c r="N108" s="44" t="n">
+        <v>99.2</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="36" t="inlineStr">
@@ -6187,9 +6571,13 @@
       <c r="K109" s="38" t="n">
         <v>2.6</v>
       </c>
-      <c r="L109" s="38" t="n"/>
+      <c r="L109" s="38" t="n">
+        <v>5554</v>
+      </c>
       <c r="M109" s="38" t="n"/>
-      <c r="N109" s="38" t="n"/>
+      <c r="N109" s="38" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="42" t="inlineStr">
@@ -6237,9 +6625,13 @@
       <c r="K110" s="44" t="n">
         <v>1.4</v>
       </c>
-      <c r="L110" s="44" t="n"/>
+      <c r="L110" s="44" t="n">
+        <v>5073</v>
+      </c>
       <c r="M110" s="44" t="n"/>
-      <c r="N110" s="44" t="n"/>
+      <c r="N110" s="44" t="n">
+        <v>99.2</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="36" t="inlineStr">
@@ -6277,9 +6669,13 @@
       <c r="I111" s="39" t="n"/>
       <c r="J111" s="38" t="n"/>
       <c r="K111" s="38" t="n"/>
-      <c r="L111" s="38" t="n"/>
+      <c r="L111" s="38" t="n">
+        <v>5560</v>
+      </c>
       <c r="M111" s="38" t="n"/>
-      <c r="N111" s="38" t="n"/>
+      <c r="N111" s="38" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="42" t="inlineStr">
@@ -6327,9 +6723,13 @@
       <c r="K112" s="44" t="n">
         <v>5.7</v>
       </c>
-      <c r="L112" s="44" t="n"/>
+      <c r="L112" s="44" t="n">
+        <v>7664</v>
+      </c>
       <c r="M112" s="44" t="n"/>
-      <c r="N112" s="44" t="n"/>
+      <c r="N112" s="44" t="n">
+        <v>98.90000000000001</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="36" t="inlineStr">
@@ -6377,9 +6777,13 @@
       <c r="K113" s="38" t="n">
         <v>4.5</v>
       </c>
-      <c r="L113" s="38" t="n"/>
+      <c r="L113" s="38" t="n">
+        <v>3274</v>
+      </c>
       <c r="M113" s="38" t="n"/>
-      <c r="N113" s="38" t="n"/>
+      <c r="N113" s="38" t="n">
+        <v>98.90000000000001</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="42" t="inlineStr">
@@ -6427,9 +6831,13 @@
       <c r="K114" s="44" t="n">
         <v>2.5</v>
       </c>
-      <c r="L114" s="44" t="n"/>
+      <c r="L114" s="44" t="n">
+        <v>3959</v>
+      </c>
       <c r="M114" s="44" t="n"/>
-      <c r="N114" s="44" t="n"/>
+      <c r="N114" s="44" t="n">
+        <v>97.7</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="36" t="inlineStr">
@@ -6477,9 +6885,13 @@
       <c r="K115" s="38" t="n">
         <v>5.1</v>
       </c>
-      <c r="L115" s="38" t="n"/>
+      <c r="L115" s="38" t="n">
+        <v>6297</v>
+      </c>
       <c r="M115" s="38" t="n"/>
-      <c r="N115" s="38" t="n"/>
+      <c r="N115" s="38" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="42" t="inlineStr">
@@ -6521,9 +6933,13 @@
       <c r="K116" s="44" t="n">
         <v>3.6</v>
       </c>
-      <c r="L116" s="44" t="n"/>
+      <c r="L116" s="44" t="n">
+        <v>6151</v>
+      </c>
       <c r="M116" s="44" t="n"/>
-      <c r="N116" s="44" t="n"/>
+      <c r="N116" s="44" t="n">
+        <v>101.6</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="36" t="inlineStr">
@@ -6565,9 +6981,13 @@
       <c r="K117" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="L117" s="38" t="n"/>
+      <c r="L117" s="38" t="n">
+        <v>4430</v>
+      </c>
       <c r="M117" s="38" t="n"/>
-      <c r="N117" s="38" t="n"/>
+      <c r="N117" s="38" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="42" t="inlineStr">
@@ -6615,9 +7035,13 @@
       <c r="K118" s="44" t="n">
         <v>6.6</v>
       </c>
-      <c r="L118" s="44" t="n"/>
+      <c r="L118" s="44" t="n">
+        <v>9538</v>
+      </c>
       <c r="M118" s="44" t="n"/>
-      <c r="N118" s="44" t="n"/>
+      <c r="N118" s="44" t="n">
+        <v>99.09999999999999</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="36" t="inlineStr">
@@ -6665,9 +7089,13 @@
       <c r="K119" s="38" t="n">
         <v>5.5</v>
       </c>
-      <c r="L119" s="38" t="n"/>
+      <c r="L119" s="38" t="n">
+        <v>8178</v>
+      </c>
       <c r="M119" s="38" t="n"/>
-      <c r="N119" s="38" t="n"/>
+      <c r="N119" s="38" t="n">
+        <v>99.09999999999999</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="42" t="inlineStr">
@@ -6715,9 +7143,13 @@
       <c r="K120" s="44" t="n">
         <v>2.8</v>
       </c>
-      <c r="L120" s="44" t="n"/>
+      <c r="L120" s="44" t="n">
+        <v>4061</v>
+      </c>
       <c r="M120" s="44" t="n"/>
-      <c r="N120" s="44" t="n"/>
+      <c r="N120" s="44" t="n">
+        <v>98.3</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="36" t="inlineStr">
@@ -6821,9 +7253,13 @@
       <c r="K122" s="44" t="n">
         <v>3.8</v>
       </c>
-      <c r="L122" s="44" t="n"/>
+      <c r="L122" s="44" t="n">
+        <v>7266</v>
+      </c>
       <c r="M122" s="44" t="n"/>
-      <c r="N122" s="44" t="n"/>
+      <c r="N122" s="44" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="36" t="inlineStr">
@@ -6861,9 +7297,13 @@
       <c r="I123" s="39" t="n"/>
       <c r="J123" s="38" t="n"/>
       <c r="K123" s="38" t="n"/>
-      <c r="L123" s="38" t="n"/>
+      <c r="L123" s="38" t="n">
+        <v>10813</v>
+      </c>
       <c r="M123" s="38" t="n"/>
-      <c r="N123" s="38" t="n"/>
+      <c r="N123" s="38" t="n">
+        <v>99.3</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="42" t="inlineStr">
@@ -6911,9 +7351,13 @@
       <c r="K124" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L124" s="44" t="n"/>
+      <c r="L124" s="44" t="n">
+        <v>4472</v>
+      </c>
       <c r="M124" s="44" t="n"/>
-      <c r="N124" s="44" t="n"/>
+      <c r="N124" s="44" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="36" t="inlineStr">
@@ -6961,9 +7405,13 @@
       <c r="K125" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L125" s="39" t="n"/>
+      <c r="L125" s="39" t="n">
+        <v>5197</v>
+      </c>
       <c r="M125" s="40" t="n"/>
-      <c r="N125" s="41" t="n"/>
+      <c r="N125" s="41" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="42" t="inlineStr">
@@ -7011,9 +7459,13 @@
       <c r="K126" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="L126" s="44" t="n"/>
+      <c r="L126" s="44" t="n">
+        <v>4750</v>
+      </c>
       <c r="M126" s="44" t="n"/>
-      <c r="N126" s="44" t="n"/>
+      <c r="N126" s="44" t="n">
+        <v>98.7</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="36" t="inlineStr">
@@ -7061,9 +7513,13 @@
       <c r="K127" s="38" t="n">
         <v>2.6</v>
       </c>
-      <c r="L127" s="38" t="n"/>
+      <c r="L127" s="38" t="n">
+        <v>3040</v>
+      </c>
       <c r="M127" s="38" t="n"/>
-      <c r="N127" s="38" t="n"/>
+      <c r="N127" s="38" t="n">
+        <v>97.7</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="42" t="inlineStr">
@@ -7111,9 +7567,13 @@
       <c r="K128" s="44" t="n">
         <v>3.5</v>
       </c>
-      <c r="L128" s="44" t="n"/>
+      <c r="L128" s="44" t="n">
+        <v>10534</v>
+      </c>
       <c r="M128" s="44" t="n"/>
-      <c r="N128" s="44" t="n"/>
+      <c r="N128" s="44" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="36" t="inlineStr">
@@ -7161,9 +7621,13 @@
       <c r="K129" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L129" s="38" t="n"/>
+      <c r="L129" s="38" t="n">
+        <v>4501</v>
+      </c>
       <c r="M129" s="38" t="n"/>
-      <c r="N129" s="38" t="n"/>
+      <c r="N129" s="38" t="n">
+        <v>97.7</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="42" t="inlineStr">
@@ -7211,9 +7675,13 @@
       <c r="K130" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L130" s="44" t="n"/>
+      <c r="L130" s="44" t="n">
+        <v>4814</v>
+      </c>
       <c r="M130" s="44" t="n"/>
-      <c r="N130" s="44" t="n"/>
+      <c r="N130" s="44" t="n">
+        <v>99.3</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="36" t="inlineStr">
@@ -7261,9 +7729,13 @@
       <c r="K131" s="38" t="n">
         <v>1.3</v>
       </c>
-      <c r="L131" s="39" t="n"/>
+      <c r="L131" s="39" t="n">
+        <v>4016</v>
+      </c>
       <c r="M131" s="40" t="n"/>
-      <c r="N131" s="41" t="n"/>
+      <c r="N131" s="41" t="n">
+        <v>98.09999999999999</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="42" t="inlineStr">
@@ -7307,9 +7779,13 @@
       <c r="K132" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="L132" s="44" t="n"/>
+      <c r="L132" s="44" t="n">
+        <v>3610</v>
+      </c>
       <c r="M132" s="44" t="n"/>
-      <c r="N132" s="44" t="n"/>
+      <c r="N132" s="44" t="n">
+        <v>99.8</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="36" t="inlineStr">
@@ -7355,9 +7831,13 @@
       <c r="K133" s="38" t="n">
         <v>7.2</v>
       </c>
-      <c r="L133" s="38" t="n"/>
+      <c r="L133" s="38" t="n">
+        <v>8036</v>
+      </c>
       <c r="M133" s="38" t="n"/>
-      <c r="N133" s="38" t="n"/>
+      <c r="N133" s="38" t="n">
+        <v>99.8</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="42" t="inlineStr">
@@ -7405,9 +7885,13 @@
       <c r="K134" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L134" s="44" t="n"/>
+      <c r="L134" s="44" t="n">
+        <v>3637</v>
+      </c>
       <c r="M134" s="44" t="n"/>
-      <c r="N134" s="44" t="n"/>
+      <c r="N134" s="44" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="36" t="inlineStr">
@@ -7455,9 +7939,13 @@
       <c r="K135" s="38" t="n">
         <v>2.2</v>
       </c>
-      <c r="L135" s="38" t="n"/>
+      <c r="L135" s="38" t="n">
+        <v>6514</v>
+      </c>
       <c r="M135" s="38" t="n"/>
-      <c r="N135" s="38" t="n"/>
+      <c r="N135" s="38" t="n">
+        <v>98.59999999999999</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="42" t="inlineStr">
@@ -7501,9 +7989,13 @@
       </c>
       <c r="J136" s="44" t="n"/>
       <c r="K136" s="44" t="n"/>
-      <c r="L136" s="44" t="n"/>
+      <c r="L136" s="44" t="n">
+        <v>6007</v>
+      </c>
       <c r="M136" s="44" t="n"/>
-      <c r="N136" s="44" t="n"/>
+      <c r="N136" s="44" t="n">
+        <v>99.59999999999999</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="36" t="inlineStr">
@@ -7663,9 +8155,13 @@
       <c r="K139" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="L139" s="38" t="n"/>
+      <c r="L139" s="38" t="n">
+        <v>6096</v>
+      </c>
       <c r="M139" s="38" t="n"/>
-      <c r="N139" s="38" t="n"/>
+      <c r="N139" s="38" t="n">
+        <v>98.8</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="42" t="inlineStr">
@@ -7761,9 +8257,13 @@
       <c r="K141" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="L141" s="38" t="n"/>
+      <c r="L141" s="38" t="n">
+        <v>6355</v>
+      </c>
       <c r="M141" s="38" t="n"/>
-      <c r="N141" s="38" t="n"/>
+      <c r="N141" s="38" t="n">
+        <v>98.90000000000001</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="42" t="inlineStr">
@@ -7811,9 +8311,13 @@
       <c r="K142" s="44" t="n">
         <v>6.1</v>
       </c>
-      <c r="L142" s="44" t="n"/>
+      <c r="L142" s="44" t="n">
+        <v>4261</v>
+      </c>
       <c r="M142" s="44" t="n"/>
-      <c r="N142" s="44" t="n"/>
+      <c r="N142" s="44" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="36" t="inlineStr">
@@ -7857,9 +8361,13 @@
       <c r="K143" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L143" s="38" t="n"/>
+      <c r="L143" s="38" t="n">
+        <v>8018</v>
+      </c>
       <c r="M143" s="38" t="n"/>
-      <c r="N143" s="38" t="n"/>
+      <c r="N143" s="38" t="n">
+        <v>98.09999999999999</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="42" t="inlineStr">
@@ -8287,9 +8795,13 @@
       <c r="I151" s="39" t="n"/>
       <c r="J151" s="38" t="n"/>
       <c r="K151" s="38" t="n"/>
-      <c r="L151" s="38" t="n"/>
+      <c r="L151" s="38" t="n">
+        <v>10088</v>
+      </c>
       <c r="M151" s="38" t="n"/>
-      <c r="N151" s="38" t="n"/>
+      <c r="N151" s="38" t="n">
+        <v>99.09999999999999</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="42" t="inlineStr">
@@ -8559,9 +9071,13 @@
       <c r="K156" s="44" t="n">
         <v>3.5</v>
       </c>
-      <c r="L156" s="44" t="n"/>
+      <c r="L156" s="44" t="n">
+        <v>12079</v>
+      </c>
       <c r="M156" s="44" t="n"/>
-      <c r="N156" s="44" t="n"/>
+      <c r="N156" s="44" t="n">
+        <v>98.3</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="36" t="inlineStr">
@@ -8919,9 +9435,13 @@
       <c r="I163" s="39" t="n"/>
       <c r="J163" s="38" t="n"/>
       <c r="K163" s="38" t="n"/>
-      <c r="L163" s="38" t="n"/>
+      <c r="L163" s="38" t="n">
+        <v>10481</v>
+      </c>
       <c r="M163" s="38" t="n"/>
-      <c r="N163" s="38" t="n"/>
+      <c r="N163" s="38" t="n">
+        <v>99.90000000000001</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="42" t="inlineStr">
@@ -9933,9 +10453,13 @@
       <c r="K182" s="44" t="n">
         <v>3.3</v>
       </c>
-      <c r="L182" s="44" t="n"/>
+      <c r="L182" s="44" t="n">
+        <v>7301</v>
+      </c>
       <c r="M182" s="44" t="n"/>
-      <c r="N182" s="44" t="n"/>
+      <c r="N182" s="44" t="n">
+        <v>98.09999999999999</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="36" t="inlineStr">
@@ -10227,9 +10751,13 @@
       <c r="K188" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="L188" s="44" t="n"/>
+      <c r="L188" s="44" t="n">
+        <v>5898</v>
+      </c>
       <c r="M188" s="44" t="n"/>
-      <c r="N188" s="44" t="n"/>
+      <c r="N188" s="44" t="n">
+        <v>97.7</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="36" t="inlineStr">
@@ -10739,9 +11267,13 @@
       <c r="K199" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="L199" s="38" t="n"/>
+      <c r="L199" s="38" t="n">
+        <v>8826</v>
+      </c>
       <c r="M199" s="38" t="n"/>
-      <c r="N199" s="38" t="n"/>
+      <c r="N199" s="38" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="42" t="inlineStr">
@@ -10871,9 +11403,13 @@
       <c r="I202" s="44" t="n"/>
       <c r="J202" s="44" t="n"/>
       <c r="K202" s="44" t="n"/>
-      <c r="L202" s="44" t="n"/>
+      <c r="L202" s="44" t="n">
+        <v>8102</v>
+      </c>
       <c r="M202" s="44" t="n"/>
-      <c r="N202" s="44" t="n"/>
+      <c r="N202" s="44" t="n">
+        <v>99.2</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="36" t="inlineStr">
@@ -10989,9 +11525,13 @@
       <c r="I205" s="39" t="n"/>
       <c r="J205" s="38" t="n"/>
       <c r="K205" s="38" t="n"/>
-      <c r="L205" s="38" t="n"/>
+      <c r="L205" s="38" t="n">
+        <v>11560</v>
+      </c>
       <c r="M205" s="38" t="n"/>
-      <c r="N205" s="38" t="n"/>
+      <c r="N205" s="38" t="n">
+        <v>99.5</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="42" t="inlineStr">
@@ -11115,9 +11655,13 @@
       <c r="I208" s="45" t="n"/>
       <c r="J208" s="44" t="n"/>
       <c r="K208" s="44" t="n"/>
-      <c r="L208" s="44" t="n"/>
+      <c r="L208" s="44" t="n">
+        <v>4452</v>
+      </c>
       <c r="M208" s="44" t="n"/>
-      <c r="N208" s="44" t="n"/>
+      <c r="N208" s="44" t="n">
+        <v>98.5</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="36" t="inlineStr">
@@ -11259,9 +11803,13 @@
       <c r="K211" s="38" t="n">
         <v>4.5</v>
       </c>
-      <c r="L211" s="38" t="n"/>
+      <c r="L211" s="38" t="n">
+        <v>6387</v>
+      </c>
       <c r="M211" s="38" t="n"/>
-      <c r="N211" s="38" t="n"/>
+      <c r="N211" s="38" t="n">
+        <v>98.3</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="50" t="inlineStr">

--- a/ai収集/機種一覧_MY_コイン単価.xlsx
+++ b/ai収集/機種一覧_MY_コイン単価.xlsx
@@ -922,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N301"/>
+  <dimension ref="A1:M301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -955,15 +955,14 @@
       </c>
       <c r="H1" s="33" t="n"/>
       <c r="I1" s="33" t="n"/>
-      <c r="J1" s="33" t="n"/>
-      <c r="K1" s="34" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="J1" s="34" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>SIS実稼働データ（平均）</t>
         </is>
       </c>
-      <c r="M1" s="33" t="n"/>
-      <c r="N1" s="34" t="n"/>
+      <c r="L1" s="33" t="n"/>
+      <c r="M1" s="34" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1008,30 +1007,25 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MY×単価(円)</t>
+          <t>ATTS</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ATTS</t>
+          <t>純増枚/G</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>純増枚/G</t>
+          <t>SIS平均アウト</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SIS平均アウト</t>
+          <t>SIS平均MY</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>SIS平均MY</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIS割数%</t>
         </is>
@@ -1075,19 +1069,16 @@
         <v>3010</v>
       </c>
       <c r="I3" s="38" t="n">
-        <v>10234</v>
+        <v>252</v>
       </c>
       <c r="J3" s="38" t="n">
-        <v>252</v>
-      </c>
-      <c r="K3" s="38" t="n">
         <v>3.2</v>
       </c>
-      <c r="L3" s="39" t="n">
+      <c r="K3" s="39" t="n">
         <v>1860</v>
       </c>
-      <c r="M3" s="40" t="n"/>
-      <c r="N3" s="41" t="n">
+      <c r="L3" s="40" t="n"/>
+      <c r="M3" s="41" t="n">
         <v>98</v>
       </c>
     </row>
@@ -1129,19 +1120,16 @@
         <v>3466</v>
       </c>
       <c r="I4" s="44" t="n">
-        <v>13864</v>
+        <v>355</v>
       </c>
       <c r="J4" s="44" t="n">
-        <v>355</v>
-      </c>
-      <c r="K4" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L4" s="45" t="n">
+      <c r="K4" s="45" t="n">
         <v>3926</v>
       </c>
-      <c r="M4" s="46" t="n"/>
-      <c r="N4" s="47" t="n">
+      <c r="L4" s="46" t="n"/>
+      <c r="M4" s="47" t="n">
         <v>97.8</v>
       </c>
     </row>
@@ -1183,19 +1171,16 @@
         <v>3822</v>
       </c>
       <c r="I5" s="38" t="n">
-        <v>17199</v>
+        <v>519</v>
       </c>
       <c r="J5" s="38" t="n">
-        <v>519</v>
-      </c>
-      <c r="K5" s="38" t="n">
         <v>7.2</v>
       </c>
-      <c r="L5" s="39" t="n">
+      <c r="K5" s="39" t="n">
         <v>8400</v>
       </c>
-      <c r="M5" s="40" t="n"/>
-      <c r="N5" s="41" t="n">
+      <c r="L5" s="40" t="n"/>
+      <c r="M5" s="41" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -1234,12 +1219,11 @@
       <c r="H6" s="44" t="n"/>
       <c r="I6" s="44" t="n"/>
       <c r="J6" s="44" t="n"/>
-      <c r="K6" s="44" t="n"/>
-      <c r="L6" s="44" t="n">
+      <c r="K6" s="44" t="n">
         <v>2791</v>
       </c>
-      <c r="M6" s="44" t="n"/>
-      <c r="N6" s="44" t="n">
+      <c r="L6" s="44" t="n"/>
+      <c r="M6" s="44" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -1274,12 +1258,11 @@
       <c r="H7" s="38" t="n"/>
       <c r="I7" s="38" t="n"/>
       <c r="J7" s="38" t="n"/>
-      <c r="K7" s="38" t="n"/>
-      <c r="L7" s="38" t="n">
+      <c r="K7" s="38" t="n">
         <v>3471</v>
       </c>
-      <c r="M7" s="38" t="n"/>
-      <c r="N7" s="38" t="n">
+      <c r="L7" s="38" t="n"/>
+      <c r="M7" s="38" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -1316,14 +1299,13 @@
       </c>
       <c r="G8" s="44" t="n"/>
       <c r="H8" s="44" t="n"/>
-      <c r="I8" s="45" t="n"/>
+      <c r="I8" s="44" t="n"/>
       <c r="J8" s="44" t="n"/>
-      <c r="K8" s="44" t="n"/>
-      <c r="L8" s="45" t="n">
+      <c r="K8" s="45" t="n">
         <v>1570</v>
       </c>
-      <c r="M8" s="46" t="n"/>
-      <c r="N8" s="47" t="n">
+      <c r="L8" s="46" t="n"/>
+      <c r="M8" s="47" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -1365,19 +1347,16 @@
         <v>2861</v>
       </c>
       <c r="I9" s="38" t="n">
-        <v>8869</v>
+        <v>293</v>
       </c>
       <c r="J9" s="38" t="n">
-        <v>293</v>
+        <v>2.6</v>
       </c>
       <c r="K9" s="38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L9" s="38" t="n">
         <v>2664</v>
       </c>
-      <c r="M9" s="38" t="n"/>
-      <c r="N9" s="38" t="n">
+      <c r="L9" s="38" t="n"/>
+      <c r="M9" s="38" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -1416,18 +1395,17 @@
         <v>3.8</v>
       </c>
       <c r="H10" s="44" t="n"/>
-      <c r="I10" s="45" t="n"/>
+      <c r="I10" s="44" t="n">
+        <v>299</v>
+      </c>
       <c r="J10" s="44" t="n">
-        <v>299</v>
-      </c>
-      <c r="K10" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L10" s="45" t="n">
+      <c r="K10" s="45" t="n">
         <v>10993</v>
       </c>
-      <c r="M10" s="46" t="n"/>
-      <c r="N10" s="47" t="n">
+      <c r="L10" s="46" t="n"/>
+      <c r="M10" s="47" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -1464,14 +1442,13 @@
       </c>
       <c r="G11" s="38" t="n"/>
       <c r="H11" s="38" t="n"/>
-      <c r="I11" s="39" t="n"/>
+      <c r="I11" s="38" t="n"/>
       <c r="J11" s="38" t="n"/>
-      <c r="K11" s="38" t="n"/>
-      <c r="L11" s="39" t="n">
+      <c r="K11" s="39" t="n">
         <v>9815</v>
       </c>
-      <c r="M11" s="40" t="n"/>
-      <c r="N11" s="41" t="n">
+      <c r="L11" s="40" t="n"/>
+      <c r="M11" s="41" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -1512,20 +1489,17 @@
       <c r="H12" s="44" t="n">
         <v>2800</v>
       </c>
-      <c r="I12" s="45" t="n">
-        <v>9240</v>
+      <c r="I12" s="44" t="n">
+        <v>636</v>
       </c>
       <c r="J12" s="44" t="n">
-        <v>636</v>
+        <v>2.6</v>
       </c>
       <c r="K12" s="44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L12" s="44" t="n">
         <v>3044</v>
       </c>
-      <c r="M12" s="44" t="n"/>
-      <c r="N12" s="44" t="n">
+      <c r="L12" s="44" t="n"/>
+      <c r="M12" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -1567,19 +1541,16 @@
         <v>2800</v>
       </c>
       <c r="I13" s="38" t="n">
-        <v>9240</v>
+        <v>273</v>
       </c>
       <c r="J13" s="38" t="n">
-        <v>273</v>
+        <v>2.7</v>
       </c>
       <c r="K13" s="38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L13" s="38" t="n">
         <v>5667</v>
       </c>
-      <c r="M13" s="38" t="n"/>
-      <c r="N13" s="38" t="n">
+      <c r="L13" s="38" t="n"/>
+      <c r="M13" s="38" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -1620,20 +1591,17 @@
       <c r="H14" s="44" t="n">
         <v>2427</v>
       </c>
-      <c r="I14" s="45" t="n">
-        <v>7281</v>
+      <c r="I14" s="44" t="n">
+        <v>476</v>
       </c>
       <c r="J14" s="44" t="n">
-        <v>476</v>
-      </c>
-      <c r="K14" s="44" t="n">
         <v>2.7</v>
       </c>
-      <c r="L14" s="45" t="n">
+      <c r="K14" s="45" t="n">
         <v>2943</v>
       </c>
-      <c r="M14" s="46" t="n"/>
-      <c r="N14" s="47" t="n">
+      <c r="L14" s="46" t="n"/>
+      <c r="M14" s="47" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -1670,14 +1638,13 @@
       </c>
       <c r="G15" s="38" t="n"/>
       <c r="H15" s="38" t="n"/>
-      <c r="I15" s="39" t="n"/>
+      <c r="I15" s="38" t="n"/>
       <c r="J15" s="38" t="n"/>
-      <c r="K15" s="38" t="n"/>
-      <c r="L15" s="39" t="n">
+      <c r="K15" s="39" t="n">
         <v>4207</v>
       </c>
-      <c r="M15" s="40" t="n"/>
-      <c r="N15" s="41" t="n">
+      <c r="L15" s="40" t="n"/>
+      <c r="M15" s="41" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -1719,19 +1686,16 @@
         <v>2435</v>
       </c>
       <c r="I16" s="44" t="n">
-        <v>6818</v>
+        <v>371</v>
       </c>
       <c r="J16" s="44" t="n">
-        <v>371</v>
+        <v>2.8</v>
       </c>
       <c r="K16" s="44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L16" s="44" t="n">
         <v>5784</v>
       </c>
-      <c r="M16" s="44" t="n"/>
-      <c r="N16" s="44" t="n">
+      <c r="L16" s="44" t="n"/>
+      <c r="M16" s="44" t="n">
         <v>99</v>
       </c>
     </row>
@@ -1766,16 +1730,15 @@
         <v>3.4</v>
       </c>
       <c r="H17" s="38" t="n"/>
-      <c r="I17" s="38" t="n"/>
+      <c r="I17" s="38" t="n">
+        <v>267</v>
+      </c>
       <c r="J17" s="38" t="n">
-        <v>267</v>
-      </c>
-      <c r="K17" s="38" t="n">
         <v>4.2</v>
       </c>
-      <c r="L17" s="39" t="n"/>
-      <c r="M17" s="40" t="n"/>
-      <c r="N17" s="41" t="n"/>
+      <c r="K17" s="39" t="n"/>
+      <c r="L17" s="40" t="n"/>
+      <c r="M17" s="41" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="42" t="inlineStr">
@@ -1815,19 +1778,16 @@
         <v>2350</v>
       </c>
       <c r="I18" s="44" t="n">
-        <v>7050</v>
+        <v>381</v>
       </c>
       <c r="J18" s="44" t="n">
-        <v>381</v>
+        <v>5</v>
       </c>
       <c r="K18" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" s="44" t="n">
         <v>4989</v>
       </c>
-      <c r="M18" s="44" t="n"/>
-      <c r="N18" s="44" t="n">
+      <c r="L18" s="44" t="n"/>
+      <c r="M18" s="44" t="n">
         <v>98.40000000000001</v>
       </c>
     </row>
@@ -1869,19 +1829,16 @@
         <v>3100</v>
       </c>
       <c r="I19" s="38" t="n">
-        <v>11160</v>
+        <v>255</v>
       </c>
       <c r="J19" s="38" t="n">
-        <v>255</v>
-      </c>
-      <c r="K19" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="39" t="n">
+      <c r="K19" s="39" t="n">
         <v>4001</v>
       </c>
-      <c r="M19" s="40" t="n"/>
-      <c r="N19" s="41" t="n">
+      <c r="L19" s="40" t="n"/>
+      <c r="M19" s="41" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -1922,20 +1879,17 @@
       <c r="H20" s="44" t="n">
         <v>2169</v>
       </c>
-      <c r="I20" s="45" t="n">
-        <v>6290</v>
+      <c r="I20" s="44" t="n">
+        <v>298</v>
       </c>
       <c r="J20" s="44" t="n">
-        <v>298</v>
-      </c>
-      <c r="K20" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="L20" s="45" t="n">
+      <c r="K20" s="45" t="n">
         <v>3270</v>
       </c>
-      <c r="M20" s="46" t="n"/>
-      <c r="N20" s="47" t="n">
+      <c r="L20" s="46" t="n"/>
+      <c r="M20" s="47" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -1974,18 +1928,17 @@
         <v>3</v>
       </c>
       <c r="H21" s="38" t="n"/>
-      <c r="I21" s="38" t="n"/>
+      <c r="I21" s="38" t="n">
+        <v>255</v>
+      </c>
       <c r="J21" s="38" t="n">
-        <v>255</v>
-      </c>
-      <c r="K21" s="38" t="n">
         <v>4.5</v>
       </c>
-      <c r="L21" s="39" t="n">
+      <c r="K21" s="39" t="n">
         <v>5120</v>
       </c>
-      <c r="M21" s="40" t="n"/>
-      <c r="N21" s="41" t="n">
+      <c r="L21" s="40" t="n"/>
+      <c r="M21" s="41" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -2027,19 +1980,16 @@
         <v>2441</v>
       </c>
       <c r="I22" s="44" t="n">
-        <v>6590</v>
+        <v>582</v>
       </c>
       <c r="J22" s="44" t="n">
-        <v>582</v>
-      </c>
-      <c r="K22" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L22" s="45" t="n">
+      <c r="K22" s="45" t="n">
         <v>3609</v>
       </c>
-      <c r="M22" s="46" t="n"/>
-      <c r="N22" s="47" t="n">
+      <c r="L22" s="46" t="n"/>
+      <c r="M22" s="47" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -2081,19 +2031,16 @@
         <v>3002</v>
       </c>
       <c r="I23" s="38" t="n">
-        <v>10206</v>
+        <v>445</v>
       </c>
       <c r="J23" s="38" t="n">
-        <v>445</v>
-      </c>
-      <c r="K23" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="L23" s="39" t="n">
+      <c r="K23" s="39" t="n">
         <v>3286</v>
       </c>
-      <c r="M23" s="40" t="n"/>
-      <c r="N23" s="41" t="n">
+      <c r="L23" s="40" t="n"/>
+      <c r="M23" s="41" t="n">
         <v>97.8</v>
       </c>
     </row>
@@ -2132,12 +2079,11 @@
       <c r="H24" s="44" t="n"/>
       <c r="I24" s="44" t="n"/>
       <c r="J24" s="44" t="n"/>
-      <c r="K24" s="44" t="n"/>
-      <c r="L24" s="45" t="n">
+      <c r="K24" s="45" t="n">
         <v>10912</v>
       </c>
-      <c r="M24" s="46" t="n"/>
-      <c r="N24" s="47" t="n">
+      <c r="L24" s="46" t="n"/>
+      <c r="M24" s="47" t="n">
         <v>99.59999999999999</v>
       </c>
     </row>
@@ -2176,18 +2122,17 @@
         <v>3.3</v>
       </c>
       <c r="H25" s="38" t="n"/>
-      <c r="I25" s="39" t="n"/>
+      <c r="I25" s="38" t="n">
+        <v>334</v>
+      </c>
       <c r="J25" s="38" t="n">
-        <v>334</v>
-      </c>
-      <c r="K25" s="38" t="n">
         <v>2.7</v>
       </c>
-      <c r="L25" s="39" t="n">
+      <c r="K25" s="39" t="n">
         <v>4298</v>
       </c>
-      <c r="M25" s="40" t="n"/>
-      <c r="N25" s="41" t="n">
+      <c r="L25" s="40" t="n"/>
+      <c r="M25" s="41" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -2228,20 +2173,17 @@
       <c r="H26" s="44" t="n">
         <v>2541</v>
       </c>
-      <c r="I26" s="45" t="n">
-        <v>7114</v>
+      <c r="I26" s="44" t="n">
+        <v>290</v>
       </c>
       <c r="J26" s="44" t="n">
-        <v>290</v>
-      </c>
-      <c r="K26" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L26" s="45" t="n">
+      <c r="K26" s="45" t="n">
         <v>5037</v>
       </c>
-      <c r="M26" s="46" t="n"/>
-      <c r="N26" s="47" t="n">
+      <c r="L26" s="46" t="n"/>
+      <c r="M26" s="47" t="n">
         <v>96.2</v>
       </c>
     </row>
@@ -2283,19 +2225,16 @@
         <v>4000</v>
       </c>
       <c r="I27" s="38" t="n">
-        <v>16000</v>
+        <v>350</v>
       </c>
       <c r="J27" s="38" t="n">
-        <v>350</v>
+        <v>10</v>
       </c>
       <c r="K27" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="L27" s="38" t="n">
         <v>4989</v>
       </c>
-      <c r="M27" s="38" t="n"/>
-      <c r="N27" s="38" t="n">
+      <c r="L27" s="38" t="n"/>
+      <c r="M27" s="38" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -2337,19 +2276,16 @@
         <v>2900</v>
       </c>
       <c r="I28" s="44" t="n">
-        <v>9280</v>
+        <v>344</v>
       </c>
       <c r="J28" s="44" t="n">
-        <v>344</v>
-      </c>
-      <c r="K28" s="44" t="n">
         <v>2.4</v>
       </c>
-      <c r="L28" s="45" t="n">
+      <c r="K28" s="45" t="n">
         <v>3511</v>
       </c>
-      <c r="M28" s="46" t="n"/>
-      <c r="N28" s="47" t="n">
+      <c r="L28" s="46" t="n"/>
+      <c r="M28" s="47" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -2391,19 +2327,16 @@
         <v>3527</v>
       </c>
       <c r="I29" s="38" t="n">
-        <v>14108</v>
+        <v>510</v>
       </c>
       <c r="J29" s="38" t="n">
-        <v>510</v>
-      </c>
-      <c r="K29" s="38" t="n">
         <v>2.9</v>
       </c>
-      <c r="L29" s="39" t="n">
+      <c r="K29" s="39" t="n">
         <v>3612</v>
       </c>
-      <c r="M29" s="40" t="n"/>
-      <c r="N29" s="41" t="n">
+      <c r="L29" s="40" t="n"/>
+      <c r="M29" s="41" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -2444,22 +2377,19 @@
       <c r="H30" s="44" t="n">
         <v>4032</v>
       </c>
-      <c r="I30" s="45" t="n">
-        <v>16934</v>
+      <c r="I30" s="44" t="n">
+        <v>547</v>
       </c>
       <c r="J30" s="44" t="n">
-        <v>547</v>
-      </c>
-      <c r="K30" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="L30" s="45" t="n">
+      <c r="K30" s="45" t="n">
         <v>7208</v>
       </c>
-      <c r="M30" s="46" t="n">
+      <c r="L30" s="46" t="n">
         <v>5033</v>
       </c>
-      <c r="N30" s="47" t="n">
+      <c r="M30" s="47" t="n">
         <v>97.8</v>
       </c>
     </row>
@@ -2500,22 +2430,19 @@
       <c r="H31" s="38" t="n">
         <v>2853</v>
       </c>
-      <c r="I31" s="39" t="n">
-        <v>9414</v>
+      <c r="I31" s="38" t="n">
+        <v>383</v>
       </c>
       <c r="J31" s="38" t="n">
-        <v>383</v>
-      </c>
-      <c r="K31" s="38" t="n">
         <v>4.1</v>
       </c>
-      <c r="L31" s="39" t="n">
+      <c r="K31" s="39" t="n">
         <v>7254</v>
       </c>
-      <c r="M31" s="40" t="n">
+      <c r="L31" s="40" t="n">
         <v>1552</v>
       </c>
-      <c r="N31" s="41" t="n">
+      <c r="M31" s="41" t="n">
         <v>99.90000000000001</v>
       </c>
     </row>
@@ -2557,19 +2484,16 @@
         <v>3297</v>
       </c>
       <c r="I32" s="44" t="n">
-        <v>11209</v>
+        <v>249</v>
       </c>
       <c r="J32" s="44" t="n">
-        <v>249</v>
-      </c>
-      <c r="K32" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="45" t="n">
+      <c r="K32" s="45" t="n">
         <v>5301</v>
       </c>
-      <c r="M32" s="46" t="n"/>
-      <c r="N32" s="47" t="n">
+      <c r="L32" s="46" t="n"/>
+      <c r="M32" s="47" t="n">
         <v>100.1</v>
       </c>
     </row>
@@ -2604,14 +2528,13 @@
         <v>2.3</v>
       </c>
       <c r="H33" s="38" t="n"/>
-      <c r="I33" s="39" t="n"/>
-      <c r="J33" s="38" t="n"/>
-      <c r="K33" s="38" t="n">
+      <c r="I33" s="38" t="n"/>
+      <c r="J33" s="38" t="n">
         <v>4.2</v>
       </c>
-      <c r="L33" s="39" t="n"/>
-      <c r="M33" s="40" t="n"/>
-      <c r="N33" s="41" t="n"/>
+      <c r="K33" s="39" t="n"/>
+      <c r="L33" s="40" t="n"/>
+      <c r="M33" s="41" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="42" t="inlineStr">
@@ -2650,20 +2573,17 @@
       <c r="H34" s="44" t="n">
         <v>2780</v>
       </c>
-      <c r="I34" s="45" t="n">
-        <v>8618</v>
+      <c r="I34" s="44" t="n">
+        <v>356</v>
       </c>
       <c r="J34" s="44" t="n">
-        <v>356</v>
-      </c>
-      <c r="K34" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="45" t="n">
+      <c r="K34" s="45" t="n">
         <v>6844</v>
       </c>
-      <c r="M34" s="46" t="n"/>
-      <c r="N34" s="47" t="n">
+      <c r="L34" s="46" t="n"/>
+      <c r="M34" s="47" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -2704,20 +2624,17 @@
       <c r="H35" s="38" t="n">
         <v>2889</v>
       </c>
-      <c r="I35" s="39" t="n">
-        <v>8667</v>
+      <c r="I35" s="38" t="n">
+        <v>689</v>
       </c>
       <c r="J35" s="38" t="n">
-        <v>689</v>
-      </c>
-      <c r="K35" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L35" s="39" t="n">
+      <c r="K35" s="39" t="n">
         <v>6909</v>
       </c>
-      <c r="M35" s="40" t="n"/>
-      <c r="N35" s="41" t="n">
+      <c r="L35" s="40" t="n"/>
+      <c r="M35" s="41" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -2758,20 +2675,17 @@
       <c r="H36" s="44" t="n">
         <v>3790</v>
       </c>
-      <c r="I36" s="45" t="n">
-        <v>14023</v>
+      <c r="I36" s="44" t="n">
+        <v>367</v>
       </c>
       <c r="J36" s="44" t="n">
-        <v>367</v>
-      </c>
-      <c r="K36" s="44" t="n">
         <v>2.7</v>
       </c>
-      <c r="L36" s="45" t="n">
+      <c r="K36" s="45" t="n">
         <v>7853</v>
       </c>
-      <c r="M36" s="46" t="n"/>
-      <c r="N36" s="47" t="n">
+      <c r="L36" s="46" t="n"/>
+      <c r="M36" s="47" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -2810,18 +2724,17 @@
         <v>2.7</v>
       </c>
       <c r="H37" s="38" t="n"/>
-      <c r="I37" s="39" t="n"/>
+      <c r="I37" s="38" t="n">
+        <v>210</v>
+      </c>
       <c r="J37" s="38" t="n">
-        <v>210</v>
-      </c>
-      <c r="K37" s="38" t="n">
         <v>3.5</v>
       </c>
-      <c r="L37" s="39" t="n">
+      <c r="K37" s="39" t="n">
         <v>3030</v>
       </c>
-      <c r="M37" s="40" t="n"/>
-      <c r="N37" s="41" t="n">
+      <c r="L37" s="40" t="n"/>
+      <c r="M37" s="41" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -2862,20 +2775,17 @@
       <c r="H38" s="44" t="n">
         <v>2544</v>
       </c>
-      <c r="I38" s="45" t="n">
-        <v>7632</v>
+      <c r="I38" s="44" t="n">
+        <v>374</v>
       </c>
       <c r="J38" s="44" t="n">
-        <v>374</v>
-      </c>
-      <c r="K38" s="44" t="n">
         <v>2.5</v>
       </c>
-      <c r="L38" s="45" t="n">
+      <c r="K38" s="45" t="n">
         <v>4242</v>
       </c>
-      <c r="M38" s="46" t="n"/>
-      <c r="N38" s="47" t="n">
+      <c r="L38" s="46" t="n"/>
+      <c r="M38" s="47" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -2916,20 +2826,17 @@
       <c r="H39" s="38" t="n">
         <v>2904</v>
       </c>
-      <c r="I39" s="39" t="n">
-        <v>9292</v>
+      <c r="I39" s="38" t="n">
+        <v>390</v>
       </c>
       <c r="J39" s="38" t="n">
-        <v>390</v>
+        <v>5</v>
       </c>
       <c r="K39" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L39" s="38" t="n">
         <v>3233</v>
       </c>
-      <c r="M39" s="38" t="n"/>
-      <c r="N39" s="38" t="n">
+      <c r="L39" s="38" t="n"/>
+      <c r="M39" s="38" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -2968,18 +2875,17 @@
         <v>3</v>
       </c>
       <c r="H40" s="44" t="n"/>
-      <c r="I40" s="45" t="n"/>
+      <c r="I40" s="44" t="n">
+        <v>240</v>
+      </c>
       <c r="J40" s="44" t="n">
-        <v>240</v>
-      </c>
-      <c r="K40" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L40" s="45" t="n">
+      <c r="K40" s="45" t="n">
         <v>6719</v>
       </c>
-      <c r="M40" s="46" t="n"/>
-      <c r="N40" s="47" t="n">
+      <c r="L40" s="46" t="n"/>
+      <c r="M40" s="47" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -3020,18 +2926,15 @@
       <c r="H41" s="38" t="n">
         <v>1792</v>
       </c>
-      <c r="I41" s="39" t="n">
-        <v>3942</v>
-      </c>
-      <c r="J41" s="38" t="n"/>
-      <c r="K41" s="38" t="n">
+      <c r="I41" s="38" t="n"/>
+      <c r="J41" s="38" t="n">
         <v>0.1</v>
       </c>
-      <c r="L41" s="39" t="n">
+      <c r="K41" s="39" t="n">
         <v>6917</v>
       </c>
-      <c r="M41" s="40" t="n"/>
-      <c r="N41" s="41" t="n">
+      <c r="L41" s="40" t="n"/>
+      <c r="M41" s="41" t="n">
         <v>99.8</v>
       </c>
     </row>
@@ -3072,20 +2975,17 @@
       <c r="H42" s="44" t="n">
         <v>4000</v>
       </c>
-      <c r="I42" s="45" t="n">
-        <v>18800</v>
+      <c r="I42" s="44" t="n">
+        <v>587</v>
       </c>
       <c r="J42" s="44" t="n">
-        <v>587</v>
-      </c>
-      <c r="K42" s="44" t="n">
         <v>2.7</v>
       </c>
-      <c r="L42" s="45" t="n">
+      <c r="K42" s="45" t="n">
         <v>4486</v>
       </c>
-      <c r="M42" s="46" t="n"/>
-      <c r="N42" s="47" t="n">
+      <c r="L42" s="46" t="n"/>
+      <c r="M42" s="47" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -3127,19 +3027,16 @@
         <v>2200</v>
       </c>
       <c r="I43" s="38" t="n">
-        <v>6160</v>
+        <v>287</v>
       </c>
       <c r="J43" s="38" t="n">
-        <v>287</v>
-      </c>
-      <c r="K43" s="38" t="n">
         <v>2.8</v>
       </c>
-      <c r="L43" s="39" t="n">
+      <c r="K43" s="39" t="n">
         <v>2675</v>
       </c>
-      <c r="M43" s="40" t="n"/>
-      <c r="N43" s="41" t="n">
+      <c r="L43" s="40" t="n"/>
+      <c r="M43" s="41" t="n">
         <v>98.40000000000001</v>
       </c>
     </row>
@@ -3180,20 +3077,17 @@
       <c r="H44" s="44" t="n">
         <v>2710</v>
       </c>
-      <c r="I44" s="45" t="n">
-        <v>8672</v>
+      <c r="I44" s="44" t="n">
+        <v>395</v>
       </c>
       <c r="J44" s="44" t="n">
-        <v>395</v>
-      </c>
-      <c r="K44" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="L44" s="45" t="n">
+      <c r="K44" s="45" t="n">
         <v>3653</v>
       </c>
-      <c r="M44" s="46" t="n"/>
-      <c r="N44" s="47" t="n">
+      <c r="L44" s="46" t="n"/>
+      <c r="M44" s="47" t="n">
         <v>98.40000000000001</v>
       </c>
     </row>
@@ -3233,15 +3127,14 @@
       </c>
       <c r="H45" s="38" t="n"/>
       <c r="I45" s="38" t="n"/>
-      <c r="J45" s="38" t="n"/>
-      <c r="K45" s="38" t="n">
+      <c r="J45" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="39" t="n">
+      <c r="K45" s="39" t="n">
         <v>10189</v>
       </c>
-      <c r="M45" s="40" t="n"/>
-      <c r="N45" s="41" t="n">
+      <c r="L45" s="40" t="n"/>
+      <c r="M45" s="41" t="n">
         <v>100.1</v>
       </c>
     </row>
@@ -3282,20 +3175,17 @@
       <c r="H46" s="44" t="n">
         <v>2517</v>
       </c>
-      <c r="I46" s="45" t="n">
-        <v>7299</v>
+      <c r="I46" s="44" t="n">
+        <v>280</v>
       </c>
       <c r="J46" s="44" t="n">
-        <v>280</v>
-      </c>
-      <c r="K46" s="44" t="n">
         <v>2.5</v>
       </c>
-      <c r="L46" s="45" t="n">
+      <c r="K46" s="45" t="n">
         <v>3578</v>
       </c>
-      <c r="M46" s="46" t="n"/>
-      <c r="N46" s="47" t="n">
+      <c r="L46" s="46" t="n"/>
+      <c r="M46" s="47" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -3332,14 +3222,13 @@
       </c>
       <c r="G47" s="38" t="n"/>
       <c r="H47" s="38" t="n"/>
-      <c r="I47" s="39" t="n"/>
+      <c r="I47" s="38" t="n"/>
       <c r="J47" s="38" t="n"/>
-      <c r="K47" s="38" t="n"/>
-      <c r="L47" s="39" t="n">
+      <c r="K47" s="39" t="n">
         <v>11235</v>
       </c>
-      <c r="M47" s="40" t="n"/>
-      <c r="N47" s="41" t="n">
+      <c r="L47" s="40" t="n"/>
+      <c r="M47" s="41" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -3378,18 +3267,17 @@
         <v>3.2</v>
       </c>
       <c r="H48" s="44" t="n"/>
-      <c r="I48" s="45" t="n"/>
+      <c r="I48" s="44" t="n">
+        <v>323</v>
+      </c>
       <c r="J48" s="44" t="n">
-        <v>323</v>
-      </c>
-      <c r="K48" s="44" t="n">
         <v>2.7</v>
       </c>
-      <c r="L48" s="45" t="n">
+      <c r="K48" s="45" t="n">
         <v>6169</v>
       </c>
-      <c r="M48" s="46" t="n"/>
-      <c r="N48" s="47" t="n">
+      <c r="L48" s="46" t="n"/>
+      <c r="M48" s="47" t="n">
         <v>99.5</v>
       </c>
     </row>
@@ -3430,22 +3318,19 @@
       <c r="H49" s="38" t="n">
         <v>4000</v>
       </c>
-      <c r="I49" s="39" t="n">
-        <v>16400</v>
+      <c r="I49" s="38" t="n">
+        <v>564</v>
       </c>
       <c r="J49" s="38" t="n">
-        <v>564</v>
-      </c>
-      <c r="K49" s="38" t="n">
         <v>7.6</v>
       </c>
-      <c r="L49" s="39" t="n">
+      <c r="K49" s="39" t="n">
         <v>8484</v>
       </c>
-      <c r="M49" s="40" t="n">
+      <c r="L49" s="40" t="n">
         <v>3639</v>
       </c>
-      <c r="N49" s="41" t="n">
+      <c r="M49" s="41" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -3484,16 +3369,15 @@
         <v>2.1</v>
       </c>
       <c r="H50" s="44" t="n"/>
-      <c r="I50" s="45" t="n"/>
-      <c r="J50" s="44" t="n"/>
-      <c r="K50" s="44" t="n">
+      <c r="I50" s="44" t="n"/>
+      <c r="J50" s="44" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L50" s="45" t="n">
+      <c r="K50" s="45" t="n">
         <v>7534</v>
       </c>
-      <c r="M50" s="46" t="n"/>
-      <c r="N50" s="47" t="n">
+      <c r="L50" s="46" t="n"/>
+      <c r="M50" s="47" t="n">
         <v>99.59999999999999</v>
       </c>
     </row>
@@ -3534,20 +3418,17 @@
       <c r="H51" s="38" t="n">
         <v>4290</v>
       </c>
-      <c r="I51" s="39" t="n">
-        <v>18876</v>
+      <c r="I51" s="38" t="n">
+        <v>404</v>
       </c>
       <c r="J51" s="38" t="n">
-        <v>404</v>
-      </c>
-      <c r="K51" s="38" t="n">
         <v>6.1</v>
       </c>
-      <c r="L51" s="39" t="n">
+      <c r="K51" s="39" t="n">
         <v>7643</v>
       </c>
-      <c r="M51" s="40" t="n"/>
-      <c r="N51" s="41" t="n">
+      <c r="L51" s="40" t="n"/>
+      <c r="M51" s="41" t="n">
         <v>100.2</v>
       </c>
     </row>
@@ -3588,20 +3469,17 @@
       <c r="H52" s="44" t="n">
         <v>3473</v>
       </c>
-      <c r="I52" s="45" t="n">
-        <v>14586</v>
+      <c r="I52" s="44" t="n">
+        <v>529</v>
       </c>
       <c r="J52" s="44" t="n">
-        <v>529</v>
-      </c>
-      <c r="K52" s="44" t="n">
         <v>3.1</v>
       </c>
-      <c r="L52" s="45" t="n">
+      <c r="K52" s="45" t="n">
         <v>2763</v>
       </c>
-      <c r="M52" s="46" t="n"/>
-      <c r="N52" s="47" t="n">
+      <c r="L52" s="46" t="n"/>
+      <c r="M52" s="47" t="n">
         <v>99.8</v>
       </c>
     </row>
@@ -3640,18 +3518,17 @@
         <v>2.6</v>
       </c>
       <c r="H53" s="38" t="n"/>
-      <c r="I53" s="39" t="n"/>
+      <c r="I53" s="38" t="n">
+        <v>549</v>
+      </c>
       <c r="J53" s="38" t="n">
-        <v>549</v>
-      </c>
-      <c r="K53" s="38" t="n">
         <v>1.1</v>
       </c>
-      <c r="L53" s="39" t="n">
+      <c r="K53" s="39" t="n">
         <v>5430</v>
       </c>
-      <c r="M53" s="40" t="n"/>
-      <c r="N53" s="41" t="n">
+      <c r="L53" s="40" t="n"/>
+      <c r="M53" s="41" t="n">
         <v>99.8</v>
       </c>
     </row>
@@ -3692,20 +3569,17 @@
       <c r="H54" s="44" t="n">
         <v>2850</v>
       </c>
-      <c r="I54" s="45" t="n">
-        <v>8835</v>
+      <c r="I54" s="44" t="n">
+        <v>361</v>
       </c>
       <c r="J54" s="44" t="n">
-        <v>361</v>
-      </c>
-      <c r="K54" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="L54" s="45" t="n">
+      <c r="K54" s="45" t="n">
         <v>6031</v>
       </c>
-      <c r="M54" s="46" t="n"/>
-      <c r="N54" s="47" t="n">
+      <c r="L54" s="46" t="n"/>
+      <c r="M54" s="47" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -3744,18 +3618,17 @@
         <v>4</v>
       </c>
       <c r="H55" s="38" t="n"/>
-      <c r="I55" s="38" t="n"/>
+      <c r="I55" s="38" t="n">
+        <v>354</v>
+      </c>
       <c r="J55" s="38" t="n">
-        <v>354</v>
-      </c>
-      <c r="K55" s="38" t="n">
         <v>2.8</v>
       </c>
-      <c r="L55" s="39" t="n">
+      <c r="K55" s="39" t="n">
         <v>3356</v>
       </c>
-      <c r="M55" s="40" t="n"/>
-      <c r="N55" s="41" t="n">
+      <c r="L55" s="40" t="n"/>
+      <c r="M55" s="41" t="n">
         <v>97.7</v>
       </c>
     </row>
@@ -3797,19 +3670,16 @@
         <v>2510</v>
       </c>
       <c r="I56" s="44" t="n">
-        <v>6526</v>
+        <v>246</v>
       </c>
       <c r="J56" s="44" t="n">
-        <v>246</v>
+        <v>8</v>
       </c>
       <c r="K56" s="44" t="n">
-        <v>8</v>
-      </c>
-      <c r="L56" s="44" t="n">
         <v>7360</v>
       </c>
-      <c r="M56" s="44" t="n"/>
-      <c r="N56" s="44" t="n">
+      <c r="L56" s="44" t="n"/>
+      <c r="M56" s="44" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -3850,20 +3720,17 @@
       <c r="H57" s="38" t="n">
         <v>3600</v>
       </c>
-      <c r="I57" s="39" t="n">
-        <v>12960</v>
+      <c r="I57" s="38" t="n">
+        <v>346</v>
       </c>
       <c r="J57" s="38" t="n">
-        <v>346</v>
-      </c>
-      <c r="K57" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="L57" s="39" t="n">
+      <c r="K57" s="39" t="n">
         <v>6157</v>
       </c>
-      <c r="M57" s="40" t="n"/>
-      <c r="N57" s="41" t="n">
+      <c r="L57" s="40" t="n"/>
+      <c r="M57" s="41" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -3902,18 +3769,17 @@
         <v>2.7</v>
       </c>
       <c r="H58" s="44" t="n"/>
-      <c r="I58" s="45" t="n"/>
+      <c r="I58" s="44" t="n">
+        <v>478</v>
+      </c>
       <c r="J58" s="44" t="n">
-        <v>478</v>
-      </c>
-      <c r="K58" s="44" t="n">
         <v>3.2</v>
       </c>
-      <c r="L58" s="45" t="n">
+      <c r="K58" s="45" t="n">
         <v>5628</v>
       </c>
-      <c r="M58" s="46" t="n"/>
-      <c r="N58" s="47" t="n">
+      <c r="L58" s="46" t="n"/>
+      <c r="M58" s="47" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -3954,20 +3820,17 @@
       <c r="H59" s="38" t="n">
         <v>2712</v>
       </c>
-      <c r="I59" s="39" t="n">
-        <v>8678</v>
+      <c r="I59" s="38" t="n">
+        <v>265</v>
       </c>
       <c r="J59" s="38" t="n">
-        <v>265</v>
-      </c>
-      <c r="K59" s="38" t="n">
         <v>2.8</v>
       </c>
-      <c r="L59" s="39" t="n">
+      <c r="K59" s="39" t="n">
         <v>3531</v>
       </c>
-      <c r="M59" s="40" t="n"/>
-      <c r="N59" s="41" t="n">
+      <c r="L59" s="40" t="n"/>
+      <c r="M59" s="41" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -4008,18 +3871,15 @@
       <c r="H60" s="44" t="n">
         <v>1995</v>
       </c>
-      <c r="I60" s="45" t="n">
-        <v>4987</v>
-      </c>
-      <c r="J60" s="44" t="n"/>
-      <c r="K60" s="44" t="n">
+      <c r="I60" s="44" t="n"/>
+      <c r="J60" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="L60" s="45" t="n">
+      <c r="K60" s="45" t="n">
         <v>6782</v>
       </c>
-      <c r="M60" s="46" t="n"/>
-      <c r="N60" s="47" t="n">
+      <c r="L60" s="46" t="n"/>
+      <c r="M60" s="47" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -4060,18 +3920,15 @@
       <c r="H61" s="38" t="n">
         <v>3108</v>
       </c>
-      <c r="I61" s="39" t="n">
-        <v>10567</v>
-      </c>
-      <c r="J61" s="38" t="n"/>
-      <c r="K61" s="38" t="n">
+      <c r="I61" s="38" t="n"/>
+      <c r="J61" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L61" s="39" t="n">
+      <c r="K61" s="39" t="n">
         <v>10308</v>
       </c>
-      <c r="M61" s="40" t="n"/>
-      <c r="N61" s="41" t="n">
+      <c r="L61" s="40" t="n"/>
+      <c r="M61" s="41" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -4113,19 +3970,16 @@
         <v>3104</v>
       </c>
       <c r="I62" s="44" t="n">
-        <v>9932</v>
+        <v>614</v>
       </c>
       <c r="J62" s="44" t="n">
-        <v>614</v>
+        <v>7</v>
       </c>
       <c r="K62" s="44" t="n">
-        <v>7</v>
-      </c>
-      <c r="L62" s="44" t="n">
         <v>4901</v>
       </c>
-      <c r="M62" s="44" t="n"/>
-      <c r="N62" s="44" t="n">
+      <c r="L62" s="44" t="n"/>
+      <c r="M62" s="44" t="n">
         <v>97.8</v>
       </c>
     </row>
@@ -4166,20 +4020,17 @@
       <c r="H63" s="38" t="n">
         <v>2745</v>
       </c>
-      <c r="I63" s="39" t="n">
-        <v>8784</v>
+      <c r="I63" s="38" t="n">
+        <v>370</v>
       </c>
       <c r="J63" s="38" t="n">
-        <v>370</v>
-      </c>
-      <c r="K63" s="38" t="n">
         <v>2.5</v>
       </c>
-      <c r="L63" s="39" t="n">
+      <c r="K63" s="39" t="n">
         <v>5554</v>
       </c>
-      <c r="M63" s="40" t="n"/>
-      <c r="N63" s="41" t="n">
+      <c r="L63" s="40" t="n"/>
+      <c r="M63" s="41" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4220,20 +4071,17 @@
       <c r="H64" s="44" t="n">
         <v>3137</v>
       </c>
-      <c r="I64" s="45" t="n">
-        <v>10665</v>
+      <c r="I64" s="44" t="n">
+        <v>279</v>
       </c>
       <c r="J64" s="44" t="n">
-        <v>279</v>
-      </c>
-      <c r="K64" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="L64" s="45" t="n">
+      <c r="K64" s="45" t="n">
         <v>5574</v>
       </c>
-      <c r="M64" s="46" t="n"/>
-      <c r="N64" s="47" t="n">
+      <c r="L64" s="46" t="n"/>
+      <c r="M64" s="47" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -4274,20 +4122,17 @@
       <c r="H65" s="38" t="n">
         <v>3030</v>
       </c>
-      <c r="I65" s="39" t="n">
-        <v>10302</v>
+      <c r="I65" s="38" t="n">
+        <v>216</v>
       </c>
       <c r="J65" s="38" t="n">
-        <v>216</v>
-      </c>
-      <c r="K65" s="38" t="n">
         <v>3.3</v>
       </c>
-      <c r="L65" s="39" t="n">
+      <c r="K65" s="39" t="n">
         <v>6631</v>
       </c>
-      <c r="M65" s="40" t="n"/>
-      <c r="N65" s="41" t="n">
+      <c r="L65" s="40" t="n"/>
+      <c r="M65" s="41" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -4328,20 +4173,17 @@
       <c r="H66" s="44" t="n">
         <v>3965</v>
       </c>
-      <c r="I66" s="45" t="n">
-        <v>16653</v>
+      <c r="I66" s="44" t="n">
+        <v>725</v>
       </c>
       <c r="J66" s="44" t="n">
-        <v>725</v>
-      </c>
-      <c r="K66" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="L66" s="45" t="n">
+      <c r="K66" s="45" t="n">
         <v>2503</v>
       </c>
-      <c r="M66" s="46" t="n"/>
-      <c r="N66" s="47" t="n">
+      <c r="L66" s="46" t="n"/>
+      <c r="M66" s="47" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -4382,20 +4224,17 @@
       <c r="H67" s="38" t="n">
         <v>3800</v>
       </c>
-      <c r="I67" s="39" t="n">
-        <v>14440</v>
+      <c r="I67" s="38" t="n">
+        <v>399</v>
       </c>
       <c r="J67" s="38" t="n">
-        <v>399</v>
+        <v>5</v>
       </c>
       <c r="K67" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L67" s="38" t="n">
         <v>4543</v>
       </c>
-      <c r="M67" s="38" t="n"/>
-      <c r="N67" s="38" t="n">
+      <c r="L67" s="38" t="n"/>
+      <c r="M67" s="38" t="n">
         <v>98</v>
       </c>
     </row>
@@ -4436,18 +4275,15 @@
       <c r="H68" s="44" t="n">
         <v>3024</v>
       </c>
-      <c r="I68" s="45" t="n">
-        <v>9676</v>
-      </c>
-      <c r="J68" s="44" t="n"/>
+      <c r="I68" s="44" t="n"/>
+      <c r="J68" s="44" t="n">
+        <v>4</v>
+      </c>
       <c r="K68" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="L68" s="44" t="n">
         <v>2282</v>
       </c>
-      <c r="M68" s="44" t="n"/>
-      <c r="N68" s="44" t="n">
+      <c r="L68" s="44" t="n"/>
+      <c r="M68" s="44" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4488,20 +4324,17 @@
       <c r="H69" s="38" t="n">
         <v>2908</v>
       </c>
-      <c r="I69" s="39" t="n">
-        <v>9305</v>
+      <c r="I69" s="38" t="n">
+        <v>370</v>
       </c>
       <c r="J69" s="38" t="n">
-        <v>370</v>
-      </c>
-      <c r="K69" s="38" t="n">
         <v>4.1</v>
       </c>
-      <c r="L69" s="39" t="n">
+      <c r="K69" s="39" t="n">
         <v>6039</v>
       </c>
-      <c r="M69" s="40" t="n"/>
-      <c r="N69" s="41" t="n">
+      <c r="L69" s="40" t="n"/>
+      <c r="M69" s="41" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -4542,20 +4375,17 @@
       <c r="H70" s="44" t="n">
         <v>1783</v>
       </c>
-      <c r="I70" s="45" t="n">
-        <v>3922</v>
+      <c r="I70" s="44" t="n">
+        <v>270</v>
       </c>
       <c r="J70" s="44" t="n">
-        <v>270</v>
-      </c>
-      <c r="K70" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="L70" s="45" t="n">
+      <c r="K70" s="45" t="n">
         <v>9038</v>
       </c>
-      <c r="M70" s="46" t="n"/>
-      <c r="N70" s="47" t="n">
+      <c r="L70" s="46" t="n"/>
+      <c r="M70" s="47" t="n">
         <v>99.40000000000001</v>
       </c>
     </row>
@@ -4596,20 +4426,17 @@
       <c r="H71" s="38" t="n">
         <v>3810</v>
       </c>
-      <c r="I71" s="39" t="n">
-        <v>16002</v>
+      <c r="I71" s="38" t="n">
+        <v>337</v>
       </c>
       <c r="J71" s="38" t="n">
-        <v>337</v>
-      </c>
-      <c r="K71" s="38" t="n">
         <v>2.7</v>
       </c>
-      <c r="L71" s="39" t="n">
+      <c r="K71" s="39" t="n">
         <v>3493</v>
       </c>
-      <c r="M71" s="40" t="n"/>
-      <c r="N71" s="41" t="n">
+      <c r="L71" s="40" t="n"/>
+      <c r="M71" s="41" t="n">
         <v>97.5</v>
       </c>
     </row>
@@ -4648,16 +4475,15 @@
         <v>2.4</v>
       </c>
       <c r="H72" s="44" t="n"/>
-      <c r="I72" s="45" t="n"/>
-      <c r="J72" s="44" t="n"/>
-      <c r="K72" s="44" t="n">
+      <c r="I72" s="44" t="n"/>
+      <c r="J72" s="44" t="n">
         <v>0.9</v>
       </c>
-      <c r="L72" s="45" t="n">
+      <c r="K72" s="45" t="n">
         <v>5438</v>
       </c>
-      <c r="M72" s="46" t="n"/>
-      <c r="N72" s="47" t="n">
+      <c r="L72" s="46" t="n"/>
+      <c r="M72" s="47" t="n">
         <v>99.2</v>
       </c>
     </row>
@@ -4692,14 +4518,13 @@
         <v>2.8</v>
       </c>
       <c r="H73" s="38" t="n"/>
-      <c r="I73" s="39" t="n"/>
-      <c r="J73" s="38" t="n"/>
-      <c r="K73" s="38" t="n">
+      <c r="I73" s="38" t="n"/>
+      <c r="J73" s="38" t="n">
         <v>5.8</v>
       </c>
-      <c r="L73" s="39" t="n"/>
-      <c r="M73" s="40" t="n"/>
-      <c r="N73" s="41" t="n"/>
+      <c r="K73" s="39" t="n"/>
+      <c r="L73" s="40" t="n"/>
+      <c r="M73" s="41" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="42" t="inlineStr">
@@ -4738,20 +4563,17 @@
       <c r="H74" s="44" t="n">
         <v>2728</v>
       </c>
-      <c r="I74" s="45" t="n">
-        <v>8456</v>
+      <c r="I74" s="44" t="n">
+        <v>249</v>
       </c>
       <c r="J74" s="44" t="n">
-        <v>249</v>
+        <v>6</v>
       </c>
       <c r="K74" s="44" t="n">
-        <v>6</v>
-      </c>
-      <c r="L74" s="44" t="n">
         <v>3612</v>
       </c>
-      <c r="M74" s="44" t="n"/>
-      <c r="N74" s="44" t="n">
+      <c r="L74" s="44" t="n"/>
+      <c r="M74" s="44" t="n">
         <v>98.40000000000001</v>
       </c>
     </row>
@@ -4790,12 +4612,11 @@
       <c r="H75" s="38" t="n"/>
       <c r="I75" s="38" t="n"/>
       <c r="J75" s="38" t="n"/>
-      <c r="K75" s="38" t="n"/>
-      <c r="L75" s="39" t="n">
+      <c r="K75" s="39" t="n">
         <v>11934</v>
       </c>
-      <c r="M75" s="40" t="n"/>
-      <c r="N75" s="41" t="n">
+      <c r="L75" s="40" t="n"/>
+      <c r="M75" s="41" t="n">
         <v>99.90000000000001</v>
       </c>
     </row>
@@ -4837,19 +4658,16 @@
         <v>3226</v>
       </c>
       <c r="I76" s="44" t="n">
-        <v>10968</v>
+        <v>418</v>
       </c>
       <c r="J76" s="44" t="n">
-        <v>418</v>
+        <v>2.9</v>
       </c>
       <c r="K76" s="44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L76" s="44" t="n">
         <v>7344</v>
       </c>
-      <c r="M76" s="44" t="n"/>
-      <c r="N76" s="44" t="n">
+      <c r="L76" s="44" t="n"/>
+      <c r="M76" s="44" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -4890,20 +4708,17 @@
       <c r="H77" s="38" t="n">
         <v>2120</v>
       </c>
-      <c r="I77" s="39" t="n">
-        <v>5300</v>
+      <c r="I77" s="38" t="n">
+        <v>352</v>
       </c>
       <c r="J77" s="38" t="n">
-        <v>352</v>
+        <v>1</v>
       </c>
       <c r="K77" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="38" t="n">
         <v>7116</v>
       </c>
-      <c r="M77" s="38" t="n"/>
-      <c r="N77" s="38" t="n">
+      <c r="L77" s="38" t="n"/>
+      <c r="M77" s="38" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -4944,22 +4759,19 @@
       <c r="H78" s="44" t="n">
         <v>2723</v>
       </c>
-      <c r="I78" s="45" t="n">
-        <v>8441</v>
+      <c r="I78" s="44" t="n">
+        <v>299</v>
       </c>
       <c r="J78" s="44" t="n">
-        <v>299</v>
+        <v>4</v>
       </c>
       <c r="K78" s="44" t="n">
-        <v>4</v>
+        <v>10353</v>
       </c>
       <c r="L78" s="44" t="n">
-        <v>10353</v>
+        <v>1760</v>
       </c>
       <c r="M78" s="44" t="n">
-        <v>1760</v>
-      </c>
-      <c r="N78" s="44" t="n">
         <v>100.1</v>
       </c>
     </row>
@@ -5000,20 +4812,17 @@
       <c r="H79" s="38" t="n">
         <v>3046</v>
       </c>
-      <c r="I79" s="39" t="n">
-        <v>9442</v>
+      <c r="I79" s="38" t="n">
+        <v>516</v>
       </c>
       <c r="J79" s="38" t="n">
-        <v>516</v>
+        <v>4.5</v>
       </c>
       <c r="K79" s="38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L79" s="38" t="n">
         <v>2858</v>
       </c>
-      <c r="M79" s="38" t="n"/>
-      <c r="N79" s="38" t="n">
+      <c r="L79" s="38" t="n"/>
+      <c r="M79" s="38" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -5046,14 +4855,13 @@
       </c>
       <c r="G80" s="48" t="n"/>
       <c r="H80" s="44" t="n"/>
-      <c r="I80" s="45" t="n"/>
+      <c r="I80" s="44" t="n"/>
       <c r="J80" s="44" t="n"/>
-      <c r="K80" s="44" t="n"/>
-      <c r="L80" s="44" t="n">
+      <c r="K80" s="44" t="n">
         <v>8294</v>
       </c>
-      <c r="M80" s="44" t="n"/>
-      <c r="N80" s="44" t="n">
+      <c r="L80" s="44" t="n"/>
+      <c r="M80" s="44" t="n">
         <v>99.40000000000001</v>
       </c>
     </row>
@@ -5094,20 +4902,17 @@
       <c r="H81" s="38" t="n">
         <v>2625</v>
       </c>
-      <c r="I81" s="39" t="n">
-        <v>7875</v>
+      <c r="I81" s="38" t="n">
+        <v>285</v>
       </c>
       <c r="J81" s="38" t="n">
-        <v>285</v>
+        <v>2.7</v>
       </c>
       <c r="K81" s="38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L81" s="38" t="n">
         <v>7390</v>
       </c>
-      <c r="M81" s="38" t="n"/>
-      <c r="N81" s="38" t="n">
+      <c r="L81" s="38" t="n"/>
+      <c r="M81" s="38" t="n">
         <v>98.40000000000001</v>
       </c>
     </row>
@@ -5148,20 +4953,17 @@
       <c r="H82" s="44" t="n">
         <v>3981</v>
       </c>
-      <c r="I82" s="45" t="n">
-        <v>14729</v>
+      <c r="I82" s="44" t="n">
+        <v>474</v>
       </c>
       <c r="J82" s="44" t="n">
-        <v>474</v>
-      </c>
-      <c r="K82" s="44" t="n">
         <v>2.6</v>
       </c>
-      <c r="L82" s="45" t="n">
+      <c r="K82" s="45" t="n">
         <v>5958</v>
       </c>
-      <c r="M82" s="46" t="n"/>
-      <c r="N82" s="47" t="n">
+      <c r="L82" s="46" t="n"/>
+      <c r="M82" s="47" t="n">
         <v>97.59999999999999</v>
       </c>
     </row>
@@ -5202,20 +5004,17 @@
       <c r="H83" s="38" t="n">
         <v>2510</v>
       </c>
-      <c r="I83" s="39" t="n">
-        <v>7028</v>
+      <c r="I83" s="38" t="n">
+        <v>282</v>
       </c>
       <c r="J83" s="38" t="n">
-        <v>282</v>
+        <v>3</v>
       </c>
       <c r="K83" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L83" s="38" t="n">
         <v>9336</v>
       </c>
-      <c r="M83" s="38" t="n"/>
-      <c r="N83" s="38" t="n">
+      <c r="L83" s="38" t="n"/>
+      <c r="M83" s="38" t="n">
         <v>97.09999999999999</v>
       </c>
     </row>
@@ -5256,20 +5055,17 @@
       <c r="H84" s="44" t="n">
         <v>3000</v>
       </c>
-      <c r="I84" s="45" t="n">
-        <v>9900</v>
+      <c r="I84" s="44" t="n">
+        <v>297</v>
       </c>
       <c r="J84" s="44" t="n">
-        <v>297</v>
+        <v>2.6</v>
       </c>
       <c r="K84" s="44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L84" s="44" t="n">
         <v>5660</v>
       </c>
-      <c r="M84" s="44" t="n"/>
-      <c r="N84" s="44" t="n">
+      <c r="L84" s="44" t="n"/>
+      <c r="M84" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -5310,20 +5106,17 @@
       <c r="H85" s="38" t="n">
         <v>2800</v>
       </c>
-      <c r="I85" s="39" t="n">
-        <v>9240</v>
+      <c r="I85" s="38" t="n">
+        <v>445</v>
       </c>
       <c r="J85" s="38" t="n">
-        <v>445</v>
+        <v>2.5</v>
       </c>
       <c r="K85" s="38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L85" s="38" t="n">
         <v>4099</v>
       </c>
-      <c r="M85" s="38" t="n"/>
-      <c r="N85" s="38" t="n">
+      <c r="L85" s="38" t="n"/>
+      <c r="M85" s="38" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -5365,21 +5158,18 @@
         <v>3330</v>
       </c>
       <c r="I86" s="44" t="n">
-        <v>13320</v>
+        <v>268</v>
       </c>
       <c r="J86" s="44" t="n">
-        <v>268</v>
+        <v>4</v>
       </c>
       <c r="K86" s="44" t="n">
-        <v>4</v>
+        <v>13601</v>
       </c>
       <c r="L86" s="44" t="n">
-        <v>13601</v>
+        <v>7702</v>
       </c>
       <c r="M86" s="44" t="n">
-        <v>7702</v>
-      </c>
-      <c r="N86" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -5420,20 +5210,17 @@
       <c r="H87" s="38" t="n">
         <v>3066</v>
       </c>
-      <c r="I87" s="39" t="n">
-        <v>10117</v>
+      <c r="I87" s="38" t="n">
+        <v>507</v>
       </c>
       <c r="J87" s="38" t="n">
-        <v>507</v>
+        <v>5</v>
       </c>
       <c r="K87" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L87" s="38" t="n">
         <v>4608</v>
       </c>
-      <c r="M87" s="38" t="n"/>
-      <c r="N87" s="38" t="n">
+      <c r="L87" s="38" t="n"/>
+      <c r="M87" s="38" t="n">
         <v>99</v>
       </c>
     </row>
@@ -5474,20 +5261,17 @@
       <c r="H88" s="44" t="n">
         <v>2470</v>
       </c>
-      <c r="I88" s="45" t="n">
-        <v>6422</v>
+      <c r="I88" s="44" t="n">
+        <v>197</v>
       </c>
       <c r="J88" s="44" t="n">
-        <v>197</v>
-      </c>
-      <c r="K88" s="44" t="n">
         <v>3.5</v>
       </c>
-      <c r="L88" s="45" t="n">
+      <c r="K88" s="45" t="n">
         <v>2352</v>
       </c>
-      <c r="M88" s="46" t="n"/>
-      <c r="N88" s="47" t="n">
+      <c r="L88" s="46" t="n"/>
+      <c r="M88" s="47" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -5528,20 +5312,17 @@
       <c r="H89" s="38" t="n">
         <v>2800</v>
       </c>
-      <c r="I89" s="39" t="n">
-        <v>8960</v>
+      <c r="I89" s="38" t="n">
+        <v>439</v>
       </c>
       <c r="J89" s="38" t="n">
-        <v>439</v>
+        <v>2.8</v>
       </c>
       <c r="K89" s="38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L89" s="38" t="n">
         <v>4589</v>
       </c>
-      <c r="M89" s="38" t="n"/>
-      <c r="N89" s="38" t="n">
+      <c r="L89" s="38" t="n"/>
+      <c r="M89" s="38" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -5583,19 +5364,16 @@
         <v>3268</v>
       </c>
       <c r="I90" s="44" t="n">
-        <v>11764</v>
+        <v>432</v>
       </c>
       <c r="J90" s="44" t="n">
-        <v>432</v>
+        <v>7</v>
       </c>
       <c r="K90" s="44" t="n">
-        <v>7</v>
-      </c>
-      <c r="L90" s="44" t="n">
         <v>5465</v>
       </c>
-      <c r="M90" s="44" t="n"/>
-      <c r="N90" s="44" t="n">
+      <c r="L90" s="44" t="n"/>
+      <c r="M90" s="44" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -5636,20 +5414,17 @@
       <c r="H91" s="38" t="n">
         <v>2733</v>
       </c>
-      <c r="I91" s="39" t="n">
-        <v>9018</v>
+      <c r="I91" s="38" t="n">
+        <v>503</v>
       </c>
       <c r="J91" s="38" t="n">
-        <v>503</v>
+        <v>5</v>
       </c>
       <c r="K91" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L91" s="38" t="n">
         <v>4215</v>
       </c>
-      <c r="M91" s="38" t="n"/>
-      <c r="N91" s="38" t="n">
+      <c r="L91" s="38" t="n"/>
+      <c r="M91" s="38" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -5690,20 +5465,17 @@
       <c r="H92" s="44" t="n">
         <v>2787</v>
       </c>
-      <c r="I92" s="45" t="n">
-        <v>8918</v>
+      <c r="I92" s="44" t="n">
+        <v>408</v>
       </c>
       <c r="J92" s="44" t="n">
-        <v>408</v>
+        <v>4.7</v>
       </c>
       <c r="K92" s="44" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L92" s="44" t="n">
         <v>5960</v>
       </c>
-      <c r="M92" s="44" t="n"/>
-      <c r="N92" s="44" t="n">
+      <c r="L92" s="44" t="n"/>
+      <c r="M92" s="44" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -5744,22 +5516,19 @@
       <c r="H93" s="38" t="n">
         <v>3359</v>
       </c>
-      <c r="I93" s="39" t="n">
-        <v>12428</v>
+      <c r="I93" s="38" t="n">
+        <v>581</v>
       </c>
       <c r="J93" s="38" t="n">
-        <v>581</v>
+        <v>5</v>
       </c>
       <c r="K93" s="38" t="n">
-        <v>5</v>
+        <v>10956</v>
       </c>
       <c r="L93" s="38" t="n">
-        <v>10956</v>
+        <v>4146</v>
       </c>
       <c r="M93" s="38" t="n">
-        <v>4146</v>
-      </c>
-      <c r="N93" s="38" t="n">
         <v>99.90000000000001</v>
       </c>
     </row>
@@ -5800,20 +5569,17 @@
       <c r="H94" s="44" t="n">
         <v>2712</v>
       </c>
-      <c r="I94" s="45" t="n">
-        <v>7593</v>
+      <c r="I94" s="44" t="n">
+        <v>599</v>
       </c>
       <c r="J94" s="44" t="n">
-        <v>599</v>
+        <v>5.2</v>
       </c>
       <c r="K94" s="44" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L94" s="44" t="n">
         <v>6195</v>
       </c>
-      <c r="M94" s="44" t="n"/>
-      <c r="N94" s="44" t="n">
+      <c r="L94" s="44" t="n"/>
+      <c r="M94" s="44" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -5854,18 +5620,15 @@
       <c r="H95" s="38" t="n">
         <v>1823</v>
       </c>
-      <c r="I95" s="39" t="n">
-        <v>4375</v>
-      </c>
-      <c r="J95" s="38" t="n"/>
+      <c r="I95" s="38" t="n"/>
+      <c r="J95" s="38" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K95" s="38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L95" s="38" t="n">
         <v>3905</v>
       </c>
-      <c r="M95" s="38" t="n"/>
-      <c r="N95" s="38" t="n">
+      <c r="L95" s="38" t="n"/>
+      <c r="M95" s="38" t="n">
         <v>99.7</v>
       </c>
     </row>
@@ -5906,20 +5669,17 @@
       <c r="H96" s="44" t="n">
         <v>3220</v>
       </c>
-      <c r="I96" s="45" t="n">
-        <v>10948</v>
+      <c r="I96" s="44" t="n">
+        <v>368</v>
       </c>
       <c r="J96" s="44" t="n">
-        <v>368</v>
+        <v>4.5</v>
       </c>
       <c r="K96" s="44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L96" s="44" t="n">
         <v>4800</v>
       </c>
-      <c r="M96" s="44" t="n"/>
-      <c r="N96" s="44" t="n">
+      <c r="L96" s="44" t="n"/>
+      <c r="M96" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -5961,19 +5721,16 @@
         <v>3273</v>
       </c>
       <c r="I97" s="38" t="n">
-        <v>13092</v>
+        <v>336</v>
       </c>
       <c r="J97" s="38" t="n">
-        <v>336</v>
+        <v>3</v>
       </c>
       <c r="K97" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L97" s="38" t="n">
         <v>2421</v>
       </c>
-      <c r="M97" s="38" t="n"/>
-      <c r="N97" s="38" t="n">
+      <c r="L97" s="38" t="n"/>
+      <c r="M97" s="38" t="n">
         <v>99</v>
       </c>
     </row>
@@ -6012,12 +5769,11 @@
       <c r="H98" s="44" t="n"/>
       <c r="I98" s="44" t="n"/>
       <c r="J98" s="44" t="n"/>
-      <c r="K98" s="44" t="n"/>
-      <c r="L98" s="44" t="n">
+      <c r="K98" s="44" t="n">
         <v>7211</v>
       </c>
-      <c r="M98" s="44" t="n"/>
-      <c r="N98" s="44" t="n">
+      <c r="L98" s="44" t="n"/>
+      <c r="M98" s="44" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -6058,18 +5814,15 @@
       <c r="H99" s="38" t="n">
         <v>2352</v>
       </c>
-      <c r="I99" s="39" t="n">
-        <v>6350</v>
-      </c>
-      <c r="J99" s="38" t="n"/>
+      <c r="I99" s="38" t="n"/>
+      <c r="J99" s="38" t="n">
+        <v>4</v>
+      </c>
       <c r="K99" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="L99" s="38" t="n">
         <v>7795</v>
       </c>
-      <c r="M99" s="38" t="n"/>
-      <c r="N99" s="38" t="n">
+      <c r="L99" s="38" t="n"/>
+      <c r="M99" s="38" t="n">
         <v>100.3</v>
       </c>
     </row>
@@ -6110,18 +5863,15 @@
       <c r="H100" s="44" t="n">
         <v>2508</v>
       </c>
-      <c r="I100" s="45" t="n">
-        <v>7022</v>
-      </c>
-      <c r="J100" s="44" t="n"/>
+      <c r="I100" s="44" t="n"/>
+      <c r="J100" s="44" t="n">
+        <v>5</v>
+      </c>
       <c r="K100" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="L100" s="44" t="n">
         <v>4826</v>
       </c>
-      <c r="M100" s="44" t="n"/>
-      <c r="N100" s="44" t="n">
+      <c r="L100" s="44" t="n"/>
+      <c r="M100" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -6163,19 +5913,16 @@
         <v>3513</v>
       </c>
       <c r="I101" s="38" t="n">
-        <v>12998</v>
+        <v>299</v>
       </c>
       <c r="J101" s="38" t="n">
-        <v>299</v>
+        <v>6</v>
       </c>
       <c r="K101" s="38" t="n">
-        <v>6</v>
-      </c>
-      <c r="L101" s="38" t="n">
         <v>5552</v>
       </c>
-      <c r="M101" s="38" t="n"/>
-      <c r="N101" s="38" t="n">
+      <c r="L101" s="38" t="n"/>
+      <c r="M101" s="38" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -6216,20 +5963,17 @@
       <c r="H102" s="44" t="n">
         <v>4572</v>
       </c>
-      <c r="I102" s="45" t="n">
-        <v>20574</v>
+      <c r="I102" s="44" t="n">
+        <v>328</v>
       </c>
       <c r="J102" s="44" t="n">
-        <v>328</v>
+        <v>4.5</v>
       </c>
       <c r="K102" s="44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L102" s="44" t="n">
         <v>9657</v>
       </c>
-      <c r="M102" s="44" t="n"/>
-      <c r="N102" s="44" t="n">
+      <c r="L102" s="44" t="n"/>
+      <c r="M102" s="44" t="n">
         <v>98</v>
       </c>
     </row>
@@ -6266,14 +6010,13 @@
       </c>
       <c r="G103" s="49" t="n"/>
       <c r="H103" s="38" t="n"/>
-      <c r="I103" s="39" t="n"/>
+      <c r="I103" s="38" t="n"/>
       <c r="J103" s="38" t="n"/>
-      <c r="K103" s="38" t="n"/>
-      <c r="L103" s="38" t="n">
+      <c r="K103" s="38" t="n">
         <v>3942</v>
       </c>
-      <c r="M103" s="38" t="n"/>
-      <c r="N103" s="38" t="n">
+      <c r="L103" s="38" t="n"/>
+      <c r="M103" s="38" t="n">
         <v>97.59999999999999</v>
       </c>
     </row>
@@ -6314,20 +6057,17 @@
       <c r="H104" s="44" t="n">
         <v>1560</v>
       </c>
-      <c r="I104" s="45" t="n">
-        <v>3900</v>
+      <c r="I104" s="44" t="n">
+        <v>493</v>
       </c>
       <c r="J104" s="44" t="n">
-        <v>493</v>
+        <v>0.4</v>
       </c>
       <c r="K104" s="44" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L104" s="44" t="n">
         <v>5573</v>
       </c>
-      <c r="M104" s="44" t="n"/>
-      <c r="N104" s="44" t="n">
+      <c r="L104" s="44" t="n"/>
+      <c r="M104" s="44" t="n">
         <v>99.40000000000001</v>
       </c>
     </row>
@@ -6368,20 +6108,17 @@
       <c r="H105" s="38" t="n">
         <v>3070</v>
       </c>
-      <c r="I105" s="39" t="n">
-        <v>9517</v>
+      <c r="I105" s="38" t="n">
+        <v>259</v>
       </c>
       <c r="J105" s="38" t="n">
-        <v>259</v>
+        <v>4.5</v>
       </c>
       <c r="K105" s="38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L105" s="38" t="n">
         <v>6771</v>
       </c>
-      <c r="M105" s="38" t="n"/>
-      <c r="N105" s="38" t="n">
+      <c r="L105" s="38" t="n"/>
+      <c r="M105" s="38" t="n">
         <v>99</v>
       </c>
     </row>
@@ -6416,16 +6153,15 @@
         <v>2.9</v>
       </c>
       <c r="H106" s="44" t="n"/>
-      <c r="I106" s="45" t="n"/>
+      <c r="I106" s="44" t="n">
+        <v>399</v>
+      </c>
       <c r="J106" s="44" t="n">
-        <v>399</v>
-      </c>
-      <c r="K106" s="44" t="n">
         <v>3.3</v>
       </c>
+      <c r="K106" s="44" t="n"/>
       <c r="L106" s="44" t="n"/>
       <c r="M106" s="44" t="n"/>
-      <c r="N106" s="44" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="36" t="inlineStr">
@@ -6465,19 +6201,16 @@
         <v>3176</v>
       </c>
       <c r="I107" s="38" t="n">
-        <v>11433</v>
+        <v>308</v>
       </c>
       <c r="J107" s="38" t="n">
-        <v>308</v>
+        <v>4.5</v>
       </c>
       <c r="K107" s="38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L107" s="38" t="n">
         <v>5088</v>
       </c>
-      <c r="M107" s="38" t="n"/>
-      <c r="N107" s="38" t="n">
+      <c r="L107" s="38" t="n"/>
+      <c r="M107" s="38" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -6514,14 +6247,13 @@
       </c>
       <c r="G108" s="48" t="n"/>
       <c r="H108" s="44" t="n"/>
-      <c r="I108" s="45" t="n"/>
+      <c r="I108" s="44" t="n"/>
       <c r="J108" s="44" t="n"/>
-      <c r="K108" s="44" t="n"/>
-      <c r="L108" s="44" t="n">
+      <c r="K108" s="44" t="n">
         <v>9984</v>
       </c>
-      <c r="M108" s="44" t="n"/>
-      <c r="N108" s="44" t="n">
+      <c r="L108" s="44" t="n"/>
+      <c r="M108" s="44" t="n">
         <v>99.2</v>
       </c>
     </row>
@@ -6563,19 +6295,16 @@
         <v>2640</v>
       </c>
       <c r="I109" s="38" t="n">
-        <v>8712</v>
+        <v>535</v>
       </c>
       <c r="J109" s="38" t="n">
-        <v>535</v>
+        <v>2.6</v>
       </c>
       <c r="K109" s="38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L109" s="38" t="n">
         <v>5554</v>
       </c>
-      <c r="M109" s="38" t="n"/>
-      <c r="N109" s="38" t="n">
+      <c r="L109" s="38" t="n"/>
+      <c r="M109" s="38" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -6616,20 +6345,17 @@
       <c r="H110" s="44" t="n">
         <v>2064</v>
       </c>
-      <c r="I110" s="45" t="n">
-        <v>4540</v>
+      <c r="I110" s="44" t="n">
+        <v>311</v>
       </c>
       <c r="J110" s="44" t="n">
-        <v>311</v>
+        <v>1.4</v>
       </c>
       <c r="K110" s="44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L110" s="44" t="n">
         <v>5073</v>
       </c>
-      <c r="M110" s="44" t="n"/>
-      <c r="N110" s="44" t="n">
+      <c r="L110" s="44" t="n"/>
+      <c r="M110" s="44" t="n">
         <v>99.2</v>
       </c>
     </row>
@@ -6666,14 +6392,13 @@
       </c>
       <c r="G111" s="49" t="n"/>
       <c r="H111" s="38" t="n"/>
-      <c r="I111" s="39" t="n"/>
+      <c r="I111" s="38" t="n"/>
       <c r="J111" s="38" t="n"/>
-      <c r="K111" s="38" t="n"/>
-      <c r="L111" s="38" t="n">
+      <c r="K111" s="38" t="n">
         <v>5560</v>
       </c>
-      <c r="M111" s="38" t="n"/>
-      <c r="N111" s="38" t="n">
+      <c r="L111" s="38" t="n"/>
+      <c r="M111" s="38" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -6714,20 +6439,17 @@
       <c r="H112" s="44" t="n">
         <v>3100</v>
       </c>
-      <c r="I112" s="45" t="n">
-        <v>9610</v>
+      <c r="I112" s="44" t="n">
+        <v>790</v>
       </c>
       <c r="J112" s="44" t="n">
-        <v>790</v>
+        <v>5.7</v>
       </c>
       <c r="K112" s="44" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L112" s="44" t="n">
         <v>7664</v>
       </c>
-      <c r="M112" s="44" t="n"/>
-      <c r="N112" s="44" t="n">
+      <c r="L112" s="44" t="n"/>
+      <c r="M112" s="44" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -6768,20 +6490,17 @@
       <c r="H113" s="38" t="n">
         <v>2640</v>
       </c>
-      <c r="I113" s="39" t="n">
-        <v>7920</v>
+      <c r="I113" s="38" t="n">
+        <v>366</v>
       </c>
       <c r="J113" s="38" t="n">
-        <v>366</v>
+        <v>4.5</v>
       </c>
       <c r="K113" s="38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L113" s="38" t="n">
         <v>3274</v>
       </c>
-      <c r="M113" s="38" t="n"/>
-      <c r="N113" s="38" t="n">
+      <c r="L113" s="38" t="n"/>
+      <c r="M113" s="38" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -6823,19 +6542,16 @@
         <v>3617</v>
       </c>
       <c r="I114" s="44" t="n">
-        <v>13744</v>
+        <v>423</v>
       </c>
       <c r="J114" s="44" t="n">
-        <v>423</v>
+        <v>2.5</v>
       </c>
       <c r="K114" s="44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L114" s="44" t="n">
         <v>3959</v>
       </c>
-      <c r="M114" s="44" t="n"/>
-      <c r="N114" s="44" t="n">
+      <c r="L114" s="44" t="n"/>
+      <c r="M114" s="44" t="n">
         <v>97.7</v>
       </c>
     </row>
@@ -6876,20 +6592,17 @@
       <c r="H115" s="38" t="n">
         <v>4051</v>
       </c>
-      <c r="I115" s="39" t="n">
-        <v>16204</v>
+      <c r="I115" s="38" t="n">
+        <v>1168</v>
       </c>
       <c r="J115" s="38" t="n">
-        <v>1168</v>
+        <v>5.1</v>
       </c>
       <c r="K115" s="38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L115" s="38" t="n">
         <v>6297</v>
       </c>
-      <c r="M115" s="38" t="n"/>
-      <c r="N115" s="38" t="n">
+      <c r="L115" s="38" t="n"/>
+      <c r="M115" s="38" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -6928,16 +6641,15 @@
         <v>2.6</v>
       </c>
       <c r="H116" s="44" t="n"/>
-      <c r="I116" s="45" t="n"/>
-      <c r="J116" s="44" t="n"/>
+      <c r="I116" s="44" t="n"/>
+      <c r="J116" s="44" t="n">
+        <v>3.6</v>
+      </c>
       <c r="K116" s="44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L116" s="44" t="n">
         <v>6151</v>
       </c>
-      <c r="M116" s="44" t="n"/>
-      <c r="N116" s="44" t="n">
+      <c r="L116" s="44" t="n"/>
+      <c r="M116" s="44" t="n">
         <v>101.6</v>
       </c>
     </row>
@@ -6976,16 +6688,15 @@
         <v>2.6</v>
       </c>
       <c r="H117" s="38" t="n"/>
-      <c r="I117" s="39" t="n"/>
-      <c r="J117" s="38" t="n"/>
+      <c r="I117" s="38" t="n"/>
+      <c r="J117" s="38" t="n">
+        <v>7</v>
+      </c>
       <c r="K117" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="L117" s="38" t="n">
         <v>4430</v>
       </c>
-      <c r="M117" s="38" t="n"/>
-      <c r="N117" s="38" t="n">
+      <c r="L117" s="38" t="n"/>
+      <c r="M117" s="38" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -7026,20 +6737,17 @@
       <c r="H118" s="44" t="n">
         <v>4253</v>
       </c>
-      <c r="I118" s="45" t="n">
-        <v>18287</v>
+      <c r="I118" s="44" t="n">
+        <v>352</v>
       </c>
       <c r="J118" s="44" t="n">
-        <v>352</v>
+        <v>6.6</v>
       </c>
       <c r="K118" s="44" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L118" s="44" t="n">
         <v>9538</v>
       </c>
-      <c r="M118" s="44" t="n"/>
-      <c r="N118" s="44" t="n">
+      <c r="L118" s="44" t="n"/>
+      <c r="M118" s="44" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -7081,19 +6789,16 @@
         <v>2837</v>
       </c>
       <c r="I119" s="38" t="n">
-        <v>9362</v>
+        <v>319</v>
       </c>
       <c r="J119" s="38" t="n">
-        <v>319</v>
+        <v>5.5</v>
       </c>
       <c r="K119" s="38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L119" s="38" t="n">
         <v>8178</v>
       </c>
-      <c r="M119" s="38" t="n"/>
-      <c r="N119" s="38" t="n">
+      <c r="L119" s="38" t="n"/>
+      <c r="M119" s="38" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -7134,20 +6839,17 @@
       <c r="H120" s="44" t="n">
         <v>2780</v>
       </c>
-      <c r="I120" s="45" t="n">
-        <v>8618</v>
+      <c r="I120" s="44" t="n">
+        <v>530</v>
       </c>
       <c r="J120" s="44" t="n">
-        <v>530</v>
+        <v>2.8</v>
       </c>
       <c r="K120" s="44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L120" s="44" t="n">
         <v>4061</v>
       </c>
-      <c r="M120" s="44" t="n"/>
-      <c r="N120" s="44" t="n">
+      <c r="L120" s="44" t="n"/>
+      <c r="M120" s="44" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -7188,22 +6890,19 @@
       <c r="H121" s="38" t="n">
         <v>3288</v>
       </c>
-      <c r="I121" s="39" t="n">
-        <v>11508</v>
+      <c r="I121" s="38" t="n">
+        <v>351</v>
       </c>
       <c r="J121" s="38" t="n">
-        <v>351</v>
+        <v>9</v>
       </c>
       <c r="K121" s="38" t="n">
-        <v>9</v>
+        <v>10483</v>
       </c>
       <c r="L121" s="38" t="n">
-        <v>10483</v>
+        <v>2664</v>
       </c>
       <c r="M121" s="38" t="n">
-        <v>2664</v>
-      </c>
-      <c r="N121" s="38" t="n">
         <v>99.8</v>
       </c>
     </row>
@@ -7244,20 +6943,17 @@
       <c r="H122" s="44" t="n">
         <v>2520</v>
       </c>
-      <c r="I122" s="45" t="n">
-        <v>7056</v>
+      <c r="I122" s="44" t="n">
+        <v>529</v>
       </c>
       <c r="J122" s="44" t="n">
-        <v>529</v>
+        <v>3.8</v>
       </c>
       <c r="K122" s="44" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L122" s="44" t="n">
         <v>7266</v>
       </c>
-      <c r="M122" s="44" t="n"/>
-      <c r="N122" s="44" t="n">
+      <c r="L122" s="44" t="n"/>
+      <c r="M122" s="44" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -7294,14 +6990,13 @@
       </c>
       <c r="G123" s="49" t="n"/>
       <c r="H123" s="38" t="n"/>
-      <c r="I123" s="39" t="n"/>
+      <c r="I123" s="38" t="n"/>
       <c r="J123" s="38" t="n"/>
-      <c r="K123" s="38" t="n"/>
-      <c r="L123" s="38" t="n">
+      <c r="K123" s="38" t="n">
         <v>10813</v>
       </c>
-      <c r="M123" s="38" t="n"/>
-      <c r="N123" s="38" t="n">
+      <c r="L123" s="38" t="n"/>
+      <c r="M123" s="38" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -7342,20 +7037,17 @@
       <c r="H124" s="44" t="n">
         <v>3080</v>
       </c>
-      <c r="I124" s="45" t="n">
-        <v>11704</v>
+      <c r="I124" s="44" t="n">
+        <v>236</v>
       </c>
       <c r="J124" s="44" t="n">
-        <v>236</v>
+        <v>3</v>
       </c>
       <c r="K124" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="L124" s="44" t="n">
         <v>4472</v>
       </c>
-      <c r="M124" s="44" t="n"/>
-      <c r="N124" s="44" t="n">
+      <c r="L124" s="44" t="n"/>
+      <c r="M124" s="44" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -7396,20 +7088,17 @@
       <c r="H125" s="38" t="n">
         <v>4003</v>
       </c>
-      <c r="I125" s="39" t="n">
-        <v>15611</v>
+      <c r="I125" s="38" t="n">
+        <v>295</v>
       </c>
       <c r="J125" s="38" t="n">
-        <v>295</v>
-      </c>
-      <c r="K125" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="L125" s="39" t="n">
+      <c r="K125" s="39" t="n">
         <v>5197</v>
       </c>
-      <c r="M125" s="40" t="n"/>
-      <c r="N125" s="41" t="n">
+      <c r="L125" s="40" t="n"/>
+      <c r="M125" s="41" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -7450,20 +7139,17 @@
       <c r="H126" s="44" t="n">
         <v>3718</v>
       </c>
-      <c r="I126" s="45" t="n">
-        <v>14872</v>
+      <c r="I126" s="44" t="n">
+        <v>381</v>
       </c>
       <c r="J126" s="44" t="n">
-        <v>381</v>
+        <v>5</v>
       </c>
       <c r="K126" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="L126" s="44" t="n">
         <v>4750</v>
       </c>
-      <c r="M126" s="44" t="n"/>
-      <c r="N126" s="44" t="n">
+      <c r="L126" s="44" t="n"/>
+      <c r="M126" s="44" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -7504,20 +7190,17 @@
       <c r="H127" s="38" t="n">
         <v>3541</v>
       </c>
-      <c r="I127" s="39" t="n">
-        <v>13455</v>
+      <c r="I127" s="38" t="n">
+        <v>390</v>
       </c>
       <c r="J127" s="38" t="n">
-        <v>390</v>
+        <v>2.6</v>
       </c>
       <c r="K127" s="38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L127" s="38" t="n">
         <v>3040</v>
       </c>
-      <c r="M127" s="38" t="n"/>
-      <c r="N127" s="38" t="n">
+      <c r="L127" s="38" t="n"/>
+      <c r="M127" s="38" t="n">
         <v>97.7</v>
       </c>
     </row>
@@ -7558,20 +7241,17 @@
       <c r="H128" s="44" t="n">
         <v>3158</v>
       </c>
-      <c r="I128" s="45" t="n">
-        <v>12000</v>
+      <c r="I128" s="44" t="n">
+        <v>288</v>
       </c>
       <c r="J128" s="44" t="n">
-        <v>288</v>
+        <v>3.5</v>
       </c>
       <c r="K128" s="44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L128" s="44" t="n">
         <v>10534</v>
       </c>
-      <c r="M128" s="44" t="n"/>
-      <c r="N128" s="44" t="n">
+      <c r="L128" s="44" t="n"/>
+      <c r="M128" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -7612,20 +7292,17 @@
       <c r="H129" s="38" t="n">
         <v>4060</v>
       </c>
-      <c r="I129" s="39" t="n">
-        <v>17458</v>
+      <c r="I129" s="38" t="n">
+        <v>421</v>
       </c>
       <c r="J129" s="38" t="n">
-        <v>421</v>
+        <v>5</v>
       </c>
       <c r="K129" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L129" s="38" t="n">
         <v>4501</v>
       </c>
-      <c r="M129" s="38" t="n"/>
-      <c r="N129" s="38" t="n">
+      <c r="L129" s="38" t="n"/>
+      <c r="M129" s="38" t="n">
         <v>97.7</v>
       </c>
     </row>
@@ -7666,20 +7343,17 @@
       <c r="H130" s="44" t="n">
         <v>3190</v>
       </c>
-      <c r="I130" s="45" t="n">
-        <v>11165</v>
+      <c r="I130" s="44" t="n">
+        <v>620</v>
       </c>
       <c r="J130" s="44" t="n">
-        <v>620</v>
+        <v>4</v>
       </c>
       <c r="K130" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="L130" s="44" t="n">
         <v>4814</v>
       </c>
-      <c r="M130" s="44" t="n"/>
-      <c r="N130" s="44" t="n">
+      <c r="L130" s="44" t="n"/>
+      <c r="M130" s="44" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -7720,20 +7394,17 @@
       <c r="H131" s="38" t="n">
         <v>2606</v>
       </c>
-      <c r="I131" s="39" t="n">
-        <v>6775</v>
+      <c r="I131" s="38" t="n">
+        <v>270</v>
       </c>
       <c r="J131" s="38" t="n">
-        <v>270</v>
-      </c>
-      <c r="K131" s="38" t="n">
         <v>1.3</v>
       </c>
-      <c r="L131" s="39" t="n">
+      <c r="K131" s="39" t="n">
         <v>4016</v>
       </c>
-      <c r="M131" s="40" t="n"/>
-      <c r="N131" s="41" t="n">
+      <c r="L131" s="40" t="n"/>
+      <c r="M131" s="41" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -7772,18 +7443,17 @@
         <v>3.3</v>
       </c>
       <c r="H132" s="44" t="n"/>
-      <c r="I132" s="45" t="n"/>
+      <c r="I132" s="44" t="n">
+        <v>239</v>
+      </c>
       <c r="J132" s="44" t="n">
-        <v>239</v>
+        <v>6</v>
       </c>
       <c r="K132" s="44" t="n">
-        <v>6</v>
-      </c>
-      <c r="L132" s="44" t="n">
         <v>3610</v>
       </c>
-      <c r="M132" s="44" t="n"/>
-      <c r="N132" s="44" t="n">
+      <c r="L132" s="44" t="n"/>
+      <c r="M132" s="44" t="n">
         <v>99.8</v>
       </c>
     </row>
@@ -7824,18 +7494,15 @@
       <c r="H133" s="38" t="n">
         <v>2235</v>
       </c>
-      <c r="I133" s="39" t="n">
-        <v>5364</v>
-      </c>
-      <c r="J133" s="38" t="n"/>
+      <c r="I133" s="38" t="n"/>
+      <c r="J133" s="38" t="n">
+        <v>7.2</v>
+      </c>
       <c r="K133" s="38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L133" s="38" t="n">
         <v>8036</v>
       </c>
-      <c r="M133" s="38" t="n"/>
-      <c r="N133" s="38" t="n">
+      <c r="L133" s="38" t="n"/>
+      <c r="M133" s="38" t="n">
         <v>99.8</v>
       </c>
     </row>
@@ -7877,19 +7544,16 @@
         <v>3491</v>
       </c>
       <c r="I134" s="44" t="n">
-        <v>12916</v>
+        <v>398</v>
       </c>
       <c r="J134" s="44" t="n">
-        <v>398</v>
+        <v>4</v>
       </c>
       <c r="K134" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="L134" s="44" t="n">
         <v>3637</v>
       </c>
-      <c r="M134" s="44" t="n"/>
-      <c r="N134" s="44" t="n">
+      <c r="L134" s="44" t="n"/>
+      <c r="M134" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -7930,20 +7594,17 @@
       <c r="H135" s="38" t="n">
         <v>3111</v>
       </c>
-      <c r="I135" s="39" t="n">
-        <v>9955</v>
+      <c r="I135" s="38" t="n">
+        <v>398</v>
       </c>
       <c r="J135" s="38" t="n">
-        <v>398</v>
+        <v>2.2</v>
       </c>
       <c r="K135" s="38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L135" s="38" t="n">
         <v>6514</v>
       </c>
-      <c r="M135" s="38" t="n"/>
-      <c r="N135" s="38" t="n">
+      <c r="L135" s="38" t="n"/>
+      <c r="M135" s="38" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -7984,16 +7645,13 @@
       <c r="H136" s="44" t="n">
         <v>1830</v>
       </c>
-      <c r="I136" s="45" t="n">
-        <v>4026</v>
-      </c>
+      <c r="I136" s="44" t="n"/>
       <c r="J136" s="44" t="n"/>
-      <c r="K136" s="44" t="n"/>
-      <c r="L136" s="44" t="n">
+      <c r="K136" s="44" t="n">
         <v>6007</v>
       </c>
-      <c r="M136" s="44" t="n"/>
-      <c r="N136" s="44" t="n">
+      <c r="L136" s="44" t="n"/>
+      <c r="M136" s="44" t="n">
         <v>99.59999999999999</v>
       </c>
     </row>
@@ -8034,22 +7692,19 @@
       <c r="H137" s="38" t="n">
         <v>4255</v>
       </c>
-      <c r="I137" s="39" t="n">
-        <v>17871</v>
+      <c r="I137" s="38" t="n">
+        <v>362</v>
       </c>
       <c r="J137" s="38" t="n">
-        <v>362</v>
-      </c>
-      <c r="K137" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="L137" s="39" t="n">
+      <c r="K137" s="39" t="n">
         <v>11546</v>
       </c>
-      <c r="M137" s="40" t="n">
+      <c r="L137" s="40" t="n">
         <v>5860</v>
       </c>
-      <c r="N137" s="41" t="n">
+      <c r="M137" s="41" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -8090,22 +7745,19 @@
       <c r="H138" s="44" t="n">
         <v>4130</v>
       </c>
-      <c r="I138" s="45" t="n">
-        <v>16933</v>
+      <c r="I138" s="44" t="n">
+        <v>417</v>
       </c>
       <c r="J138" s="44" t="n">
-        <v>417</v>
+        <v>9</v>
       </c>
       <c r="K138" s="44" t="n">
-        <v>9</v>
+        <v>6547</v>
       </c>
       <c r="L138" s="44" t="n">
-        <v>6547</v>
+        <v>5416</v>
       </c>
       <c r="M138" s="44" t="n">
-        <v>5416</v>
-      </c>
-      <c r="N138" s="44" t="n">
         <v>97.2</v>
       </c>
     </row>
@@ -8147,19 +7799,16 @@
         <v>2802</v>
       </c>
       <c r="I139" s="38" t="n">
-        <v>8125</v>
+        <v>216</v>
       </c>
       <c r="J139" s="38" t="n">
-        <v>216</v>
+        <v>6</v>
       </c>
       <c r="K139" s="38" t="n">
-        <v>6</v>
-      </c>
-      <c r="L139" s="38" t="n">
         <v>6096</v>
       </c>
-      <c r="M139" s="38" t="n"/>
-      <c r="N139" s="38" t="n">
+      <c r="L139" s="38" t="n"/>
+      <c r="M139" s="38" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -8198,20 +7847,19 @@
         <v>3.3</v>
       </c>
       <c r="H140" s="44" t="n"/>
-      <c r="I140" s="45" t="n"/>
+      <c r="I140" s="44" t="n">
+        <v>321</v>
+      </c>
       <c r="J140" s="44" t="n">
-        <v>321</v>
+        <v>3.3</v>
       </c>
       <c r="K140" s="44" t="n">
-        <v>3.3</v>
+        <v>11608</v>
       </c>
       <c r="L140" s="44" t="n">
-        <v>11608</v>
+        <v>4854</v>
       </c>
       <c r="M140" s="44" t="n">
-        <v>4854</v>
-      </c>
-      <c r="N140" s="44" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -8250,18 +7898,17 @@
         <v>3.4</v>
       </c>
       <c r="H141" s="38" t="n"/>
-      <c r="I141" s="39" t="n"/>
+      <c r="I141" s="38" t="n">
+        <v>405</v>
+      </c>
       <c r="J141" s="38" t="n">
-        <v>405</v>
+        <v>4</v>
       </c>
       <c r="K141" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="L141" s="38" t="n">
         <v>6355</v>
       </c>
-      <c r="M141" s="38" t="n"/>
-      <c r="N141" s="38" t="n">
+      <c r="L141" s="38" t="n"/>
+      <c r="M141" s="38" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -8302,20 +7949,17 @@
       <c r="H142" s="44" t="n">
         <v>2890</v>
       </c>
-      <c r="I142" s="45" t="n">
-        <v>10693</v>
+      <c r="I142" s="44" t="n">
+        <v>267</v>
       </c>
       <c r="J142" s="44" t="n">
-        <v>267</v>
+        <v>6.1</v>
       </c>
       <c r="K142" s="44" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="L142" s="44" t="n">
         <v>4261</v>
       </c>
-      <c r="M142" s="44" t="n"/>
-      <c r="N142" s="44" t="n">
+      <c r="L142" s="44" t="n"/>
+      <c r="M142" s="44" t="n">
         <v>99</v>
       </c>
     </row>
@@ -8352,20 +7996,17 @@
       <c r="H143" s="38" t="n">
         <v>3600</v>
       </c>
-      <c r="I143" s="39" t="n">
-        <v>13680</v>
+      <c r="I143" s="38" t="n">
+        <v>259</v>
       </c>
       <c r="J143" s="38" t="n">
-        <v>259</v>
+        <v>5</v>
       </c>
       <c r="K143" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L143" s="38" t="n">
         <v>8018</v>
       </c>
-      <c r="M143" s="38" t="n"/>
-      <c r="N143" s="38" t="n">
+      <c r="L143" s="38" t="n"/>
+      <c r="M143" s="38" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -8406,22 +8047,19 @@
       <c r="H144" s="44" t="n">
         <v>3168</v>
       </c>
-      <c r="I144" s="45" t="n">
-        <v>10454</v>
+      <c r="I144" s="44" t="n">
+        <v>309</v>
       </c>
       <c r="J144" s="44" t="n">
-        <v>309</v>
+        <v>4</v>
       </c>
       <c r="K144" s="44" t="n">
-        <v>4</v>
+        <v>12429</v>
       </c>
       <c r="L144" s="44" t="n">
-        <v>12429</v>
+        <v>3740</v>
       </c>
       <c r="M144" s="44" t="n">
-        <v>3740</v>
-      </c>
-      <c r="N144" s="44" t="n">
         <v>99.5</v>
       </c>
     </row>
@@ -8462,22 +8100,19 @@
       <c r="H145" s="38" t="n">
         <v>3176</v>
       </c>
-      <c r="I145" s="39" t="n">
-        <v>10163</v>
+      <c r="I145" s="38" t="n">
+        <v>456</v>
       </c>
       <c r="J145" s="38" t="n">
-        <v>456</v>
+        <v>3</v>
       </c>
       <c r="K145" s="38" t="n">
-        <v>3</v>
+        <v>6428</v>
       </c>
       <c r="L145" s="38" t="n">
-        <v>6428</v>
+        <v>3717</v>
       </c>
       <c r="M145" s="38" t="n">
-        <v>3717</v>
-      </c>
-      <c r="N145" s="38" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -8518,22 +8153,19 @@
       <c r="H146" s="44" t="n">
         <v>3505</v>
       </c>
-      <c r="I146" s="45" t="n">
-        <v>12968</v>
+      <c r="I146" s="44" t="n">
+        <v>328</v>
       </c>
       <c r="J146" s="44" t="n">
-        <v>328</v>
+        <v>4.7</v>
       </c>
       <c r="K146" s="44" t="n">
-        <v>4.7</v>
+        <v>5707</v>
       </c>
       <c r="L146" s="44" t="n">
-        <v>5707</v>
+        <v>2468</v>
       </c>
       <c r="M146" s="44" t="n">
-        <v>2468</v>
-      </c>
-      <c r="N146" s="44" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -8575,21 +8207,18 @@
         <v>2311</v>
       </c>
       <c r="I147" s="38" t="n">
-        <v>6008</v>
+        <v>160</v>
       </c>
       <c r="J147" s="38" t="n">
-        <v>160</v>
+        <v>5.6</v>
       </c>
       <c r="K147" s="38" t="n">
-        <v>5.6</v>
+        <v>4773</v>
       </c>
       <c r="L147" s="38" t="n">
-        <v>4773</v>
+        <v>2292</v>
       </c>
       <c r="M147" s="38" t="n">
-        <v>2292</v>
-      </c>
-      <c r="N147" s="38" t="n">
         <v>98.40000000000001</v>
       </c>
     </row>
@@ -8631,21 +8260,18 @@
         <v>3503</v>
       </c>
       <c r="I148" s="44" t="n">
-        <v>12961</v>
+        <v>320</v>
       </c>
       <c r="J148" s="44" t="n">
-        <v>320</v>
+        <v>4.5</v>
       </c>
       <c r="K148" s="44" t="n">
-        <v>4.5</v>
+        <v>7921</v>
       </c>
       <c r="L148" s="44" t="n">
-        <v>7921</v>
+        <v>4706</v>
       </c>
       <c r="M148" s="44" t="n">
-        <v>4706</v>
-      </c>
-      <c r="N148" s="44" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -8684,22 +8310,19 @@
       <c r="H149" s="38" t="n">
         <v>4333</v>
       </c>
-      <c r="I149" s="39" t="n">
-        <v>18631</v>
+      <c r="I149" s="38" t="n">
+        <v>449</v>
       </c>
       <c r="J149" s="38" t="n">
-        <v>449</v>
+        <v>5</v>
       </c>
       <c r="K149" s="38" t="n">
-        <v>5</v>
+        <v>12133</v>
       </c>
       <c r="L149" s="38" t="n">
-        <v>12133</v>
+        <v>8827</v>
       </c>
       <c r="M149" s="38" t="n">
-        <v>8827</v>
-      </c>
-      <c r="N149" s="38" t="n">
         <v>97.7</v>
       </c>
     </row>
@@ -8740,22 +8363,19 @@
       <c r="H150" s="44" t="n">
         <v>3666</v>
       </c>
-      <c r="I150" s="45" t="n">
-        <v>14664</v>
+      <c r="I150" s="44" t="n">
+        <v>591</v>
       </c>
       <c r="J150" s="44" t="n">
-        <v>591</v>
+        <v>8.5</v>
       </c>
       <c r="K150" s="44" t="n">
-        <v>8.5</v>
+        <v>9860</v>
       </c>
       <c r="L150" s="44" t="n">
-        <v>9860</v>
+        <v>3925</v>
       </c>
       <c r="M150" s="44" t="n">
-        <v>3925</v>
-      </c>
-      <c r="N150" s="44" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -8792,14 +8412,13 @@
       </c>
       <c r="G151" s="49" t="n"/>
       <c r="H151" s="38" t="n"/>
-      <c r="I151" s="39" t="n"/>
+      <c r="I151" s="38" t="n"/>
       <c r="J151" s="38" t="n"/>
-      <c r="K151" s="38" t="n"/>
-      <c r="L151" s="38" t="n">
+      <c r="K151" s="38" t="n">
         <v>10088</v>
       </c>
-      <c r="M151" s="38" t="n"/>
-      <c r="N151" s="38" t="n">
+      <c r="L151" s="38" t="n"/>
+      <c r="M151" s="38" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -8840,22 +8459,19 @@
       <c r="H152" s="44" t="n">
         <v>4085</v>
       </c>
-      <c r="I152" s="45" t="n">
-        <v>17157</v>
+      <c r="I152" s="44" t="n">
+        <v>435</v>
       </c>
       <c r="J152" s="44" t="n">
-        <v>435</v>
+        <v>5</v>
       </c>
       <c r="K152" s="44" t="n">
-        <v>5</v>
+        <v>7200</v>
       </c>
       <c r="L152" s="44" t="n">
-        <v>7200</v>
+        <v>4837</v>
       </c>
       <c r="M152" s="44" t="n">
-        <v>4837</v>
-      </c>
-      <c r="N152" s="44" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -8896,22 +8512,19 @@
       <c r="H153" s="38" t="n">
         <v>3500</v>
       </c>
-      <c r="I153" s="39" t="n">
-        <v>14000</v>
+      <c r="I153" s="38" t="n">
+        <v>289</v>
       </c>
       <c r="J153" s="38" t="n">
-        <v>289</v>
+        <v>4.7</v>
       </c>
       <c r="K153" s="38" t="n">
-        <v>4.7</v>
+        <v>11610</v>
       </c>
       <c r="L153" s="38" t="n">
-        <v>11610</v>
+        <v>5537</v>
       </c>
       <c r="M153" s="38" t="n">
-        <v>5537</v>
-      </c>
-      <c r="N153" s="38" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -8952,22 +8565,19 @@
       <c r="H154" s="44" t="n">
         <v>3005</v>
       </c>
-      <c r="I154" s="45" t="n">
-        <v>9015</v>
+      <c r="I154" s="44" t="n">
+        <v>425</v>
       </c>
       <c r="J154" s="44" t="n">
-        <v>425</v>
+        <v>4</v>
       </c>
       <c r="K154" s="44" t="n">
-        <v>4</v>
+        <v>10387</v>
       </c>
       <c r="L154" s="44" t="n">
-        <v>10387</v>
+        <v>5178</v>
       </c>
       <c r="M154" s="44" t="n">
-        <v>5178</v>
-      </c>
-      <c r="N154" s="44" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -9007,21 +8617,18 @@
         <v>3569</v>
       </c>
       <c r="I155" s="38" t="n">
-        <v>13562</v>
+        <v>597</v>
       </c>
       <c r="J155" s="38" t="n">
-        <v>597</v>
+        <v>6</v>
       </c>
       <c r="K155" s="38" t="n">
-        <v>6</v>
+        <v>9994</v>
       </c>
       <c r="L155" s="38" t="n">
-        <v>9994</v>
+        <v>4396</v>
       </c>
       <c r="M155" s="38" t="n">
-        <v>4396</v>
-      </c>
-      <c r="N155" s="38" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -9062,20 +8669,17 @@
       <c r="H156" s="44" t="n">
         <v>3320</v>
       </c>
-      <c r="I156" s="45" t="n">
-        <v>13612</v>
+      <c r="I156" s="44" t="n">
+        <v>288</v>
       </c>
       <c r="J156" s="44" t="n">
-        <v>288</v>
+        <v>3.5</v>
       </c>
       <c r="K156" s="44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L156" s="44" t="n">
         <v>12079</v>
       </c>
-      <c r="M156" s="44" t="n"/>
-      <c r="N156" s="44" t="n">
+      <c r="L156" s="44" t="n"/>
+      <c r="M156" s="44" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -9114,22 +8718,19 @@
       <c r="H157" s="38" t="n">
         <v>3480</v>
       </c>
-      <c r="I157" s="39" t="n">
-        <v>13572</v>
+      <c r="I157" s="38" t="n">
+        <v>395</v>
       </c>
       <c r="J157" s="38" t="n">
-        <v>395</v>
+        <v>9</v>
       </c>
       <c r="K157" s="38" t="n">
-        <v>9</v>
+        <v>8531</v>
       </c>
       <c r="L157" s="38" t="n">
-        <v>8531</v>
+        <v>5548</v>
       </c>
       <c r="M157" s="38" t="n">
-        <v>5548</v>
-      </c>
-      <c r="N157" s="38" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -9168,22 +8769,19 @@
       <c r="H158" s="44" t="n">
         <v>3059</v>
       </c>
-      <c r="I158" s="45" t="n">
-        <v>9788</v>
+      <c r="I158" s="44" t="n">
+        <v>291</v>
       </c>
       <c r="J158" s="44" t="n">
-        <v>291</v>
+        <v>5</v>
       </c>
       <c r="K158" s="44" t="n">
-        <v>5</v>
+        <v>8086</v>
       </c>
       <c r="L158" s="44" t="n">
-        <v>8086</v>
+        <v>3822</v>
       </c>
       <c r="M158" s="44" t="n">
-        <v>3822</v>
-      </c>
-      <c r="N158" s="44" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -9224,22 +8822,19 @@
       <c r="H159" s="38" t="n">
         <v>3007</v>
       </c>
-      <c r="I159" s="39" t="n">
-        <v>9622</v>
+      <c r="I159" s="38" t="n">
+        <v>408</v>
       </c>
       <c r="J159" s="38" t="n">
-        <v>408</v>
+        <v>5.4</v>
       </c>
       <c r="K159" s="38" t="n">
-        <v>5.4</v>
+        <v>14230</v>
       </c>
       <c r="L159" s="38" t="n">
-        <v>14230</v>
+        <v>6686</v>
       </c>
       <c r="M159" s="38" t="n">
-        <v>6686</v>
-      </c>
-      <c r="N159" s="38" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -9280,20 +8875,17 @@
       <c r="H160" s="44" t="n">
         <v>2305</v>
       </c>
-      <c r="I160" s="45" t="n">
-        <v>5762</v>
-      </c>
-      <c r="J160" s="44" t="n"/>
+      <c r="I160" s="44" t="n"/>
+      <c r="J160" s="44" t="n">
+        <v>6.5</v>
+      </c>
       <c r="K160" s="44" t="n">
-        <v>6.5</v>
+        <v>15647</v>
       </c>
       <c r="L160" s="44" t="n">
-        <v>15647</v>
+        <v>-34</v>
       </c>
       <c r="M160" s="44" t="n">
-        <v>-34</v>
-      </c>
-      <c r="N160" s="44" t="n">
         <v>100.7</v>
       </c>
     </row>
@@ -9334,22 +8926,19 @@
       <c r="H161" s="38" t="n">
         <v>5005</v>
       </c>
-      <c r="I161" s="39" t="n">
-        <v>25525</v>
+      <c r="I161" s="38" t="n">
+        <v>197</v>
       </c>
       <c r="J161" s="38" t="n">
-        <v>197</v>
+        <v>5</v>
       </c>
       <c r="K161" s="38" t="n">
-        <v>5</v>
+        <v>9048</v>
       </c>
       <c r="L161" s="38" t="n">
-        <v>9048</v>
+        <v>2844</v>
       </c>
       <c r="M161" s="38" t="n">
-        <v>2844</v>
-      </c>
-      <c r="N161" s="38" t="n">
         <v>99.5</v>
       </c>
     </row>
@@ -9388,14 +8977,13 @@
       <c r="H162" s="44" t="n"/>
       <c r="I162" s="44" t="n"/>
       <c r="J162" s="44" t="n"/>
-      <c r="K162" s="44" t="n"/>
+      <c r="K162" s="44" t="n">
+        <v>11642</v>
+      </c>
       <c r="L162" s="44" t="n">
-        <v>11642</v>
+        <v>1329</v>
       </c>
       <c r="M162" s="44" t="n">
-        <v>1329</v>
-      </c>
-      <c r="N162" s="44" t="n">
         <v>99.8</v>
       </c>
     </row>
@@ -9432,14 +9020,13 @@
       </c>
       <c r="G163" s="49" t="n"/>
       <c r="H163" s="38" t="n"/>
-      <c r="I163" s="39" t="n"/>
+      <c r="I163" s="38" t="n"/>
       <c r="J163" s="38" t="n"/>
-      <c r="K163" s="38" t="n"/>
-      <c r="L163" s="38" t="n">
+      <c r="K163" s="38" t="n">
         <v>10481</v>
       </c>
-      <c r="M163" s="38" t="n"/>
-      <c r="N163" s="38" t="n">
+      <c r="L163" s="38" t="n"/>
+      <c r="M163" s="38" t="n">
         <v>99.90000000000001</v>
       </c>
     </row>
@@ -9481,21 +9068,18 @@
         <v>4000</v>
       </c>
       <c r="I164" s="44" t="n">
-        <v>16000</v>
+        <v>844</v>
       </c>
       <c r="J164" s="44" t="n">
-        <v>844</v>
+        <v>6</v>
       </c>
       <c r="K164" s="44" t="n">
-        <v>6</v>
+        <v>12223</v>
       </c>
       <c r="L164" s="44" t="n">
-        <v>12223</v>
+        <v>7242</v>
       </c>
       <c r="M164" s="44" t="n">
-        <v>7242</v>
-      </c>
-      <c r="N164" s="44" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -9536,22 +9120,19 @@
       <c r="H165" s="38" t="n">
         <v>4500</v>
       </c>
-      <c r="I165" s="39" t="n">
-        <v>19350</v>
+      <c r="I165" s="38" t="n">
+        <v>328</v>
       </c>
       <c r="J165" s="38" t="n">
-        <v>328</v>
+        <v>4.5</v>
       </c>
       <c r="K165" s="38" t="n">
-        <v>4.5</v>
+        <v>7448</v>
       </c>
       <c r="L165" s="38" t="n">
-        <v>7448</v>
+        <v>5417</v>
       </c>
       <c r="M165" s="38" t="n">
-        <v>5417</v>
-      </c>
-      <c r="N165" s="38" t="n">
         <v>97.5</v>
       </c>
     </row>
@@ -9591,21 +9172,18 @@
         <v>3246</v>
       </c>
       <c r="I166" s="44" t="n">
-        <v>11685</v>
+        <v>417</v>
       </c>
       <c r="J166" s="44" t="n">
-        <v>417</v>
+        <v>5.1</v>
       </c>
       <c r="K166" s="44" t="n">
-        <v>5.1</v>
+        <v>14811</v>
       </c>
       <c r="L166" s="44" t="n">
-        <v>14811</v>
+        <v>7968</v>
       </c>
       <c r="M166" s="44" t="n">
-        <v>7968</v>
-      </c>
-      <c r="N166" s="44" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -9644,22 +9222,19 @@
       <c r="H167" s="38" t="n">
         <v>3319</v>
       </c>
-      <c r="I167" s="39" t="n">
-        <v>10288</v>
+      <c r="I167" s="38" t="n">
+        <v>395</v>
       </c>
       <c r="J167" s="38" t="n">
-        <v>395</v>
+        <v>5</v>
       </c>
       <c r="K167" s="38" t="n">
-        <v>5</v>
+        <v>9778</v>
       </c>
       <c r="L167" s="38" t="n">
-        <v>9778</v>
+        <v>4870</v>
       </c>
       <c r="M167" s="38" t="n">
-        <v>4870</v>
-      </c>
-      <c r="N167" s="38" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -9699,21 +9274,18 @@
         <v>4053</v>
       </c>
       <c r="I168" s="44" t="n">
-        <v>16212</v>
+        <v>394</v>
       </c>
       <c r="J168" s="44" t="n">
-        <v>394</v>
+        <v>4</v>
       </c>
       <c r="K168" s="44" t="n">
-        <v>4</v>
+        <v>15698</v>
       </c>
       <c r="L168" s="44" t="n">
-        <v>15698</v>
+        <v>6774</v>
       </c>
       <c r="M168" s="44" t="n">
-        <v>6774</v>
-      </c>
-      <c r="N168" s="44" t="n">
         <v>99</v>
       </c>
     </row>
@@ -9753,21 +9325,18 @@
         <v>4151</v>
       </c>
       <c r="I169" s="38" t="n">
-        <v>17434</v>
+        <v>573</v>
       </c>
       <c r="J169" s="38" t="n">
-        <v>573</v>
+        <v>5.4</v>
       </c>
       <c r="K169" s="38" t="n">
-        <v>5.4</v>
+        <v>11399</v>
       </c>
       <c r="L169" s="38" t="n">
-        <v>11399</v>
+        <v>7882</v>
       </c>
       <c r="M169" s="38" t="n">
-        <v>7882</v>
-      </c>
-      <c r="N169" s="38" t="n">
         <v>97.8</v>
       </c>
     </row>
@@ -9806,22 +9375,19 @@
       <c r="H170" s="44" t="n">
         <v>2674</v>
       </c>
-      <c r="I170" s="45" t="n">
-        <v>7754</v>
+      <c r="I170" s="44" t="n">
+        <v>359</v>
       </c>
       <c r="J170" s="44" t="n">
-        <v>359</v>
-      </c>
-      <c r="K170" s="44" t="n">
         <v>3.4</v>
       </c>
-      <c r="L170" s="45" t="n">
+      <c r="K170" s="45" t="n">
         <v>14080</v>
       </c>
-      <c r="M170" s="46" t="n">
+      <c r="L170" s="46" t="n">
         <v>5057</v>
       </c>
-      <c r="N170" s="47" t="n">
+      <c r="M170" s="47" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -9861,21 +9427,18 @@
         <v>2972</v>
       </c>
       <c r="I171" s="38" t="n">
-        <v>9510</v>
+        <v>325</v>
       </c>
       <c r="J171" s="38" t="n">
-        <v>325</v>
+        <v>4</v>
       </c>
       <c r="K171" s="38" t="n">
-        <v>4</v>
+        <v>14093</v>
       </c>
       <c r="L171" s="38" t="n">
-        <v>14093</v>
+        <v>6580</v>
       </c>
       <c r="M171" s="38" t="n">
-        <v>6580</v>
-      </c>
-      <c r="N171" s="38" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -9914,22 +9477,19 @@
       <c r="H172" s="44" t="n">
         <v>4083</v>
       </c>
-      <c r="I172" s="45" t="n">
-        <v>15923</v>
+      <c r="I172" s="44" t="n">
+        <v>470</v>
       </c>
       <c r="J172" s="44" t="n">
-        <v>470</v>
+        <v>5</v>
       </c>
       <c r="K172" s="44" t="n">
-        <v>5</v>
+        <v>9904</v>
       </c>
       <c r="L172" s="44" t="n">
-        <v>9904</v>
+        <v>6167</v>
       </c>
       <c r="M172" s="44" t="n">
-        <v>6167</v>
-      </c>
-      <c r="N172" s="44" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -9966,20 +9526,19 @@
       </c>
       <c r="G173" s="49" t="n"/>
       <c r="H173" s="38" t="n"/>
-      <c r="I173" s="39" t="n"/>
+      <c r="I173" s="38" t="n">
+        <v>478</v>
+      </c>
       <c r="J173" s="38" t="n">
-        <v>478</v>
+        <v>2.5</v>
       </c>
       <c r="K173" s="38" t="n">
-        <v>2.5</v>
+        <v>5094</v>
       </c>
       <c r="L173" s="38" t="n">
-        <v>5094</v>
+        <v>2756</v>
       </c>
       <c r="M173" s="38" t="n">
-        <v>2756</v>
-      </c>
-      <c r="N173" s="38" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -10019,21 +9578,18 @@
         <v>2803</v>
       </c>
       <c r="I174" s="44" t="n">
-        <v>8689</v>
+        <v>384</v>
       </c>
       <c r="J174" s="44" t="n">
-        <v>384</v>
+        <v>5.3</v>
       </c>
       <c r="K174" s="44" t="n">
-        <v>5.3</v>
+        <v>10304</v>
       </c>
       <c r="L174" s="44" t="n">
-        <v>10304</v>
+        <v>5488</v>
       </c>
       <c r="M174" s="44" t="n">
-        <v>5488</v>
-      </c>
-      <c r="N174" s="44" t="n">
         <v>98.40000000000001</v>
       </c>
     </row>
@@ -10070,20 +9626,19 @@
       </c>
       <c r="G175" s="49" t="n"/>
       <c r="H175" s="38" t="n"/>
-      <c r="I175" s="39" t="n"/>
+      <c r="I175" s="38" t="n">
+        <v>295</v>
+      </c>
       <c r="J175" s="38" t="n">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="K175" s="38" t="n">
-        <v>6</v>
+        <v>4509</v>
       </c>
       <c r="L175" s="38" t="n">
-        <v>4509</v>
+        <v>2654</v>
       </c>
       <c r="M175" s="38" t="n">
-        <v>2654</v>
-      </c>
-      <c r="N175" s="38" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -10122,22 +9677,19 @@
       <c r="H176" s="44" t="n">
         <v>4000</v>
       </c>
-      <c r="I176" s="45" t="n">
-        <v>16000</v>
+      <c r="I176" s="44" t="n">
+        <v>379</v>
       </c>
       <c r="J176" s="44" t="n">
-        <v>379</v>
+        <v>7.1</v>
       </c>
       <c r="K176" s="44" t="n">
-        <v>7.1</v>
+        <v>13601</v>
       </c>
       <c r="L176" s="44" t="n">
-        <v>13601</v>
+        <v>7702</v>
       </c>
       <c r="M176" s="44" t="n">
-        <v>7702</v>
-      </c>
-      <c r="N176" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -10176,20 +9728,17 @@
       <c r="H177" s="38" t="n">
         <v>3339</v>
       </c>
-      <c r="I177" s="39" t="n">
-        <v>10684</v>
-      </c>
-      <c r="J177" s="38" t="n"/>
+      <c r="I177" s="38" t="n"/>
+      <c r="J177" s="38" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K177" s="38" t="n">
-        <v>0.4</v>
+        <v>8620</v>
       </c>
       <c r="L177" s="38" t="n">
-        <v>8620</v>
+        <v>5467</v>
       </c>
       <c r="M177" s="38" t="n">
-        <v>5467</v>
-      </c>
-      <c r="N177" s="38" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -10228,22 +9777,19 @@
       <c r="H178" s="44" t="n">
         <v>3456</v>
       </c>
-      <c r="I178" s="45" t="n">
-        <v>12096</v>
+      <c r="I178" s="44" t="n">
+        <v>354</v>
       </c>
       <c r="J178" s="44" t="n">
-        <v>354</v>
+        <v>3.7</v>
       </c>
       <c r="K178" s="44" t="n">
-        <v>3.7</v>
+        <v>12703</v>
       </c>
       <c r="L178" s="44" t="n">
-        <v>12703</v>
+        <v>5902</v>
       </c>
       <c r="M178" s="44" t="n">
-        <v>5902</v>
-      </c>
-      <c r="N178" s="44" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -10283,21 +9829,18 @@
         <v>2998</v>
       </c>
       <c r="I179" s="38" t="n">
-        <v>9593</v>
+        <v>654</v>
       </c>
       <c r="J179" s="38" t="n">
-        <v>654</v>
+        <v>2.6</v>
       </c>
       <c r="K179" s="38" t="n">
-        <v>2.6</v>
+        <v>14004</v>
       </c>
       <c r="L179" s="38" t="n">
-        <v>14004</v>
+        <v>4302</v>
       </c>
       <c r="M179" s="38" t="n">
-        <v>4302</v>
-      </c>
-      <c r="N179" s="38" t="n">
         <v>99.40000000000001</v>
       </c>
     </row>
@@ -10336,22 +9879,19 @@
       <c r="H180" s="44" t="n">
         <v>4832</v>
       </c>
-      <c r="I180" s="45" t="n">
-        <v>25126</v>
+      <c r="I180" s="44" t="n">
+        <v>380</v>
       </c>
       <c r="J180" s="44" t="n">
-        <v>380</v>
+        <v>5</v>
       </c>
       <c r="K180" s="44" t="n">
-        <v>5</v>
+        <v>10956</v>
       </c>
       <c r="L180" s="44" t="n">
-        <v>10956</v>
+        <v>4146</v>
       </c>
       <c r="M180" s="44" t="n">
-        <v>4146</v>
-      </c>
-      <c r="N180" s="44" t="n">
         <v>99.90000000000001</v>
       </c>
     </row>
@@ -10390,22 +9930,19 @@
       <c r="H181" s="38" t="n">
         <v>3600</v>
       </c>
-      <c r="I181" s="39" t="n">
-        <v>11880</v>
+      <c r="I181" s="38" t="n">
+        <v>397</v>
       </c>
       <c r="J181" s="38" t="n">
-        <v>397</v>
+        <v>5</v>
       </c>
       <c r="K181" s="38" t="n">
-        <v>5</v>
+        <v>6047</v>
       </c>
       <c r="L181" s="38" t="n">
-        <v>6047</v>
+        <v>2390</v>
       </c>
       <c r="M181" s="38" t="n">
-        <v>2390</v>
-      </c>
-      <c r="N181" s="38" t="n">
         <v>99.40000000000001</v>
       </c>
     </row>
@@ -10444,20 +9981,17 @@
       <c r="H182" s="44" t="n">
         <v>2900</v>
       </c>
-      <c r="I182" s="45" t="n">
-        <v>9280</v>
+      <c r="I182" s="44" t="n">
+        <v>274</v>
       </c>
       <c r="J182" s="44" t="n">
-        <v>274</v>
+        <v>3.3</v>
       </c>
       <c r="K182" s="44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L182" s="44" t="n">
         <v>7301</v>
       </c>
-      <c r="M182" s="44" t="n"/>
-      <c r="N182" s="44" t="n">
+      <c r="L182" s="44" t="n"/>
+      <c r="M182" s="44" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -10494,20 +10028,19 @@
       </c>
       <c r="G183" s="49" t="n"/>
       <c r="H183" s="38" t="n"/>
-      <c r="I183" s="38" t="n"/>
+      <c r="I183" s="38" t="n">
+        <v>353</v>
+      </c>
       <c r="J183" s="38" t="n">
-        <v>353</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K183" s="38" t="n">
-        <v>8.699999999999999</v>
+        <v>14031</v>
       </c>
       <c r="L183" s="38" t="n">
-        <v>14031</v>
+        <v>6498</v>
       </c>
       <c r="M183" s="38" t="n">
-        <v>6498</v>
-      </c>
-      <c r="N183" s="38" t="n">
         <v>99</v>
       </c>
     </row>
@@ -10544,16 +10077,15 @@
       </c>
       <c r="G184" s="48" t="n"/>
       <c r="H184" s="44" t="n"/>
-      <c r="I184" s="45" t="n"/>
+      <c r="I184" s="44" t="n"/>
       <c r="J184" s="44" t="n"/>
-      <c r="K184" s="44" t="n"/>
+      <c r="K184" s="44" t="n">
+        <v>8137</v>
+      </c>
       <c r="L184" s="44" t="n">
-        <v>8137</v>
+        <v>4074</v>
       </c>
       <c r="M184" s="44" t="n">
-        <v>4074</v>
-      </c>
-      <c r="N184" s="44" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -10592,22 +10124,19 @@
       <c r="H185" s="38" t="n">
         <v>4012</v>
       </c>
-      <c r="I185" s="39" t="n">
-        <v>16449</v>
+      <c r="I185" s="38" t="n">
+        <v>460</v>
       </c>
       <c r="J185" s="38" t="n">
-        <v>460</v>
-      </c>
-      <c r="K185" s="38" t="n">
         <v>6.6</v>
       </c>
-      <c r="L185" s="39" t="n">
+      <c r="K185" s="39" t="n">
         <v>7887</v>
       </c>
-      <c r="M185" s="40" t="n">
+      <c r="L185" s="40" t="n">
         <v>4840</v>
       </c>
-      <c r="N185" s="41" t="n">
+      <c r="M185" s="41" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -10646,22 +10175,19 @@
       <c r="H186" s="44" t="n">
         <v>3467</v>
       </c>
-      <c r="I186" s="45" t="n">
-        <v>12134</v>
+      <c r="I186" s="44" t="n">
+        <v>561</v>
       </c>
       <c r="J186" s="44" t="n">
-        <v>561</v>
-      </c>
-      <c r="K186" s="44" t="n">
         <v>4.5</v>
       </c>
-      <c r="L186" s="45" t="n">
+      <c r="K186" s="45" t="n">
         <v>10862</v>
       </c>
-      <c r="M186" s="46" t="n">
+      <c r="L186" s="46" t="n">
         <v>4070</v>
       </c>
-      <c r="N186" s="47" t="n">
+      <c r="M186" s="47" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -10698,20 +10224,19 @@
       </c>
       <c r="G187" s="38" t="n"/>
       <c r="H187" s="38" t="n"/>
-      <c r="I187" s="38" t="n"/>
+      <c r="I187" s="38" t="n">
+        <v>329</v>
+      </c>
       <c r="J187" s="38" t="n">
-        <v>329</v>
+        <v>3.3</v>
       </c>
       <c r="K187" s="38" t="n">
-        <v>3.3</v>
+        <v>8775</v>
       </c>
       <c r="L187" s="38" t="n">
-        <v>8775</v>
+        <v>5557</v>
       </c>
       <c r="M187" s="38" t="n">
-        <v>5557</v>
-      </c>
-      <c r="N187" s="38" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -10744,18 +10269,17 @@
       <c r="F188" s="43" t="n"/>
       <c r="G188" s="48" t="n"/>
       <c r="H188" s="44" t="n"/>
-      <c r="I188" s="44" t="n"/>
+      <c r="I188" s="44" t="n">
+        <v>336</v>
+      </c>
       <c r="J188" s="44" t="n">
-        <v>336</v>
+        <v>0.3</v>
       </c>
       <c r="K188" s="44" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L188" s="44" t="n">
         <v>5898</v>
       </c>
-      <c r="M188" s="44" t="n"/>
-      <c r="N188" s="44" t="n">
+      <c r="L188" s="44" t="n"/>
+      <c r="M188" s="44" t="n">
         <v>97.7</v>
       </c>
     </row>
@@ -10792,20 +10316,19 @@
       </c>
       <c r="G189" s="49" t="n"/>
       <c r="H189" s="38" t="n"/>
-      <c r="I189" s="39" t="n"/>
+      <c r="I189" s="38" t="n">
+        <v>320</v>
+      </c>
       <c r="J189" s="38" t="n">
-        <v>320</v>
+        <v>4</v>
       </c>
       <c r="K189" s="38" t="n">
-        <v>4</v>
+        <v>5402</v>
       </c>
       <c r="L189" s="38" t="n">
-        <v>5402</v>
+        <v>1717</v>
       </c>
       <c r="M189" s="38" t="n">
-        <v>1717</v>
-      </c>
-      <c r="N189" s="38" t="n">
         <v>99.59999999999999</v>
       </c>
     </row>
@@ -10844,18 +10367,15 @@
       <c r="H190" s="44" t="n">
         <v>2096</v>
       </c>
-      <c r="I190" s="45" t="n">
-        <v>5449</v>
-      </c>
+      <c r="I190" s="44" t="n"/>
       <c r="J190" s="44" t="n"/>
-      <c r="K190" s="44" t="n"/>
+      <c r="K190" s="44" t="n">
+        <v>8932</v>
+      </c>
       <c r="L190" s="44" t="n">
-        <v>8932</v>
+        <v>2401</v>
       </c>
       <c r="M190" s="44" t="n">
-        <v>2401</v>
-      </c>
-      <c r="N190" s="44" t="n">
         <v>99.2</v>
       </c>
     </row>
@@ -10892,20 +10412,19 @@
       </c>
       <c r="G191" s="49" t="n"/>
       <c r="H191" s="38" t="n"/>
-      <c r="I191" s="39" t="n"/>
+      <c r="I191" s="38" t="n">
+        <v>445</v>
+      </c>
       <c r="J191" s="38" t="n">
-        <v>445</v>
+        <v>5.8</v>
       </c>
       <c r="K191" s="38" t="n">
-        <v>5.8</v>
+        <v>10181</v>
       </c>
       <c r="L191" s="38" t="n">
-        <v>10181</v>
+        <v>7131</v>
       </c>
       <c r="M191" s="38" t="n">
-        <v>7131</v>
-      </c>
-      <c r="N191" s="38" t="n">
         <v>97.59999999999999</v>
       </c>
     </row>
@@ -10942,16 +10461,15 @@
       </c>
       <c r="G192" s="48" t="n"/>
       <c r="H192" s="44" t="n"/>
-      <c r="I192" s="45" t="n"/>
+      <c r="I192" s="44" t="n"/>
       <c r="J192" s="44" t="n"/>
-      <c r="K192" s="44" t="n"/>
+      <c r="K192" s="44" t="n">
+        <v>11696</v>
+      </c>
       <c r="L192" s="44" t="n">
-        <v>11696</v>
+        <v>4827</v>
       </c>
       <c r="M192" s="44" t="n">
-        <v>4827</v>
-      </c>
-      <c r="N192" s="44" t="n">
         <v>98.59999999999999</v>
       </c>
     </row>
@@ -10990,14 +10508,13 @@
       <c r="H193" s="38" t="n"/>
       <c r="I193" s="38" t="n"/>
       <c r="J193" s="38" t="n"/>
-      <c r="K193" s="38" t="n"/>
+      <c r="K193" s="38" t="n">
+        <v>7996</v>
+      </c>
       <c r="L193" s="38" t="n">
-        <v>7996</v>
+        <v>3774</v>
       </c>
       <c r="M193" s="38" t="n">
-        <v>3774</v>
-      </c>
-      <c r="N193" s="38" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -11034,16 +10551,15 @@
       </c>
       <c r="G194" s="48" t="n"/>
       <c r="H194" s="44" t="n"/>
-      <c r="I194" s="45" t="n"/>
+      <c r="I194" s="44" t="n"/>
       <c r="J194" s="44" t="n"/>
-      <c r="K194" s="44" t="n"/>
+      <c r="K194" s="44" t="n">
+        <v>7867</v>
+      </c>
       <c r="L194" s="44" t="n">
-        <v>7867</v>
+        <v>2999</v>
       </c>
       <c r="M194" s="44" t="n">
-        <v>2999</v>
-      </c>
-      <c r="N194" s="44" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -11082,22 +10598,19 @@
       <c r="H195" s="38" t="n">
         <v>2937</v>
       </c>
-      <c r="I195" s="39" t="n">
-        <v>8811</v>
+      <c r="I195" s="38" t="n">
+        <v>596</v>
       </c>
       <c r="J195" s="38" t="n">
-        <v>596</v>
+        <v>2</v>
       </c>
       <c r="K195" s="38" t="n">
-        <v>2</v>
+        <v>7755</v>
       </c>
       <c r="L195" s="38" t="n">
-        <v>7755</v>
+        <v>3816</v>
       </c>
       <c r="M195" s="38" t="n">
-        <v>3816</v>
-      </c>
-      <c r="N195" s="38" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -11136,22 +10649,19 @@
       <c r="H196" s="44" t="n">
         <v>3380</v>
       </c>
-      <c r="I196" s="45" t="n">
-        <v>11830</v>
+      <c r="I196" s="44" t="n">
+        <v>386</v>
       </c>
       <c r="J196" s="44" t="n">
-        <v>386</v>
+        <v>5</v>
       </c>
       <c r="K196" s="44" t="n">
-        <v>5</v>
+        <v>14273</v>
       </c>
       <c r="L196" s="44" t="n">
-        <v>14273</v>
+        <v>6721</v>
       </c>
       <c r="M196" s="44" t="n">
-        <v>6721</v>
-      </c>
-      <c r="N196" s="44" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -11189,7 +10699,6 @@
       <c r="K197" s="38" t="n"/>
       <c r="L197" s="38" t="n"/>
       <c r="M197" s="38" t="n"/>
-      <c r="N197" s="38" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="50" t="inlineStr">
@@ -11218,16 +10727,15 @@
         <v>2.53</v>
       </c>
       <c r="H198" s="52" t="n"/>
-      <c r="I198" s="53" t="n"/>
+      <c r="I198" s="52" t="n"/>
       <c r="J198" s="52" t="n"/>
-      <c r="K198" s="52" t="n"/>
+      <c r="K198" s="52" t="n">
+        <v>5996</v>
+      </c>
       <c r="L198" s="52" t="n">
-        <v>5996</v>
+        <v>4388</v>
       </c>
       <c r="M198" s="52" t="n">
-        <v>4388</v>
-      </c>
-      <c r="N198" s="52" t="n">
         <v>97.3</v>
       </c>
     </row>
@@ -11260,18 +10768,17 @@
       <c r="F199" s="37" t="n"/>
       <c r="G199" s="49" t="n"/>
       <c r="H199" s="38" t="n"/>
-      <c r="I199" s="39" t="n"/>
+      <c r="I199" s="38" t="n">
+        <v>296</v>
+      </c>
       <c r="J199" s="38" t="n">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="K199" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="L199" s="38" t="n">
         <v>8826</v>
       </c>
-      <c r="M199" s="38" t="n"/>
-      <c r="N199" s="38" t="n">
+      <c r="L199" s="38" t="n"/>
+      <c r="M199" s="38" t="n">
         <v>99</v>
       </c>
     </row>
@@ -11306,18 +10813,15 @@
       <c r="H200" s="44" t="n">
         <v>2236</v>
       </c>
-      <c r="I200" s="45" t="n">
-        <v>5590</v>
-      </c>
+      <c r="I200" s="44" t="n"/>
       <c r="J200" s="44" t="n"/>
-      <c r="K200" s="44" t="n"/>
+      <c r="K200" s="44" t="n">
+        <v>13267</v>
+      </c>
       <c r="L200" s="44" t="n">
-        <v>13267</v>
+        <v>3128</v>
       </c>
       <c r="M200" s="44" t="n">
-        <v>3128</v>
-      </c>
-      <c r="N200" s="44" t="n">
         <v>99.40000000000001</v>
       </c>
     </row>
@@ -11353,21 +10857,18 @@
         <v>3183</v>
       </c>
       <c r="I201" s="38" t="n">
-        <v>10822</v>
+        <v>594</v>
       </c>
       <c r="J201" s="38" t="n">
-        <v>594</v>
+        <v>4.2</v>
       </c>
       <c r="K201" s="38" t="n">
-        <v>4.2</v>
+        <v>9496</v>
       </c>
       <c r="L201" s="38" t="n">
-        <v>9496</v>
+        <v>3214</v>
       </c>
       <c r="M201" s="38" t="n">
-        <v>3214</v>
-      </c>
-      <c r="N201" s="38" t="n">
         <v>99.5</v>
       </c>
     </row>
@@ -11402,12 +10903,11 @@
       <c r="H202" s="44" t="n"/>
       <c r="I202" s="44" t="n"/>
       <c r="J202" s="44" t="n"/>
-      <c r="K202" s="44" t="n"/>
-      <c r="L202" s="44" t="n">
+      <c r="K202" s="44" t="n">
         <v>8102</v>
       </c>
-      <c r="M202" s="44" t="n"/>
-      <c r="N202" s="44" t="n">
+      <c r="L202" s="44" t="n"/>
+      <c r="M202" s="44" t="n">
         <v>99.2</v>
       </c>
     </row>
@@ -11440,16 +10940,15 @@
       <c r="F203" s="37" t="n"/>
       <c r="G203" s="49" t="n"/>
       <c r="H203" s="38" t="n"/>
-      <c r="I203" s="39" t="n"/>
+      <c r="I203" s="38" t="n"/>
       <c r="J203" s="38" t="n"/>
-      <c r="K203" s="38" t="n"/>
+      <c r="K203" s="38" t="n">
+        <v>5131</v>
+      </c>
       <c r="L203" s="38" t="n">
-        <v>5131</v>
+        <v>1545</v>
       </c>
       <c r="M203" s="38" t="n">
-        <v>1545</v>
-      </c>
-      <c r="N203" s="38" t="n">
         <v>98.90000000000001</v>
       </c>
     </row>
@@ -11480,16 +10979,15 @@
         <v>1.99</v>
       </c>
       <c r="H204" s="52" t="n"/>
-      <c r="I204" s="53" t="n"/>
+      <c r="I204" s="52" t="n"/>
       <c r="J204" s="52" t="n"/>
-      <c r="K204" s="52" t="n"/>
+      <c r="K204" s="52" t="n">
+        <v>11242</v>
+      </c>
       <c r="L204" s="52" t="n">
-        <v>11242</v>
+        <v>3294</v>
       </c>
       <c r="M204" s="52" t="n">
-        <v>3294</v>
-      </c>
-      <c r="N204" s="52" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -11522,14 +11020,13 @@
       <c r="F205" s="37" t="n"/>
       <c r="G205" s="49" t="n"/>
       <c r="H205" s="38" t="n"/>
-      <c r="I205" s="39" t="n"/>
+      <c r="I205" s="38" t="n"/>
       <c r="J205" s="38" t="n"/>
-      <c r="K205" s="38" t="n"/>
-      <c r="L205" s="38" t="n">
+      <c r="K205" s="38" t="n">
         <v>11560</v>
       </c>
-      <c r="M205" s="38" t="n"/>
-      <c r="N205" s="38" t="n">
+      <c r="L205" s="38" t="n"/>
+      <c r="M205" s="38" t="n">
         <v>99.5</v>
       </c>
     </row>
@@ -11562,16 +11059,15 @@
       <c r="F206" s="43" t="n"/>
       <c r="G206" s="44" t="n"/>
       <c r="H206" s="44" t="n"/>
-      <c r="I206" s="44" t="n"/>
+      <c r="I206" s="44" t="n">
+        <v>155</v>
+      </c>
       <c r="J206" s="44" t="n">
-        <v>155</v>
-      </c>
-      <c r="K206" s="44" t="n">
         <v>2.9</v>
       </c>
+      <c r="K206" s="44" t="n"/>
       <c r="L206" s="44" t="n"/>
       <c r="M206" s="44" t="n"/>
-      <c r="N206" s="44" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="36" t="inlineStr">
@@ -11604,22 +11100,19 @@
       <c r="H207" s="38" t="n">
         <v>3930</v>
       </c>
-      <c r="I207" s="39" t="n">
-        <v>15720</v>
+      <c r="I207" s="38" t="n">
+        <v>229</v>
       </c>
       <c r="J207" s="38" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="K207" s="38" t="n">
-        <v>5</v>
+        <v>7448</v>
       </c>
       <c r="L207" s="38" t="n">
-        <v>7448</v>
+        <v>3770</v>
       </c>
       <c r="M207" s="38" t="n">
-        <v>3770</v>
-      </c>
-      <c r="N207" s="38" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -11652,14 +11145,13 @@
       <c r="F208" s="43" t="n"/>
       <c r="G208" s="48" t="n"/>
       <c r="H208" s="44" t="n"/>
-      <c r="I208" s="45" t="n"/>
+      <c r="I208" s="44" t="n"/>
       <c r="J208" s="44" t="n"/>
-      <c r="K208" s="44" t="n"/>
-      <c r="L208" s="44" t="n">
+      <c r="K208" s="44" t="n">
         <v>4452</v>
       </c>
-      <c r="M208" s="44" t="n"/>
-      <c r="N208" s="44" t="n">
+      <c r="L208" s="44" t="n"/>
+      <c r="M208" s="44" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -11694,22 +11186,19 @@
       <c r="H209" s="38" t="n">
         <v>3912</v>
       </c>
-      <c r="I209" s="39" t="n">
-        <v>14083</v>
+      <c r="I209" s="38" t="n">
+        <v>598</v>
       </c>
       <c r="J209" s="38" t="n">
-        <v>598</v>
+        <v>5.1</v>
       </c>
       <c r="K209" s="38" t="n">
-        <v>5.1</v>
+        <v>12936</v>
       </c>
       <c r="L209" s="38" t="n">
-        <v>12936</v>
+        <v>6195</v>
       </c>
       <c r="M209" s="38" t="n">
-        <v>6195</v>
-      </c>
-      <c r="N209" s="38" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -11745,21 +11234,18 @@
         <v>2953</v>
       </c>
       <c r="I210" s="44" t="n">
-        <v>9154</v>
+        <v>403</v>
       </c>
       <c r="J210" s="44" t="n">
-        <v>403</v>
+        <v>4.5</v>
       </c>
       <c r="K210" s="44" t="n">
-        <v>4.5</v>
+        <v>8074</v>
       </c>
       <c r="L210" s="44" t="n">
-        <v>8074</v>
+        <v>3756</v>
       </c>
       <c r="M210" s="44" t="n">
-        <v>3756</v>
-      </c>
-      <c r="N210" s="44" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -11795,19 +11281,16 @@
         <v>2912</v>
       </c>
       <c r="I211" s="38" t="n">
-        <v>9318</v>
+        <v>398</v>
       </c>
       <c r="J211" s="38" t="n">
-        <v>398</v>
+        <v>4.5</v>
       </c>
       <c r="K211" s="38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L211" s="38" t="n">
         <v>6387</v>
       </c>
-      <c r="M211" s="38" t="n"/>
-      <c r="N211" s="38" t="n">
+      <c r="L211" s="38" t="n"/>
+      <c r="M211" s="38" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -11840,14 +11323,13 @@
       <c r="H212" s="52" t="n"/>
       <c r="I212" s="52" t="n"/>
       <c r="J212" s="52" t="n"/>
-      <c r="K212" s="52" t="n"/>
+      <c r="K212" s="52" t="n">
+        <v>6148</v>
+      </c>
       <c r="L212" s="52" t="n">
-        <v>6148</v>
+        <v>2903</v>
       </c>
       <c r="M212" s="52" t="n">
-        <v>2903</v>
-      </c>
-      <c r="N212" s="52" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -11880,14 +11362,13 @@
       <c r="H213" s="52" t="n"/>
       <c r="I213" s="52" t="n"/>
       <c r="J213" s="52" t="n"/>
-      <c r="K213" s="52" t="n"/>
-      <c r="L213" s="53" t="n">
+      <c r="K213" s="53" t="n">
         <v>7780</v>
       </c>
-      <c r="M213" s="56" t="n">
+      <c r="L213" s="56" t="n">
         <v>4303</v>
       </c>
-      <c r="N213" s="57" t="n">
+      <c r="M213" s="57" t="n">
         <v>98.3</v>
       </c>
     </row>
@@ -11922,14 +11403,13 @@
       <c r="H214" s="44" t="n"/>
       <c r="I214" s="44" t="n"/>
       <c r="J214" s="44" t="n"/>
-      <c r="K214" s="44" t="n"/>
-      <c r="L214" s="45" t="n">
+      <c r="K214" s="45" t="n">
         <v>11940</v>
       </c>
-      <c r="M214" s="46" t="n">
+      <c r="L214" s="46" t="n">
         <v>4534</v>
       </c>
-      <c r="N214" s="47" t="n">
+      <c r="M214" s="47" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -11964,14 +11444,13 @@
       <c r="H215" s="38" t="n"/>
       <c r="I215" s="38" t="n"/>
       <c r="J215" s="38" t="n"/>
-      <c r="K215" s="38" t="n"/>
-      <c r="L215" s="39" t="n">
+      <c r="K215" s="39" t="n">
         <v>7113</v>
       </c>
-      <c r="M215" s="40" t="n">
+      <c r="L215" s="40" t="n">
         <v>3743</v>
       </c>
-      <c r="N215" s="41" t="n">
+      <c r="M215" s="41" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -12006,14 +11485,13 @@
       <c r="H216" s="44" t="n"/>
       <c r="I216" s="44" t="n"/>
       <c r="J216" s="44" t="n"/>
-      <c r="K216" s="44" t="n"/>
-      <c r="L216" s="45" t="n">
+      <c r="K216" s="45" t="n">
         <v>7113</v>
       </c>
-      <c r="M216" s="46" t="n">
+      <c r="L216" s="46" t="n">
         <v>3743</v>
       </c>
-      <c r="N216" s="47" t="n">
+      <c r="M216" s="47" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -12046,14 +11524,13 @@
       <c r="H217" s="52" t="n"/>
       <c r="I217" s="52" t="n"/>
       <c r="J217" s="52" t="n"/>
-      <c r="K217" s="52" t="n"/>
-      <c r="L217" s="53" t="n">
+      <c r="K217" s="53" t="n">
         <v>8711</v>
       </c>
-      <c r="M217" s="56" t="n">
+      <c r="L217" s="56" t="n">
         <v>4944</v>
       </c>
-      <c r="N217" s="57" t="n">
+      <c r="M217" s="57" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -12086,14 +11563,13 @@
       <c r="H218" s="52" t="n"/>
       <c r="I218" s="52" t="n"/>
       <c r="J218" s="52" t="n"/>
-      <c r="K218" s="52" t="n"/>
-      <c r="L218" s="53" t="n">
+      <c r="K218" s="53" t="n">
         <v>12296</v>
       </c>
-      <c r="M218" s="56" t="n">
+      <c r="L218" s="56" t="n">
         <v>4891</v>
       </c>
-      <c r="N218" s="57" t="n">
+      <c r="M218" s="57" t="n">
         <v>99</v>
       </c>
     </row>
@@ -12126,14 +11602,13 @@
       <c r="H219" s="52" t="n"/>
       <c r="I219" s="52" t="n"/>
       <c r="J219" s="52" t="n"/>
-      <c r="K219" s="52" t="n"/>
-      <c r="L219" s="53" t="n">
+      <c r="K219" s="53" t="n">
         <v>12704</v>
       </c>
-      <c r="M219" s="56" t="n">
+      <c r="L219" s="56" t="n">
         <v>2943</v>
       </c>
-      <c r="N219" s="57" t="n">
+      <c r="M219" s="57" t="n">
         <v>99.5</v>
       </c>
     </row>
@@ -12166,14 +11641,13 @@
       <c r="H220" s="52" t="n"/>
       <c r="I220" s="52" t="n"/>
       <c r="J220" s="52" t="n"/>
-      <c r="K220" s="52" t="n"/>
-      <c r="L220" s="53" t="n">
+      <c r="K220" s="53" t="n">
         <v>3225</v>
       </c>
-      <c r="M220" s="56" t="n">
+      <c r="L220" s="56" t="n">
         <v>2292</v>
       </c>
-      <c r="N220" s="57" t="n">
+      <c r="M220" s="57" t="n">
         <v>97.5</v>
       </c>
     </row>
@@ -12206,14 +11680,13 @@
       <c r="H221" s="52" t="n"/>
       <c r="I221" s="52" t="n"/>
       <c r="J221" s="52" t="n"/>
-      <c r="K221" s="52" t="n"/>
-      <c r="L221" s="53" t="n">
+      <c r="K221" s="53" t="n">
         <v>11649</v>
       </c>
-      <c r="M221" s="56" t="n">
+      <c r="L221" s="56" t="n">
         <v>6369</v>
       </c>
-      <c r="N221" s="57" t="n">
+      <c r="M221" s="57" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -12246,14 +11719,13 @@
       <c r="H222" s="52" t="n"/>
       <c r="I222" s="52" t="n"/>
       <c r="J222" s="52" t="n"/>
-      <c r="K222" s="52" t="n"/>
-      <c r="L222" s="53" t="n">
+      <c r="K222" s="53" t="n">
         <v>13350</v>
       </c>
-      <c r="M222" s="56" t="n">
+      <c r="L222" s="56" t="n">
         <v>6325</v>
       </c>
-      <c r="N222" s="57" t="n">
+      <c r="M222" s="57" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -12286,14 +11758,13 @@
       <c r="H223" s="52" t="n"/>
       <c r="I223" s="52" t="n"/>
       <c r="J223" s="52" t="n"/>
-      <c r="K223" s="52" t="n"/>
-      <c r="L223" s="53" t="n">
+      <c r="K223" s="53" t="n">
         <v>9188</v>
       </c>
-      <c r="M223" s="56" t="n">
+      <c r="L223" s="56" t="n">
         <v>6094</v>
       </c>
-      <c r="N223" s="57" t="n">
+      <c r="M223" s="57" t="n">
         <v>97.8</v>
       </c>
     </row>
@@ -12326,14 +11797,13 @@
       <c r="H224" s="52" t="n"/>
       <c r="I224" s="52" t="n"/>
       <c r="J224" s="52" t="n"/>
-      <c r="K224" s="52" t="n"/>
-      <c r="L224" s="53" t="n">
+      <c r="K224" s="53" t="n">
         <v>12732</v>
       </c>
-      <c r="M224" s="56" t="n">
+      <c r="L224" s="56" t="n">
         <v>6613</v>
       </c>
-      <c r="N224" s="57" t="n">
+      <c r="M224" s="57" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -12366,14 +11836,13 @@
       <c r="H225" s="52" t="n"/>
       <c r="I225" s="52" t="n"/>
       <c r="J225" s="52" t="n"/>
-      <c r="K225" s="52" t="n"/>
-      <c r="L225" s="53" t="n">
+      <c r="K225" s="53" t="n">
         <v>10074</v>
       </c>
-      <c r="M225" s="56" t="n">
+      <c r="L225" s="56" t="n">
         <v>5219</v>
       </c>
-      <c r="N225" s="57" t="n">
+      <c r="M225" s="57" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -12406,14 +11875,13 @@
       <c r="H226" s="52" t="n"/>
       <c r="I226" s="52" t="n"/>
       <c r="J226" s="52" t="n"/>
-      <c r="K226" s="52" t="n"/>
-      <c r="L226" s="53" t="n">
+      <c r="K226" s="53" t="n">
         <v>6913</v>
       </c>
-      <c r="M226" s="56" t="n">
+      <c r="L226" s="56" t="n">
         <v>5259</v>
       </c>
-      <c r="N226" s="57" t="n">
+      <c r="M226" s="57" t="n">
         <v>97.5</v>
       </c>
     </row>
@@ -12446,14 +11914,13 @@
       <c r="H227" s="52" t="n"/>
       <c r="I227" s="52" t="n"/>
       <c r="J227" s="52" t="n"/>
-      <c r="K227" s="52" t="n"/>
-      <c r="L227" s="53" t="n">
+      <c r="K227" s="53" t="n">
         <v>11048</v>
       </c>
-      <c r="M227" s="56" t="n">
+      <c r="L227" s="56" t="n">
         <v>4002</v>
       </c>
-      <c r="N227" s="57" t="n">
+      <c r="M227" s="57" t="n">
         <v>99.5</v>
       </c>
     </row>
@@ -12486,14 +11953,13 @@
       <c r="H228" s="52" t="n"/>
       <c r="I228" s="52" t="n"/>
       <c r="J228" s="52" t="n"/>
-      <c r="K228" s="52" t="n"/>
-      <c r="L228" s="53" t="n">
+      <c r="K228" s="53" t="n">
         <v>12530</v>
       </c>
-      <c r="M228" s="56" t="n">
+      <c r="L228" s="56" t="n">
         <v>3162</v>
       </c>
-      <c r="N228" s="57" t="n">
+      <c r="M228" s="57" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -12526,14 +11992,13 @@
       <c r="H229" s="52" t="n"/>
       <c r="I229" s="52" t="n"/>
       <c r="J229" s="52" t="n"/>
-      <c r="K229" s="52" t="n"/>
-      <c r="L229" s="53" t="n">
+      <c r="K229" s="53" t="n">
         <v>8798</v>
       </c>
-      <c r="M229" s="56" t="n">
+      <c r="L229" s="56" t="n">
         <v>3954</v>
       </c>
-      <c r="N229" s="57" t="n">
+      <c r="M229" s="57" t="n">
         <v>99</v>
       </c>
     </row>
@@ -12566,14 +12031,13 @@
       <c r="H230" s="52" t="n"/>
       <c r="I230" s="52" t="n"/>
       <c r="J230" s="52" t="n"/>
-      <c r="K230" s="52" t="n"/>
-      <c r="L230" s="53" t="n">
+      <c r="K230" s="53" t="n">
         <v>10673</v>
       </c>
-      <c r="M230" s="56" t="n">
+      <c r="L230" s="56" t="n">
         <v>6725</v>
       </c>
-      <c r="N230" s="57" t="n">
+      <c r="M230" s="57" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -12606,14 +12070,13 @@
       <c r="H231" s="52" t="n"/>
       <c r="I231" s="52" t="n"/>
       <c r="J231" s="52" t="n"/>
-      <c r="K231" s="52" t="n"/>
-      <c r="L231" s="53" t="n">
+      <c r="K231" s="53" t="n">
         <v>14578</v>
       </c>
-      <c r="M231" s="56" t="n">
+      <c r="L231" s="56" t="n">
         <v>5801</v>
       </c>
-      <c r="N231" s="57" t="n">
+      <c r="M231" s="57" t="n">
         <v>99</v>
       </c>
     </row>
@@ -12646,14 +12109,13 @@
       <c r="H232" s="52" t="n"/>
       <c r="I232" s="52" t="n"/>
       <c r="J232" s="52" t="n"/>
-      <c r="K232" s="52" t="n"/>
-      <c r="L232" s="53" t="n">
+      <c r="K232" s="53" t="n">
         <v>8814</v>
       </c>
-      <c r="M232" s="56" t="n">
+      <c r="L232" s="56" t="n">
         <v>3099</v>
       </c>
-      <c r="N232" s="57" t="n">
+      <c r="M232" s="57" t="n">
         <v>99.40000000000001</v>
       </c>
     </row>
@@ -12686,14 +12148,13 @@
       <c r="H233" s="52" t="n"/>
       <c r="I233" s="52" t="n"/>
       <c r="J233" s="52" t="n"/>
-      <c r="K233" s="52" t="n"/>
-      <c r="L233" s="53" t="n">
+      <c r="K233" s="53" t="n">
         <v>12321</v>
       </c>
-      <c r="M233" s="56" t="n">
+      <c r="L233" s="56" t="n">
         <v>6505</v>
       </c>
-      <c r="N233" s="57" t="n">
+      <c r="M233" s="57" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -12726,14 +12187,13 @@
       <c r="H234" s="52" t="n"/>
       <c r="I234" s="52" t="n"/>
       <c r="J234" s="52" t="n"/>
-      <c r="K234" s="52" t="n"/>
-      <c r="L234" s="53" t="n">
+      <c r="K234" s="53" t="n">
         <v>9318</v>
       </c>
-      <c r="M234" s="56" t="n">
+      <c r="L234" s="56" t="n">
         <v>5266</v>
       </c>
-      <c r="N234" s="57" t="n">
+      <c r="M234" s="57" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -12766,14 +12226,13 @@
       <c r="H235" s="52" t="n"/>
       <c r="I235" s="52" t="n"/>
       <c r="J235" s="52" t="n"/>
-      <c r="K235" s="52" t="n"/>
-      <c r="L235" s="53" t="n">
+      <c r="K235" s="53" t="n">
         <v>10732</v>
       </c>
-      <c r="M235" s="56" t="n">
+      <c r="L235" s="56" t="n">
         <v>4299</v>
       </c>
-      <c r="N235" s="57" t="n">
+      <c r="M235" s="57" t="n">
         <v>99</v>
       </c>
     </row>
@@ -12806,14 +12265,13 @@
       <c r="H236" s="52" t="n"/>
       <c r="I236" s="52" t="n"/>
       <c r="J236" s="52" t="n"/>
-      <c r="K236" s="52" t="n"/>
-      <c r="L236" s="53" t="n">
+      <c r="K236" s="53" t="n">
         <v>14042</v>
       </c>
-      <c r="M236" s="56" t="n">
+      <c r="L236" s="56" t="n">
         <v>4175</v>
       </c>
-      <c r="N236" s="57" t="n">
+      <c r="M236" s="57" t="n">
         <v>99.7</v>
       </c>
     </row>
@@ -12846,14 +12304,13 @@
       <c r="H237" s="52" t="n"/>
       <c r="I237" s="52" t="n"/>
       <c r="J237" s="52" t="n"/>
-      <c r="K237" s="52" t="n"/>
-      <c r="L237" s="53" t="n">
+      <c r="K237" s="53" t="n">
         <v>11130</v>
       </c>
-      <c r="M237" s="56" t="n">
+      <c r="L237" s="56" t="n">
         <v>4825</v>
       </c>
-      <c r="N237" s="57" t="n">
+      <c r="M237" s="57" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -12886,18 +12343,15 @@
       <c r="H238" s="52" t="n">
         <v>1904</v>
       </c>
-      <c r="I238" s="52" t="n">
-        <v>2989</v>
-      </c>
+      <c r="I238" s="52" t="n"/>
       <c r="J238" s="52" t="n"/>
-      <c r="K238" s="52" t="n"/>
-      <c r="L238" s="53" t="n">
+      <c r="K238" s="53" t="n">
         <v>19449</v>
       </c>
-      <c r="M238" s="56" t="n">
+      <c r="L238" s="56" t="n">
         <v>-180</v>
       </c>
-      <c r="N238" s="57" t="n">
+      <c r="M238" s="57" t="n">
         <v>100.5</v>
       </c>
     </row>
@@ -12930,14 +12384,13 @@
       <c r="H239" s="52" t="n"/>
       <c r="I239" s="52" t="n"/>
       <c r="J239" s="52" t="n"/>
-      <c r="K239" s="52" t="n"/>
-      <c r="L239" s="53" t="n">
+      <c r="K239" s="53" t="n">
         <v>11627</v>
       </c>
-      <c r="M239" s="56" t="n">
+      <c r="L239" s="56" t="n">
         <v>2691</v>
       </c>
-      <c r="N239" s="57" t="n">
+      <c r="M239" s="57" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -12970,14 +12423,13 @@
       <c r="H240" s="52" t="n"/>
       <c r="I240" s="52" t="n"/>
       <c r="J240" s="52" t="n"/>
-      <c r="K240" s="52" t="n"/>
-      <c r="L240" s="53" t="n">
+      <c r="K240" s="53" t="n">
         <v>15495</v>
       </c>
-      <c r="M240" s="56" t="n">
+      <c r="L240" s="56" t="n">
         <v>6811</v>
       </c>
-      <c r="N240" s="57" t="n">
+      <c r="M240" s="57" t="n">
         <v>98.8</v>
       </c>
     </row>
@@ -13010,14 +12462,13 @@
       <c r="H241" s="52" t="n"/>
       <c r="I241" s="52" t="n"/>
       <c r="J241" s="52" t="n"/>
-      <c r="K241" s="52" t="n"/>
-      <c r="L241" s="53" t="n">
+      <c r="K241" s="53" t="n">
         <v>15500</v>
       </c>
-      <c r="M241" s="56" t="n">
+      <c r="L241" s="56" t="n">
         <v>7453</v>
       </c>
-      <c r="N241" s="57" t="n">
+      <c r="M241" s="57" t="n">
         <v>98.7</v>
       </c>
     </row>
@@ -13050,18 +12501,15 @@
       <c r="H242" s="52" t="n">
         <v>3053</v>
       </c>
-      <c r="I242" s="52" t="n">
-        <v>10808</v>
-      </c>
+      <c r="I242" s="52" t="n"/>
       <c r="J242" s="52" t="n"/>
-      <c r="K242" s="52" t="n"/>
-      <c r="L242" s="53" t="n">
+      <c r="K242" s="53" t="n">
         <v>8447</v>
       </c>
-      <c r="M242" s="56" t="n">
+      <c r="L242" s="56" t="n">
         <v>4967</v>
       </c>
-      <c r="N242" s="57" t="n">
+      <c r="M242" s="57" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -13094,14 +12542,13 @@
       <c r="H243" s="52" t="n"/>
       <c r="I243" s="52" t="n"/>
       <c r="J243" s="52" t="n"/>
-      <c r="K243" s="52" t="n"/>
-      <c r="L243" s="53" t="n">
+      <c r="K243" s="53" t="n">
         <v>12301</v>
       </c>
-      <c r="M243" s="56" t="n">
+      <c r="L243" s="56" t="n">
         <v>2281</v>
       </c>
-      <c r="N243" s="57" t="n">
+      <c r="M243" s="57" t="n">
         <v>99.7</v>
       </c>
     </row>
@@ -13134,14 +12581,13 @@
       <c r="H244" s="52" t="n"/>
       <c r="I244" s="52" t="n"/>
       <c r="J244" s="52" t="n"/>
-      <c r="K244" s="52" t="n"/>
-      <c r="L244" s="53" t="n">
+      <c r="K244" s="53" t="n">
         <v>20438</v>
       </c>
-      <c r="M244" s="56" t="n">
+      <c r="L244" s="56" t="n">
         <v>7237</v>
       </c>
-      <c r="N244" s="57" t="n">
+      <c r="M244" s="57" t="n">
         <v>99.2</v>
       </c>
     </row>
@@ -13174,14 +12620,13 @@
       <c r="H245" s="52" t="n"/>
       <c r="I245" s="52" t="n"/>
       <c r="J245" s="52" t="n"/>
-      <c r="K245" s="52" t="n"/>
-      <c r="L245" s="53" t="n">
+      <c r="K245" s="53" t="n">
         <v>14037</v>
       </c>
-      <c r="M245" s="56" t="n">
+      <c r="L245" s="56" t="n">
         <v>4507</v>
       </c>
-      <c r="N245" s="57" t="n">
+      <c r="M245" s="57" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
@@ -13214,14 +12659,13 @@
       <c r="H246" s="52" t="n"/>
       <c r="I246" s="52" t="n"/>
       <c r="J246" s="52" t="n"/>
-      <c r="K246" s="52" t="n"/>
-      <c r="L246" s="53" t="n">
+      <c r="K246" s="53" t="n">
         <v>12796</v>
       </c>
-      <c r="M246" s="56" t="n">
+      <c r="L246" s="56" t="n">
         <v>10223</v>
       </c>
-      <c r="N246" s="57" t="n">
+      <c r="M246" s="57" t="n">
         <v>97.40000000000001</v>
       </c>
     </row>
@@ -13254,14 +12698,13 @@
       <c r="H247" s="52" t="n"/>
       <c r="I247" s="52" t="n"/>
       <c r="J247" s="52" t="n"/>
-      <c r="K247" s="52" t="n"/>
-      <c r="L247" s="53" t="n">
+      <c r="K247" s="53" t="n">
         <v>14970</v>
       </c>
-      <c r="M247" s="56" t="n">
+      <c r="L247" s="56" t="n">
         <v>9841</v>
       </c>
-      <c r="N247" s="57" t="n">
+      <c r="M247" s="57" t="n">
         <v>97.7</v>
       </c>
     </row>
@@ -13294,14 +12737,13 @@
       <c r="H248" s="52" t="n"/>
       <c r="I248" s="52" t="n"/>
       <c r="J248" s="52" t="n"/>
-      <c r="K248" s="52" t="n"/>
-      <c r="L248" s="53" t="n">
+      <c r="K248" s="53" t="n">
         <v>23680</v>
       </c>
-      <c r="M248" s="56" t="n">
+      <c r="L248" s="56" t="n">
         <v>26886</v>
       </c>
-      <c r="N248" s="57" t="n">
+      <c r="M248" s="57" t="n">
         <v>95.7</v>
       </c>
     </row>
@@ -13334,14 +12776,13 @@
       <c r="H249" s="52" t="n"/>
       <c r="I249" s="52" t="n"/>
       <c r="J249" s="52" t="n"/>
-      <c r="K249" s="52" t="n"/>
-      <c r="L249" s="53" t="n">
+      <c r="K249" s="53" t="n">
         <v>12853</v>
       </c>
-      <c r="M249" s="56" t="n">
+      <c r="L249" s="56" t="n">
         <v>8412</v>
       </c>
-      <c r="N249" s="57" t="n">
+      <c r="M249" s="57" t="n">
         <v>97.90000000000001</v>
       </c>
     </row>
@@ -13374,14 +12815,13 @@
       <c r="H250" s="52" t="n"/>
       <c r="I250" s="52" t="n"/>
       <c r="J250" s="52" t="n"/>
-      <c r="K250" s="52" t="n"/>
-      <c r="L250" s="53" t="n">
+      <c r="K250" s="53" t="n">
         <v>12934</v>
       </c>
-      <c r="M250" s="56" t="n">
+      <c r="L250" s="56" t="n">
         <v>8152</v>
       </c>
-      <c r="N250" s="57" t="n">
+      <c r="M250" s="57" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -13414,14 +12854,13 @@
       <c r="H251" s="52" t="n"/>
       <c r="I251" s="52" t="n"/>
       <c r="J251" s="52" t="n"/>
-      <c r="K251" s="52" t="n"/>
-      <c r="L251" s="53" t="n">
+      <c r="K251" s="53" t="n">
         <v>17904</v>
       </c>
-      <c r="M251" s="56" t="n">
+      <c r="L251" s="56" t="n">
         <v>13862</v>
       </c>
-      <c r="N251" s="57" t="n">
+      <c r="M251" s="57" t="n">
         <v>97.40000000000001</v>
       </c>
     </row>
@@ -13454,14 +12893,13 @@
       <c r="H252" s="52" t="n"/>
       <c r="I252" s="52" t="n"/>
       <c r="J252" s="52" t="n"/>
-      <c r="K252" s="52" t="n"/>
-      <c r="L252" s="53" t="n">
+      <c r="K252" s="53" t="n">
         <v>16901</v>
       </c>
-      <c r="M252" s="56" t="n">
+      <c r="L252" s="56" t="n">
         <v>10075</v>
       </c>
-      <c r="N252" s="57" t="n">
+      <c r="M252" s="57" t="n">
         <v>98.09999999999999</v>
       </c>
     </row>
@@ -13479,7 +12917,6 @@
       <c r="K253" s="60" t="n"/>
       <c r="L253" s="60" t="n"/>
       <c r="M253" s="60" t="n"/>
-      <c r="N253" s="60" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="60" t="n"/>
@@ -13495,7 +12932,6 @@
       <c r="K254" s="60" t="n"/>
       <c r="L254" s="60" t="n"/>
       <c r="M254" s="60" t="n"/>
-      <c r="N254" s="60" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="60" t="n"/>
@@ -13511,7 +12947,6 @@
       <c r="K255" s="60" t="n"/>
       <c r="L255" s="60" t="n"/>
       <c r="M255" s="60" t="n"/>
-      <c r="N255" s="60" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="60" t="n"/>
@@ -13527,7 +12962,6 @@
       <c r="K256" s="60" t="n"/>
       <c r="L256" s="60" t="n"/>
       <c r="M256" s="60" t="n"/>
-      <c r="N256" s="60" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="60" t="n"/>
@@ -13543,7 +12977,6 @@
       <c r="K257" s="60" t="n"/>
       <c r="L257" s="60" t="n"/>
       <c r="M257" s="60" t="n"/>
-      <c r="N257" s="60" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="60" t="n"/>
@@ -13559,7 +12992,6 @@
       <c r="K258" s="60" t="n"/>
       <c r="L258" s="60" t="n"/>
       <c r="M258" s="60" t="n"/>
-      <c r="N258" s="60" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="60" t="n"/>
@@ -13575,7 +13007,6 @@
       <c r="K259" s="60" t="n"/>
       <c r="L259" s="60" t="n"/>
       <c r="M259" s="60" t="n"/>
-      <c r="N259" s="60" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="60" t="n"/>
@@ -13591,7 +13022,6 @@
       <c r="K260" s="60" t="n"/>
       <c r="L260" s="60" t="n"/>
       <c r="M260" s="60" t="n"/>
-      <c r="N260" s="60" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="60" t="n"/>
@@ -13607,7 +13037,6 @@
       <c r="K261" s="60" t="n"/>
       <c r="L261" s="60" t="n"/>
       <c r="M261" s="60" t="n"/>
-      <c r="N261" s="60" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="60" t="n"/>
@@ -13623,7 +13052,6 @@
       <c r="K262" s="60" t="n"/>
       <c r="L262" s="60" t="n"/>
       <c r="M262" s="60" t="n"/>
-      <c r="N262" s="60" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="60" t="n"/>
@@ -13639,7 +13067,6 @@
       <c r="K263" s="60" t="n"/>
       <c r="L263" s="60" t="n"/>
       <c r="M263" s="60" t="n"/>
-      <c r="N263" s="60" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="60" t="n"/>
@@ -13655,7 +13082,6 @@
       <c r="K264" s="60" t="n"/>
       <c r="L264" s="60" t="n"/>
       <c r="M264" s="60" t="n"/>
-      <c r="N264" s="60" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="60" t="n"/>
@@ -13671,7 +13097,6 @@
       <c r="K265" s="60" t="n"/>
       <c r="L265" s="60" t="n"/>
       <c r="M265" s="60" t="n"/>
-      <c r="N265" s="60" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="60" t="n"/>
@@ -13687,7 +13112,6 @@
       <c r="K266" s="60" t="n"/>
       <c r="L266" s="60" t="n"/>
       <c r="M266" s="60" t="n"/>
-      <c r="N266" s="60" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="60" t="n"/>
@@ -13703,7 +13127,6 @@
       <c r="K267" s="60" t="n"/>
       <c r="L267" s="60" t="n"/>
       <c r="M267" s="60" t="n"/>
-      <c r="N267" s="60" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="60" t="n"/>
@@ -13719,7 +13142,6 @@
       <c r="K268" s="60" t="n"/>
       <c r="L268" s="60" t="n"/>
       <c r="M268" s="60" t="n"/>
-      <c r="N268" s="60" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="60" t="n"/>
@@ -13735,7 +13157,6 @@
       <c r="K269" s="60" t="n"/>
       <c r="L269" s="60" t="n"/>
       <c r="M269" s="60" t="n"/>
-      <c r="N269" s="60" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="60" t="n"/>
@@ -13751,7 +13172,6 @@
       <c r="K270" s="60" t="n"/>
       <c r="L270" s="60" t="n"/>
       <c r="M270" s="60" t="n"/>
-      <c r="N270" s="60" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="60" t="n"/>
@@ -13767,7 +13187,6 @@
       <c r="K271" s="60" t="n"/>
       <c r="L271" s="60" t="n"/>
       <c r="M271" s="60" t="n"/>
-      <c r="N271" s="60" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="60" t="n"/>
@@ -13783,7 +13202,6 @@
       <c r="K272" s="60" t="n"/>
       <c r="L272" s="60" t="n"/>
       <c r="M272" s="60" t="n"/>
-      <c r="N272" s="60" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="60" t="n"/>
@@ -13799,7 +13217,6 @@
       <c r="K273" s="60" t="n"/>
       <c r="L273" s="60" t="n"/>
       <c r="M273" s="60" t="n"/>
-      <c r="N273" s="60" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="60" t="n"/>
@@ -13815,7 +13232,6 @@
       <c r="K274" s="60" t="n"/>
       <c r="L274" s="60" t="n"/>
       <c r="M274" s="60" t="n"/>
-      <c r="N274" s="60" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="60" t="n"/>
@@ -13831,7 +13247,6 @@
       <c r="K275" s="60" t="n"/>
       <c r="L275" s="60" t="n"/>
       <c r="M275" s="60" t="n"/>
-      <c r="N275" s="60" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="60" t="n"/>
@@ -13847,7 +13262,6 @@
       <c r="K276" s="60" t="n"/>
       <c r="L276" s="60" t="n"/>
       <c r="M276" s="60" t="n"/>
-      <c r="N276" s="60" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="60" t="n"/>
@@ -13863,7 +13277,6 @@
       <c r="K277" s="60" t="n"/>
       <c r="L277" s="60" t="n"/>
       <c r="M277" s="60" t="n"/>
-      <c r="N277" s="60" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="60" t="n"/>
@@ -13879,7 +13292,6 @@
       <c r="K278" s="60" t="n"/>
       <c r="L278" s="60" t="n"/>
       <c r="M278" s="60" t="n"/>
-      <c r="N278" s="60" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="60" t="n"/>
@@ -13895,7 +13307,6 @@
       <c r="K279" s="60" t="n"/>
       <c r="L279" s="60" t="n"/>
       <c r="M279" s="60" t="n"/>
-      <c r="N279" s="60" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="60" t="n"/>
@@ -13911,7 +13322,6 @@
       <c r="K280" s="60" t="n"/>
       <c r="L280" s="60" t="n"/>
       <c r="M280" s="60" t="n"/>
-      <c r="N280" s="60" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="60" t="n"/>
@@ -13927,7 +13337,6 @@
       <c r="K281" s="60" t="n"/>
       <c r="L281" s="60" t="n"/>
       <c r="M281" s="60" t="n"/>
-      <c r="N281" s="60" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="60" t="n"/>
@@ -13943,7 +13352,6 @@
       <c r="K282" s="60" t="n"/>
       <c r="L282" s="60" t="n"/>
       <c r="M282" s="60" t="n"/>
-      <c r="N282" s="60" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="60" t="n"/>
@@ -13959,7 +13367,6 @@
       <c r="K283" s="60" t="n"/>
       <c r="L283" s="60" t="n"/>
       <c r="M283" s="60" t="n"/>
-      <c r="N283" s="60" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="60" t="n"/>
@@ -13975,7 +13382,6 @@
       <c r="K284" s="60" t="n"/>
       <c r="L284" s="60" t="n"/>
       <c r="M284" s="60" t="n"/>
-      <c r="N284" s="60" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="60" t="n"/>
@@ -13991,7 +13397,6 @@
       <c r="K285" s="60" t="n"/>
       <c r="L285" s="60" t="n"/>
       <c r="M285" s="60" t="n"/>
-      <c r="N285" s="60" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="60" t="n"/>
@@ -14007,7 +13412,6 @@
       <c r="K286" s="60" t="n"/>
       <c r="L286" s="60" t="n"/>
       <c r="M286" s="60" t="n"/>
-      <c r="N286" s="60" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="60" t="n"/>
@@ -14023,7 +13427,6 @@
       <c r="K287" s="60" t="n"/>
       <c r="L287" s="60" t="n"/>
       <c r="M287" s="60" t="n"/>
-      <c r="N287" s="60" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="60" t="n"/>
@@ -14039,7 +13442,6 @@
       <c r="K288" s="60" t="n"/>
       <c r="L288" s="60" t="n"/>
       <c r="M288" s="60" t="n"/>
-      <c r="N288" s="60" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="60" t="n"/>
@@ -14055,7 +13457,6 @@
       <c r="K289" s="60" t="n"/>
       <c r="L289" s="60" t="n"/>
       <c r="M289" s="60" t="n"/>
-      <c r="N289" s="60" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="60" t="n"/>
@@ -14071,7 +13472,6 @@
       <c r="K290" s="60" t="n"/>
       <c r="L290" s="60" t="n"/>
       <c r="M290" s="60" t="n"/>
-      <c r="N290" s="60" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="60" t="n"/>
@@ -14087,7 +13487,6 @@
       <c r="K291" s="60" t="n"/>
       <c r="L291" s="60" t="n"/>
       <c r="M291" s="60" t="n"/>
-      <c r="N291" s="60" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="60" t="n"/>
@@ -14103,7 +13502,6 @@
       <c r="K292" s="60" t="n"/>
       <c r="L292" s="60" t="n"/>
       <c r="M292" s="60" t="n"/>
-      <c r="N292" s="60" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="60" t="n"/>
@@ -14119,7 +13517,6 @@
       <c r="K293" s="60" t="n"/>
       <c r="L293" s="60" t="n"/>
       <c r="M293" s="60" t="n"/>
-      <c r="N293" s="60" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="60" t="n"/>
@@ -14135,7 +13532,6 @@
       <c r="K294" s="60" t="n"/>
       <c r="L294" s="60" t="n"/>
       <c r="M294" s="60" t="n"/>
-      <c r="N294" s="60" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="60" t="n"/>
@@ -14151,7 +13547,6 @@
       <c r="K295" s="60" t="n"/>
       <c r="L295" s="60" t="n"/>
       <c r="M295" s="60" t="n"/>
-      <c r="N295" s="60" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="60" t="n"/>
@@ -14167,7 +13562,6 @@
       <c r="K296" s="60" t="n"/>
       <c r="L296" s="60" t="n"/>
       <c r="M296" s="60" t="n"/>
-      <c r="N296" s="60" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="60" t="n"/>
@@ -14183,7 +13577,6 @@
       <c r="K297" s="60" t="n"/>
       <c r="L297" s="60" t="n"/>
       <c r="M297" s="60" t="n"/>
-      <c r="N297" s="60" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="60" t="n"/>
@@ -14199,7 +13592,6 @@
       <c r="K298" s="60" t="n"/>
       <c r="L298" s="60" t="n"/>
       <c r="M298" s="60" t="n"/>
-      <c r="N298" s="60" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="60" t="n"/>
@@ -14215,7 +13607,6 @@
       <c r="K299" s="60" t="n"/>
       <c r="L299" s="60" t="n"/>
       <c r="M299" s="60" t="n"/>
-      <c r="N299" s="60" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="60" t="n"/>
@@ -14231,7 +13622,6 @@
       <c r="K300" s="60" t="n"/>
       <c r="L300" s="60" t="n"/>
       <c r="M300" s="60" t="n"/>
-      <c r="N300" s="60" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="60" t="n"/>
@@ -14247,7 +13637,6 @@
       <c r="K301" s="60" t="n"/>
       <c r="L301" s="60" t="n"/>
       <c r="M301" s="60" t="n"/>
-      <c r="N301" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
